--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF42DF0-B96E-BF48-88F9-4F810A0FF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14234EB1-98E8-3E44-B1AF-037F6CB95FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="980" windowWidth="32760" windowHeight="20500" activeTab="1" xr2:uid="{024C4FC4-B888-4944-B532-B224FCAEABAE}"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="33600" windowHeight="20520" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
   <sheets>
     <sheet name="Items and code" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="stdform">STD!$A:$B</definedName>
-    <definedName name="units">Factors!$C$3:$F$18</definedName>
+    <definedName name="units">Factors!$C$3:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="230">
   <si>
     <t>ITM_PINTLQtoML</t>
   </si>
@@ -641,6 +641,96 @@
   </si>
   <si>
     <t>temp</t>
+  </si>
+  <si>
+    <t>ITM_MLtoIN3</t>
+  </si>
+  <si>
+    <t>ITM_IN3toML</t>
+  </si>
+  <si>
+    <t>ITM_FT3toGLUK</t>
+  </si>
+  <si>
+    <t>ITM_GLUKtoFT3</t>
+  </si>
+  <si>
+    <t>ITM_LtoFT3</t>
+  </si>
+  <si>
+    <t>ITM_FT3toL</t>
+  </si>
+  <si>
+    <t>ITM_LtoQTUS</t>
+  </si>
+  <si>
+    <t>ITM_QTUStoL</t>
+  </si>
+  <si>
+    <t>mℓ→in.Ⅳ</t>
+  </si>
+  <si>
+    <t>in.Ⅳ→mℓ</t>
+  </si>
+  <si>
+    <t>ft.Ⅳ→gal␭</t>
+  </si>
+  <si>
+    <t>gal␭→ft.Ⅳ</t>
+  </si>
+  <si>
+    <t>ℓ→ft.Ⅳ</t>
+  </si>
+  <si>
+    <t>ft.Ⅳ→ℓ</t>
+  </si>
+  <si>
+    <t>ℓ→qt.␮</t>
+  </si>
+  <si>
+    <t>qt.␮→ℓ</t>
+  </si>
+  <si>
+    <t>IN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</t>
+  </si>
+  <si>
+    <t>"m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3</t>
+  </si>
+  <si>
+    <t>"ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK</t>
+  </si>
+  <si>
+    <t>"GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</t>
+  </si>
+  <si>
+    <t>STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3</t>
+  </si>
+  <si>
+    <t>"ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre</t>
+  </si>
+  <si>
+    <t>STD_litre STD_RIGHT_ARROW "qt" STD_US</t>
+  </si>
+  <si>
+    <t>"qt" STD_US STD_RIGHT_ARROW STD_litre</t>
+  </si>
+  <si>
+    <t>FT3</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>(ft × 12 × 2.54)^3</t>
+  </si>
+  <si>
+    <t>(in x 2.54) ^ 3</t>
+  </si>
+  <si>
+    <t>ml x 1000</t>
   </si>
 </sst>
 </file>
@@ -652,7 +742,7 @@
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0000000000000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -754,8 +844,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,8 +933,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -992,11 +1121,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1118,7 +1273,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1127,7 +1281,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1162,15 +1315,46 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1505,17 +1689,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8086E2D2-A619-CD41-963B-CA5F79ED1F95}">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="58.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" style="79" customWidth="1"/>
+    <col min="6" max="6" width="58.83203125" style="79" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.83203125" style="79" customWidth="1"/>
     <col min="8" max="8" width="225" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="20.5" style="79" customWidth="1"/>
+    <col min="10" max="11" width="10.83203125" style="79"/>
     <col min="12" max="12" width="144.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1523,7 +1709,7 @@
     <row r="1" spans="1:14" ht="16">
       <c r="A1"/>
       <c r="B1"/>
-      <c r="F1">
+      <c r="F1" s="79">
         <f>LEN(F24)</f>
         <v>57</v>
       </c>
@@ -1536,7 +1722,7 @@
       <c r="B2"/>
     </row>
     <row r="3" spans="1:14" ht="16">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>197</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1545,1694 +1731,2102 @@
       <c r="C3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="I3" s="69" t="s">
+      <c r="I3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="J3" s="69" t="s">
+      <c r="J3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="69" t="s">
+      <c r="K3" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="L3" s="54" t="s">
+      <c r="L3" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="N3" s="54" t="s">
+      <c r="N3" s="52" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="66" t="str">
+      <c r="D4" s="64" t="str">
         <f>VLOOKUP(A4,Factors!D:K,8,0)</f>
         <v>constFactorCupcFzus</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" s="79" t="str">
         <f>VLOOKUP(A4,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F4" s="43" t="str">
-        <f t="shared" ref="F4:F35" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
+      <c r="F4" s="81" t="str">
+        <f t="shared" ref="F4:F43" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G4" s="43" t="str">
+      <c r="G4" s="81" t="str">
         <f>MID(F4,1,SEARCH("STD_RIGHT_ARROW",F4)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H4" s="51" t="str">
+      <c r="H4" s="49" t="str">
         <f>"/* NNNN */  UNIT_CONV("&amp;D4&amp;","&amp;REPT(CHAR(32),21-LEN(D4))&amp;"    "&amp;E4&amp;",      "&amp;F4&amp;","&amp;REPT(CHAR(32),60-LEN(F4))&amp;G4&amp;REPT(CHAR(32),60-LEN(G4))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcFzus,      multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="82">
         <f>VLOOKUP(A4,Factors!D:G,4,0)</f>
         <v>8.0000079970243636</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J4" s="79" t="str">
         <f>SUBSTITUTE(TEXT(I4,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>8.000007997024360000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K4" s="50" t="str">
+      <c r="K4" s="82" t="str">
         <f>VLOOKUP(A4,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
-      <c r="L4" s="52" t="str">
+      <c r="L4" s="50" t="str">
         <f>IF(E4="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K4&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K4))&amp;CHAR(34)&amp;"+"&amp;J4&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("CupcFzus",      "+8.000007997024360000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N4" s="68" t="str">
+      <c r="N4" s="65" t="str">
         <f>"    ["&amp;D4&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K4&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcFzus] = &amp;const_CupcFzus,</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="66" t="str">
+      <c r="D5" s="64" t="str">
         <f>VLOOKUP(A5,Factors!D:K,8,0)</f>
         <v>constFactorCupcMl</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" s="79" t="str">
         <f>VLOOKUP(A5,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F5" s="43" t="str">
+      <c r="F5" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G5" s="43" t="str">
-        <f t="shared" ref="G5:G35" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
+      <c r="G5" s="81" t="str">
+        <f t="shared" ref="G5:G43" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H5" s="51" t="str">
-        <f t="shared" ref="H5:H35" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
+      <c r="H5" s="49" t="str">
+        <f t="shared" ref="H5:H43" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcMl,        multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="79">
         <f>VLOOKUP(A5,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J5" t="str">
-        <f t="shared" ref="J5:J35" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+      <c r="J5" s="79" t="str">
+        <f t="shared" ref="J5:J43" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K5" s="50" t="str">
+      <c r="K5" s="82" t="str">
         <f>VLOOKUP(A5,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
-      <c r="L5" s="52" t="str">
-        <f t="shared" ref="L5:L35" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
+      <c r="L5" s="50" t="str">
+        <f t="shared" ref="L5:L43" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("CupcMl",        "+2.365882365000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N5" s="68" t="str">
-        <f t="shared" ref="N5:N35" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
+      <c r="N5" s="65" t="str">
+        <f t="shared" ref="N5:N43" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcMl] = &amp;const_CupcMl,</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="66" t="str">
+      <c r="D6" s="64" t="str">
         <f>VLOOKUP(A6,Factors!D:K,8,0)</f>
         <v>constFactorCupukFzuk</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" s="79" t="str">
         <f>VLOOKUP(A6,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F6" s="43" t="str">
+      <c r="F6" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G6" s="43" t="str">
+      <c r="G6" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H6" s="51" t="str">
+      <c r="H6" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukFzuk,     multiply,      "cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="79">
         <f>VLOOKUP(A6,Factors!D:G,4,0)</f>
         <v>9.9999868018625211</v>
       </c>
-      <c r="J6" t="str">
+      <c r="J6" s="79" t="str">
         <f t="shared" si="3"/>
         <v>9.999986801862520000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K6" s="50" t="str">
+      <c r="K6" s="82" t="str">
         <f>VLOOKUP(A6,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
-      <c r="L6" s="52" t="str">
+      <c r="L6" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("CupukFzuk",     "+9.999986801862520000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N6" s="68" t="str">
+      <c r="N6" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorCupukFzuk] = &amp;const_CupukFzuk,</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="64" t="str">
         <f>VLOOKUP(A7,Factors!D:K,8,0)</f>
         <v>constFactorCupukMl</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" s="79" t="str">
         <f>VLOOKUP(A7,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F7" s="43" t="str">
+      <c r="F7" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G7" s="43" t="str">
+      <c r="G7" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H7" s="51" t="str">
+      <c r="H7" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukMl,       multiply,      "cup" STD_UK STD_RIGHT_ARROW "ml",                           "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="79">
         <f>VLOOKUP(A7,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J7" s="79" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K7" s="50" t="str">
+      <c r="K7" s="82" t="str">
         <f>VLOOKUP(A7,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
-      <c r="L7" s="52" t="str">
+      <c r="L7" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("CupukMl",       "+2.841306250000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N7" s="68" t="str">
+      <c r="N7" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorCupukMl] = &amp;const_CupukMl,</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="66" t="str">
+      <c r="D8" s="64" t="str">
         <f>VLOOKUP(A8,Factors!D:K,8,0)</f>
         <v>constFactorFzukCupuk</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8" s="79" t="str">
         <f>VLOOKUP(A8,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F8" s="43" t="str">
+      <c r="F8" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G8" s="43" t="str">
+      <c r="G8" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H8" s="51" t="str">
+      <c r="H8" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukCupuk,       divide,      "floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="79">
         <f>VLOOKUP(A8,Factors!D:G,4,0)</f>
         <v>9.9999868018625211</v>
       </c>
-      <c r="J8" t="str">
+      <c r="J8" s="79" t="str">
         <f t="shared" si="3"/>
         <v>9.999986801862520000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K8" s="50" t="str">
+      <c r="K8" s="82" t="str">
         <f>VLOOKUP(A8,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
-      <c r="L8" s="52" t="str">
+      <c r="L8" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="68" t="str">
+      <c r="N8" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukCupuk] = &amp;const_CupukFzuk,</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="66" t="str">
+      <c r="D9" s="64" t="str">
         <f>VLOOKUP(A9,Factors!D:K,8,0)</f>
         <v>constFactorFzukTbspuk</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" s="79" t="str">
         <f>VLOOKUP(A9,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F9" s="43" t="str">
+      <c r="F9" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G9" s="43" t="str">
+      <c r="G9" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H9" s="51" t="str">
+      <c r="H9" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTbspuk,    multiply,      "floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK,                 "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="79">
         <f>VLOOKUP(A9,Factors!D:G,4,0)</f>
         <v>1.6000021117047836</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J9" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.600002111704780000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K9" s="50" t="str">
+      <c r="K9" s="82" t="str">
         <f>VLOOKUP(A9,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
-      <c r="L9" s="52" t="str">
+      <c r="L9" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("FzukTbspuk",    "+1.600002111704780000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N9" s="68" t="str">
+      <c r="N9" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukTbspuk] = &amp;const_FzukTbspuk,</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="66" t="str">
+      <c r="D10" s="64" t="str">
         <f>VLOOKUP(A10,Factors!D:K,8,0)</f>
         <v>constFactorFzukTspuk</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" s="79" t="str">
         <f>VLOOKUP(A10,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F10" s="43" t="str">
+      <c r="F10" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G10" s="43" t="str">
+      <c r="G10" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H10" s="51" t="str">
+      <c r="H10" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTspuk,     multiply,      "floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="79">
         <f>VLOOKUP(A10,Factors!D:G,4,0)</f>
         <v>4.8000063351143778</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J10" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K10" s="50" t="str">
+      <c r="K10" s="82" t="str">
         <f>VLOOKUP(A10,Factors!D:N,11,0)</f>
         <v>FzukTspuk</v>
       </c>
-      <c r="L10" s="52" t="str">
+      <c r="L10" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("FzukTspuk",     "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N10" s="68" t="str">
+      <c r="N10" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukTspuk] = &amp;const_FzukTspuk,</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="66" t="str">
+      <c r="D11" s="64" t="str">
         <f>VLOOKUP(A11,Factors!D:K,8,0)</f>
         <v>constFactorFzusCupc</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11" s="79" t="str">
         <f>VLOOKUP(A11,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F11" s="43" t="str">
+      <c r="F11" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G11" s="43" t="str">
+      <c r="G11" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H11" s="51" t="str">
+      <c r="H11" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusCupc,        divide,      "floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="79">
         <f>VLOOKUP(A11,Factors!D:G,4,0)</f>
         <v>8.0000079970243636</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J11" s="79" t="str">
         <f t="shared" si="3"/>
         <v>8.000007997024360000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K11" s="50" t="str">
+      <c r="K11" s="82" t="str">
         <f>VLOOKUP(A11,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
-      <c r="L11" s="52" t="str">
+      <c r="L11" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N11" s="68" t="str">
+      <c r="N11" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusCupc] = &amp;const_CupcFzus,</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="66" t="str">
+      <c r="D12" s="64" t="str">
         <f>VLOOKUP(A12,Factors!D:K,8,0)</f>
         <v>constFactorFzusTbspc</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12" s="79" t="str">
         <f>VLOOKUP(A12,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F12" s="43" t="str">
+      <c r="F12" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G12" s="43" t="str">
+      <c r="G12" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H12" s="51" t="str">
+      <c r="H12" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTbspc,     multiply,      "floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,       "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="79">
         <f>VLOOKUP(A12,Factors!D:G,4,0)</f>
         <v>1.9999980007459077</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J12" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.999998000745910000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K12" s="50" t="str">
+      <c r="K12" s="82" t="str">
         <f>VLOOKUP(A12,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
-      <c r="L12" s="52" t="str">
+      <c r="L12" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("FzusTbspc",     "+1.999998000745910000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N12" s="68" t="str">
+      <c r="N12" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusTbspc] = &amp;const_FzusTbspc,</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="71" t="s">
+      <c r="B13" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="66" t="str">
+      <c r="D13" s="64" t="str">
         <f>VLOOKUP(A13,Factors!D:K,8,0)</f>
         <v>constFactorFzusTspc</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13" s="79" t="str">
         <f>VLOOKUP(A13,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F13" s="43" t="str">
+      <c r="F13" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G13" s="43" t="str">
+      <c r="G13" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H13" s="51" t="str">
+      <c r="H13" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTspc,      multiply,      "floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="79">
         <f>VLOOKUP(A13,Factors!D:G,4,0)</f>
         <v>5.9999940022377229</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J13" s="79" t="str">
         <f t="shared" si="3"/>
         <v>5.999994002237720000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K13" s="50" t="str">
+      <c r="K13" s="82" t="str">
         <f>VLOOKUP(A13,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
-      <c r="L13" s="52" t="str">
+      <c r="L13" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("FzusTspc",      "+5.999994002237720000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N13" s="68" t="str">
+      <c r="N13" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusTspc] = &amp;const_FzusTspc,</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="66" t="str">
+      <c r="D14" s="64" t="str">
         <f>VLOOKUP(A14,Factors!D:K,8,0)</f>
         <v>constFactorMlCupc</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" s="79" t="str">
         <f>VLOOKUP(A14,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F14" s="43" t="str">
+      <c r="F14" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G14" s="43" t="str">
+      <c r="G14" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H14" s="51" t="str">
+      <c r="H14" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupc,          divide,      "ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="79">
         <f>VLOOKUP(A14,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J14" s="79" t="str">
         <f t="shared" si="3"/>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K14" s="50" t="str">
+      <c r="K14" s="82" t="str">
         <f>VLOOKUP(A14,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
-      <c r="L14" s="52" t="str">
+      <c r="L14" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N14" s="68" t="str">
+      <c r="N14" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlCupc] = &amp;const_CupcMl,</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="66" t="str">
+      <c r="D15" s="64" t="str">
         <f>VLOOKUP(A15,Factors!D:K,8,0)</f>
         <v>constFactorMlCupuk</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15" s="79" t="str">
         <f>VLOOKUP(A15,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F15" s="43" t="str">
+      <c r="F15" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G15" s="43" t="str">
+      <c r="G15" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H15" s="51" t="str">
+      <c r="H15" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupuk,         divide,      "ml" STD_RIGHT_ARROW "cup" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="79">
         <f>VLOOKUP(A15,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J15" t="str">
+      <c r="J15" s="79" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K15" s="50" t="str">
+      <c r="K15" s="82" t="str">
         <f>VLOOKUP(A15,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
-      <c r="L15" s="52" t="str">
+      <c r="L15" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N15" s="68" t="str">
+      <c r="N15" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlCupuk] = &amp;const_CupukMl,</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="66" t="str">
+      <c r="D16" s="64" t="str">
         <f>VLOOKUP(A16,Factors!D:K,8,0)</f>
         <v>constFactorMlPintlq</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16" s="79" t="str">
         <f>VLOOKUP(A16,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F16" s="43" t="str">
+      <c r="F16" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q</v>
       </c>
-      <c r="G16" s="43" t="str">
+      <c r="G16" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H16" s="51" t="str">
+      <c r="H16" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintlq,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q,   "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="79">
         <f>VLOOKUP(A16,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J16" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K16" s="50" t="str">
+      <c r="K16" s="82" t="str">
         <f>VLOOKUP(A16,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
-      <c r="L16" s="52" t="str">
+      <c r="L16" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N16" s="68" t="str">
+      <c r="N16" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlPintlq] = &amp;const_PintlqMl,</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="71" t="s">
+      <c r="B17" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="66" t="str">
+      <c r="D17" s="64" t="str">
         <f>VLOOKUP(A17,Factors!D:K,8,0)</f>
         <v>constFactorMlPintuk</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17" s="79" t="str">
         <f>VLOOKUP(A17,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F17" s="43" t="str">
+      <c r="F17" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_UK</v>
       </c>
-      <c r="G17" s="43" t="str">
+      <c r="G17" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H17" s="51" t="str">
+      <c r="H17" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintuk,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="79">
         <f>VLOOKUP(A17,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J17" s="79" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K17" s="50" t="str">
+      <c r="K17" s="82" t="str">
         <f>VLOOKUP(A17,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
-      <c r="L17" s="52" t="str">
+      <c r="L17" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N17" s="68" t="str">
+      <c r="N17" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlPintuk] = &amp;const_PintukMl,</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="70" t="s">
+      <c r="A18" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="66" t="str">
+      <c r="D18" s="64" t="str">
         <f>VLOOKUP(A18,Factors!D:K,8,0)</f>
         <v>constFactorMlQt</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18" s="79" t="str">
         <f>VLOOKUP(A18,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F18" s="43" t="str">
+      <c r="F18" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "qt." STD_UK</v>
       </c>
-      <c r="G18" s="43" t="str">
+      <c r="G18" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H18" s="51" t="str">
+      <c r="H18" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlQt,            divide,      "ml" STD_RIGHT_ARROW "qt." STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="79">
         <f>VLOOKUP(A18,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J18" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K18" s="50" t="str">
+      <c r="K18" s="82" t="str">
         <f>VLOOKUP(A18,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
-      <c r="L18" s="52" t="str">
+      <c r="L18" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N18" s="68" t="str">
+      <c r="N18" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlQt] = &amp;const_QtMl,</v>
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="66" t="str">
+      <c r="D19" s="64" t="str">
         <f>VLOOKUP(A19,Factors!D:K,8,0)</f>
         <v>constFactorMlQtus</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19" s="79" t="str">
         <f>VLOOKUP(A19,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F19" s="43" t="str">
+      <c r="F19" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "qt." STD_US</v>
       </c>
-      <c r="G19" s="43" t="str">
+      <c r="G19" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H19" s="51" t="str">
+      <c r="H19" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlQtus,          divide,      "ml" STD_RIGHT_ARROW "qt." STD_US,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="79">
         <f>VLOOKUP(A19,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J19" s="79" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K19" s="50" t="str">
+      <c r="K19" s="82" t="str">
         <f>VLOOKUP(A19,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
-      <c r="L19" s="52" t="str">
+      <c r="L19" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N19" s="68" t="str">
+      <c r="N19" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlQtus] = &amp;const_QtusMl,</v>
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="66" t="str">
+      <c r="D20" s="64" t="str">
         <f>VLOOKUP(A20,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspc</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20" s="79" t="str">
         <f>VLOOKUP(A20,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F20" s="43" t="str">
+      <c r="F20" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G20" s="43" t="str">
+      <c r="G20" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H20" s="51" t="str">
+      <c r="H20" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspc,         divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,                "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="79">
         <f>VLOOKUP(A20,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J20" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K20" s="50" t="str">
+      <c r="K20" s="82" t="str">
         <f>VLOOKUP(A20,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
-      <c r="L20" s="52" t="str">
+      <c r="L20" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N20" s="68" t="str">
+      <c r="N20" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTbspc] = &amp;const_TbspcMl,</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="66" t="str">
+      <c r="D21" s="64" t="str">
         <f>VLOOKUP(A21,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspuk</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21" s="79" t="str">
         <f>VLOOKUP(A21,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F21" s="43" t="str">
+      <c r="F21" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G21" s="43" t="str">
+      <c r="G21" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H21" s="51" t="str">
+      <c r="H21" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspuk,        divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="79">
         <f>VLOOKUP(A21,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J21" t="str">
+      <c r="J21" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K21" s="50" t="str">
+      <c r="K21" s="82" t="str">
         <f>VLOOKUP(A21,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
-      <c r="L21" s="52" t="str">
+      <c r="L21" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N21" s="68" t="str">
+      <c r="N21" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTbspuk] = &amp;const_TbspukMl,</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="70" t="s">
+      <c r="A22" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="66" t="str">
+      <c r="D22" s="64" t="str">
         <f>VLOOKUP(A22,Factors!D:K,8,0)</f>
         <v>constFactorMlTspc</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22" s="79" t="str">
         <f>VLOOKUP(A22,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F22" s="43" t="str">
+      <c r="F22" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G22" s="43" t="str">
+      <c r="G22" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H22" s="51" t="str">
+      <c r="H22" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspc,          divide,      "ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="79">
         <f>VLOOKUP(A22,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J22" t="str">
+      <c r="J22" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K22" s="50" t="str">
+      <c r="K22" s="82" t="str">
         <f>VLOOKUP(A22,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
-      <c r="L22" s="52" t="str">
+      <c r="L22" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N22" s="68" t="str">
+      <c r="N22" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTspc] = &amp;const_TspcMl,</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="66" t="str">
+      <c r="D23" s="64" t="str">
         <f>VLOOKUP(A23,Factors!D:K,8,0)</f>
         <v>constFactorMlTspuk</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23" s="79" t="str">
         <f>VLOOKUP(A23,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F23" s="43" t="str">
+      <c r="F23" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G23" s="43" t="str">
+      <c r="G23" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H23" s="51" t="str">
+      <c r="H23" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspuk,         divide,      "ml" STD_RIGHT_ARROW "tsp" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="79">
         <f>VLOOKUP(A23,Factors!D:G,4,0)</f>
         <v>5.9193880208333001</v>
       </c>
-      <c r="J23" t="str">
+      <c r="J23" s="79" t="str">
         <f t="shared" si="3"/>
         <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K23" s="50" t="str">
+      <c r="K23" s="82" t="str">
         <f>VLOOKUP(A23,Factors!D:N,11,0)</f>
         <v>TspukMl</v>
       </c>
-      <c r="L23" s="52" t="str">
+      <c r="L23" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N23" s="68" t="str">
+      <c r="N23" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTspuk] = &amp;const_TspukMl,</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="66" t="str">
+      <c r="D24" s="64" t="str">
         <f>VLOOKUP(A24,Factors!D:K,8,0)</f>
         <v>constFactorPintlqMl</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E24" s="79" t="str">
         <f>VLOOKUP(A24,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F24" s="43" t="str">
+      <c r="F24" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G24" s="43" t="str">
+      <c r="G24" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW</v>
       </c>
-      <c r="H24" s="51" t="str">
+      <c r="H24" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintlqMl,      multiply,      "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml",   "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW        ),</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="79">
         <f>VLOOKUP(A24,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J24" t="str">
+      <c r="J24" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K24" s="50" t="str">
+      <c r="K24" s="82" t="str">
         <f>VLOOKUP(A24,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
-      <c r="L24" s="52" t="str">
+      <c r="L24" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("PintlqMl",      "+4.731764730000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N24" s="68" t="str">
+      <c r="N24" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorPintlqMl] = &amp;const_PintlqMl,</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="66" t="str">
+      <c r="D25" s="64" t="str">
         <f>VLOOKUP(A25,Factors!D:K,8,0)</f>
         <v>constFactorPintukMl</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E25" s="79" t="str">
         <f>VLOOKUP(A25,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F25" s="43" t="str">
+      <c r="F25" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G25" s="43" t="str">
+      <c r="G25" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H25" s="51" t="str">
+      <c r="H25" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintukMl,      multiply,      "pint" STD_UK STD_RIGHT_ARROW "ml",                          "pint" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="79">
         <f>VLOOKUP(A25,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J25" t="str">
+      <c r="J25" s="79" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K25" s="50" t="str">
+      <c r="K25" s="82" t="str">
         <f>VLOOKUP(A25,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
-      <c r="L25" s="52" t="str">
+      <c r="L25" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("PintukMl",      "+5.682612500000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N25" s="68" t="str">
+      <c r="N25" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorPintukMl] = &amp;const_PintukMl,</v>
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="71" t="s">
+      <c r="B26" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="66" t="str">
+      <c r="D26" s="64" t="str">
         <f>VLOOKUP(A26,Factors!D:K,8,0)</f>
         <v>constFactorQtMl</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E26" s="79" t="str">
         <f>VLOOKUP(A26,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F26" s="43" t="str">
+      <c r="F26" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"qt." STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G26" s="43" t="str">
+      <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"qt." STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H26" s="51" t="str">
+      <c r="H26" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtMl,          multiply,      "qt." STD_UK STD_RIGHT_ARROW "ml",                           "qt." STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="79">
         <f>VLOOKUP(A26,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J26" t="str">
+      <c r="J26" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K26" s="50" t="str">
+      <c r="K26" s="82" t="str">
         <f>VLOOKUP(A26,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
-      <c r="L26" s="52" t="str">
+      <c r="L26" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("QtMl",          "+1.136522500000000000000000000000000000000000000000000000e+03");</v>
       </c>
-      <c r="N26" s="68" t="str">
+      <c r="N26" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorQtMl] = &amp;const_QtMl,</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="71" t="s">
+      <c r="B27" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="70" t="s">
+      <c r="C27" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="66" t="str">
+      <c r="D27" s="64" t="str">
         <f>VLOOKUP(A27,Factors!D:K,8,0)</f>
         <v>constFactorQtusMl</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E27" s="79" t="str">
         <f>VLOOKUP(A27,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F27" s="43" t="str">
+      <c r="F27" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"qt." STD_US STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G27" s="43" t="str">
+      <c r="G27" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"qt." STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H27" s="51" t="str">
+      <c r="H27" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtusMl,        multiply,      "qt." STD_US STD_RIGHT_ARROW "ml",                           "qt." STD_US STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="79">
         <f>VLOOKUP(A27,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J27" s="79" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K27" s="50" t="str">
+      <c r="K27" s="82" t="str">
         <f>VLOOKUP(A27,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
-      <c r="L27" s="52" t="str">
+      <c r="L27" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("QtusMl",        "+9.463529460000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N27" s="68" t="str">
+      <c r="N27" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorQtusMl] = &amp;const_QtusMl,</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="70" t="s">
+      <c r="C28" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="66" t="str">
+      <c r="D28" s="64" t="str">
         <f>VLOOKUP(A28,Factors!D:K,8,0)</f>
         <v>constFactorTbspcFzus</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E28" s="79" t="str">
         <f>VLOOKUP(A28,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F28" s="43" t="str">
+      <c r="F28" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G28" s="43" t="str">
+      <c r="G28" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H28" s="51" t="str">
+      <c r="H28" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcFzus,       divide,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,       "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="79">
         <f>VLOOKUP(A28,Factors!D:G,4,0)</f>
         <v>1.9999980007459077</v>
       </c>
-      <c r="J28" t="str">
+      <c r="J28" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.999998000745910000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K28" s="50" t="str">
+      <c r="K28" s="82" t="str">
         <f>VLOOKUP(A28,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
-      <c r="L28" s="52" t="str">
+      <c r="L28" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N28" s="68" t="str">
+      <c r="N28" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspcFzus] = &amp;const_FzusTbspc,</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="66" t="str">
+      <c r="D29" s="64" t="str">
         <f>VLOOKUP(A29,Factors!D:K,8,0)</f>
         <v>constFactorTbspcMl</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E29" s="79" t="str">
         <f>VLOOKUP(A29,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F29" s="43" t="str">
+      <c r="F29" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G29" s="43" t="str">
+      <c r="G29" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H29" s="51" t="str">
+      <c r="H29" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcMl,       multiply,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="79">
         <f>VLOOKUP(A29,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J29" t="str">
+      <c r="J29" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K29" s="50" t="str">
+      <c r="K29" s="82" t="str">
         <f>VLOOKUP(A29,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
-      <c r="L29" s="52" t="str">
+      <c r="L29" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TbspcMl",       "+1.478676478125000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N29" s="68" t="str">
+      <c r="N29" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspcMl] = &amp;const_TbspcMl,</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="66" t="str">
+      <c r="D30" s="64" t="str">
         <f>VLOOKUP(A30,Factors!D:K,8,0)</f>
         <v>constFactorTbspukFzuk</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E30" s="79" t="str">
         <f>VLOOKUP(A30,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F30" s="43" t="str">
+      <c r="F30" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G30" s="43" t="str">
+      <c r="G30" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H30" s="51" t="str">
+      <c r="H30" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukFzuk,      divide,      "Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                 "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="79">
         <f>VLOOKUP(A30,Factors!D:G,4,0)</f>
         <v>1.6000021117047836</v>
       </c>
-      <c r="J30" t="str">
+      <c r="J30" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.600002111704780000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K30" s="50" t="str">
+      <c r="K30" s="82" t="str">
         <f>VLOOKUP(A30,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
-      <c r="L30" s="52" t="str">
+      <c r="L30" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N30" s="68" t="str">
+      <c r="N30" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspukFzuk] = &amp;const_FzukTbspuk,</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="70" t="s">
+      <c r="A31" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="66" t="str">
+      <c r="D31" s="64" t="str">
         <f>VLOOKUP(A31,Factors!D:K,8,0)</f>
         <v>constFactorTbspukMl</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E31" s="79" t="str">
         <f>VLOOKUP(A31,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F31" s="43" t="str">
+      <c r="F31" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G31" s="43" t="str">
+      <c r="G31" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H31" s="51" t="str">
+      <c r="H31" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukMl,      multiply,      "Tbsp" STD_UK STD_RIGHT_ARROW "ml",                          "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="79">
         <f>VLOOKUP(A31,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J31" s="79" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K31" s="50" t="str">
+      <c r="K31" s="82" t="str">
         <f>VLOOKUP(A31,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
-      <c r="L31" s="52" t="str">
+      <c r="L31" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TbspukMl",      "+1.775816406250000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N31" s="68" t="str">
+      <c r="N31" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspukMl] = &amp;const_TbspukMl,</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="71" t="s">
+      <c r="B32" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="66" t="str">
+      <c r="D32" s="64" t="str">
         <f>VLOOKUP(A32,Factors!D:K,8,0)</f>
         <v>constFactorTspcFzus</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E32" s="79" t="str">
         <f>VLOOKUP(A32,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F32" s="43" t="str">
+      <c r="F32" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G32" s="43" t="str">
+      <c r="G32" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H32" s="51" t="str">
+      <c r="H32" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcFzus,        divide,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="79">
         <f>VLOOKUP(A32,Factors!D:G,4,0)</f>
         <v>5.9999940022377229</v>
       </c>
-      <c r="J32" t="str">
+      <c r="J32" s="79" t="str">
         <f t="shared" si="3"/>
         <v>5.999994002237720000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K32" s="50" t="str">
+      <c r="K32" s="82" t="str">
         <f>VLOOKUP(A32,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
-      <c r="L32" s="52" t="str">
+      <c r="L32" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N32" s="68" t="str">
+      <c r="N32" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTspcFzus] = &amp;const_FzusTspc,</v>
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="71" t="s">
+      <c r="B33" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="66" t="str">
+      <c r="D33" s="64" t="str">
         <f>VLOOKUP(A33,Factors!D:K,8,0)</f>
         <v>constFactorTspcMl</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E33" s="79" t="str">
         <f>VLOOKUP(A33,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F33" s="43" t="str">
+      <c r="F33" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G33" s="43" t="str">
+      <c r="G33" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H33" s="51" t="str">
+      <c r="H33" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcMl,        multiply,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="79">
         <f>VLOOKUP(A33,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J33" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K33" s="50" t="str">
+      <c r="K33" s="82" t="str">
         <f>VLOOKUP(A33,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
-      <c r="L33" s="52" t="str">
+      <c r="L33" s="50" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TspcMl",        "+4.928921593750000000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N33" s="68" t="str">
+      <c r="N33" s="65" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTspcMl] = &amp;const_TspcMl,</v>
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="71" t="s">
+      <c r="B34" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="66" t="str">
+      <c r="D34" s="64" t="str">
         <f>VLOOKUP(A34,Factors!D:K,8,0)</f>
         <v>constFactorTspukFzuk</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E34" s="79" t="str">
         <f>VLOOKUP(A34,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F34" s="43" t="str">
+      <c r="F34" s="81" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G34" s="43" t="str">
+      <c r="G34" s="81" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H34" s="51" t="str">
+      <c r="H34" s="49" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukFzuk,       divide,      "tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="79">
         <f>VLOOKUP(A34,Factors!D:G,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="79" t="str">
+        <f t="shared" si="3"/>
+        <v>0.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K34" s="82" t="str">
+        <f>VLOOKUP(A34,Factors!D:N,11,0)</f>
+        <v>FzukTspuk</v>
+      </c>
+      <c r="L34" s="50" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N34" s="65" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    [constFactorTspukFzuk] = &amp;const_FzukTspuk,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="64" t="str">
+        <f>VLOOKUP(A35,Factors!D:K,8,0)</f>
+        <v>constFactorTspukMl</v>
+      </c>
+      <c r="E35" s="79" t="str">
+        <f>VLOOKUP(A35,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F35" s="81" t="str">
+        <f t="shared" ref="F35:F43" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
+        <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
+      </c>
+      <c r="G35" s="81" t="str">
+        <f t="shared" ref="G35:G43" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
+        <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H35" s="49" t="str">
+        <f t="shared" ref="H35:H43" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
+        <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
+      </c>
+      <c r="I35" s="79">
+        <f>VLOOKUP(A35,Factors!D:G,4,0)</f>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="J35" s="79" t="str">
+        <f t="shared" ref="J35:J43" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+        <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K35" s="82" t="str">
+        <f>VLOOKUP(A35,Factors!D:N,11,0)</f>
+        <v>TspukMl</v>
+      </c>
+      <c r="L35" s="50" t="str">
+        <f t="shared" ref="L35:L43" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
+        <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833300000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N35" s="65" t="str">
+        <f t="shared" ref="N35:N43" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
+        <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="64" t="str">
+        <f>VLOOKUP(A36,Factors!D:K,8,0)</f>
+        <v>constFactorMlIn3</v>
+      </c>
+      <c r="E36" s="79" t="str">
+        <f>VLOOKUP(A36,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F36" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>"m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3</v>
+      </c>
+      <c r="G36" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>"m" STD_litre STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H36" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorMlIn3,           divide,      "m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3,                "m" STD_litre STD_RIGHT_ARROW                               ),</v>
+      </c>
+      <c r="I36" s="79">
+        <f>VLOOKUP(A36,Factors!D:G,4,0)</f>
         <v>4.8000063351143778</v>
       </c>
-      <c r="J34" t="str">
+      <c r="J36" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K36" s="82" t="str">
+        <f>VLOOKUP(A36,Factors!D:N,11,0)</f>
+        <v>In3Ml</v>
+      </c>
+      <c r="L36" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N36" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorMlIn3] = &amp;const_In3Ml,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="64" t="str">
+        <f>VLOOKUP(A37,Factors!D:K,8,0)</f>
+        <v>constFactorIn3Ml</v>
+      </c>
+      <c r="E37" s="79" t="str">
+        <f>VLOOKUP(A37,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F37" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</v>
+      </c>
+      <c r="G37" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H37" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorIn3Ml,         multiply,       "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre,                "in" STD_SUP_3 STD_RIGHT_ARROW                             ),</v>
+      </c>
+      <c r="I37" s="79">
+        <f>VLOOKUP(A37,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J37" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K37" s="82" t="str">
+        <f>VLOOKUP(A37,Factors!D:N,11,0)</f>
+        <v>In3Ml</v>
+      </c>
+      <c r="L37" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("In3Ml",         "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N37" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorIn3Ml] = &amp;const_In3Ml,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="69" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="64" t="str">
+        <f>VLOOKUP(A38,Factors!D:K,8,0)</f>
+        <v>constFactorFt3Gluk</v>
+      </c>
+      <c r="E38" s="79" t="str">
+        <f>VLOOKUP(A38,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F38" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK</v>
+      </c>
+      <c r="G38" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H38" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorFt3Gluk,       multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK,                  "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
+      </c>
+      <c r="I38" s="79">
+        <f>VLOOKUP(A38,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J38" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K38" s="82" t="str">
+        <f>VLOOKUP(A38,Factors!D:N,11,0)</f>
+        <v>Ft3Gluk</v>
+      </c>
+      <c r="L38" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("Ft3Gluk",       "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N38" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorFt3Gluk] = &amp;const_Ft3Gluk,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="64" t="str">
+        <f>VLOOKUP(A39,Factors!D:K,8,0)</f>
+        <v>constFactorGlukFt3</v>
+      </c>
+      <c r="E39" s="79" t="str">
+        <f>VLOOKUP(A39,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F39" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>"GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</v>
+      </c>
+      <c r="G39" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>"GL" STD_UK STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H39" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorGlukFt3,         divide,      "GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3,                  "GL" STD_UK STD_RIGHT_ARROW                                 ),</v>
+      </c>
+      <c r="I39" s="79">
+        <f>VLOOKUP(A39,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J39" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K39" s="82" t="str">
+        <f>VLOOKUP(A39,Factors!D:N,11,0)</f>
+        <v>Ft3Gluk</v>
+      </c>
+      <c r="L39" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N39" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorGlukFt3] = &amp;const_Ft3Gluk,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="64" t="str">
+        <f>VLOOKUP(A40,Factors!D:K,8,0)</f>
+        <v>constFactorLFt3</v>
+      </c>
+      <c r="E40" s="79" t="str">
+        <f>VLOOKUP(A40,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F40" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3</v>
+      </c>
+      <c r="G40" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>STD_litre STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H40" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorLFt3,            divide,      STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3,                    STD_litre STD_RIGHT_ARROW                                   ),</v>
+      </c>
+      <c r="I40" s="79">
+        <f>VLOOKUP(A40,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J40" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K40" s="82" t="str">
+        <f>VLOOKUP(A40,Factors!D:N,11,0)</f>
+        <v>Ft3L</v>
+      </c>
+      <c r="L40" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N40" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorLFt3] = &amp;const_Ft3L,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="69" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="64" t="str">
+        <f>VLOOKUP(A41,Factors!D:K,8,0)</f>
+        <v>constFactorFt3L</v>
+      </c>
+      <c r="E41" s="79" t="str">
+        <f>VLOOKUP(A41,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F41" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre</v>
+      </c>
+      <c r="G41" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H41" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorFt3L,          multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre,                    "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
+      </c>
+      <c r="I41" s="79">
+        <f>VLOOKUP(A41,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J41" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K41" s="82" t="str">
+        <f>VLOOKUP(A41,Factors!D:N,11,0)</f>
+        <v>Ft3L</v>
+      </c>
+      <c r="L41" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("Ft3L",          "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N41" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorFt3L] = &amp;const_Ft3L,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>206</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="64" t="str">
+        <f>VLOOKUP(A42,Factors!D:K,8,0)</f>
+        <v>constFactorLQtus</v>
+      </c>
+      <c r="E42" s="79" t="str">
+        <f>VLOOKUP(A42,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F42" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>STD_litre STD_RIGHT_ARROW "qt" STD_US</v>
+      </c>
+      <c r="G42" s="81" t="str">
+        <f t="shared" si="7"/>
+        <v>STD_litre STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H42" s="49" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorLQtus,         multiply,      STD_litre STD_RIGHT_ARROW "qt" STD_US,                       STD_litre STD_RIGHT_ARROW                                   ),</v>
+      </c>
+      <c r="I42" s="79">
+        <f>VLOOKUP(A42,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J42" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K42" s="82" t="str">
+        <f>VLOOKUP(A42,Factors!D:N,11,0)</f>
+        <v>LQtus</v>
+      </c>
+      <c r="L42" s="50" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("LQtus",         "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N42" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorLQtus] = &amp;const_LQtus,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="64" t="str">
+        <f>VLOOKUP(A43,Factors!D:K,8,0)</f>
+        <v>constFactorQtusL</v>
+      </c>
+      <c r="E43" s="79" t="str">
+        <f>VLOOKUP(A43,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F43" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>"qt" STD_US STD_RIGHT_ARROW STD_litre</v>
+      </c>
+      <c r="G43" s="81" t="str">
+        <f t="shared" si="1"/>
+        <v>"qt" STD_US STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H43" s="49" t="str">
+        <f t="shared" si="2"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorQtusL,           divide,      "qt" STD_US STD_RIGHT_ARROW STD_litre,                       "qt" STD_US STD_RIGHT_ARROW                                 ),</v>
+      </c>
+      <c r="I43" s="79">
+        <f>VLOOKUP(A43,Factors!D:G,4,0)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="J43" s="79" t="str">
         <f t="shared" si="3"/>
         <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K34" s="50" t="str">
-        <f>VLOOKUP(A34,Factors!D:N,11,0)</f>
-        <v>FzukTspuk</v>
-      </c>
-      <c r="L34" s="52" t="str">
+      <c r="K43" s="82" t="str">
+        <f>VLOOKUP(A43,Factors!D:N,11,0)</f>
+        <v>LQtus</v>
+      </c>
+      <c r="L43" s="50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N34" s="68" t="str">
+      <c r="N43" s="65" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    [constFactorTspukFzuk] = &amp;const_FzukTspuk,</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="66" t="str">
-        <f>VLOOKUP(A35,Factors!D:K,8,0)</f>
-        <v>constFactorTspukMl</v>
-      </c>
-      <c r="E35" t="str">
-        <f>VLOOKUP(A35,Factors!D:N,10,0)</f>
-        <v>multiply</v>
-      </c>
-      <c r="F35" s="43" t="str">
-        <f t="shared" si="0"/>
-        <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
-      </c>
-      <c r="G35" s="43" t="str">
-        <f t="shared" si="1"/>
-        <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
-      </c>
-      <c r="H35" s="51" t="str">
-        <f t="shared" si="2"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
-      </c>
-      <c r="I35">
-        <f>VLOOKUP(A35,Factors!D:G,4,0)</f>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="J35" t="str">
-        <f t="shared" si="3"/>
-        <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K35" s="50" t="str">
-        <f>VLOOKUP(A35,Factors!D:N,11,0)</f>
-        <v>TspukMl</v>
-      </c>
-      <c r="L35" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833300000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N35" s="68" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="4" t="s">
+        <v xml:space="preserve">    [constFactorQtusL] = &amp;const_LQtus,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="4" t="s">
+    <row r="46" spans="1:14">
+      <c r="A46" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B39">
-    <sortCondition ref="A4:A39"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B47">
+    <sortCondition ref="A4:A47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3241,7 +3835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAAB5F5-5A0E-F540-8CD7-68987B744E5F}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -3249,22 +3843,21 @@
     <col min="3" max="3" width="7.83203125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14">
-      <c r="F1" s="55"/>
-    </row>
-    <row r="2" spans="3:14" ht="17" thickBot="1">
-      <c r="F2" s="55" t="s">
+    <row r="1" spans="1:14">
+      <c r="F1" s="53"/>
+    </row>
+    <row r="2" spans="1:14" ht="17" thickBot="1">
+      <c r="F2" s="53" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="3:14" ht="18">
+    <row r="3" spans="1:14" ht="18">
       <c r="C3" s="42" t="s">
         <v>114</v>
       </c>
@@ -3274,18 +3867,18 @@
       <c r="E3" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="54">
         <v>473.17647299999999</v>
       </c>
-      <c r="J3" s="44">
+      <c r="J3" s="43">
         <f>F3/F5</f>
         <v>2</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="44" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="3:14" ht="18">
+    <row r="4" spans="1:14" ht="18">
       <c r="C4" s="30" t="s">
         <v>111</v>
       </c>
@@ -3295,18 +3888,18 @@
       <c r="E4" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="55">
         <f xml:space="preserve"> 2 * F3</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J4" s="44">
+      <c r="J4" s="43">
         <f>F4/F3</f>
         <v>2</v>
       </c>
-      <c r="K4" s="45" t="s">
+      <c r="K4" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="L4" s="45" t="s">
+      <c r="L4" s="44" t="s">
         <v>178</v>
       </c>
       <c r="M4">
@@ -3318,7 +3911,7 @@
         <v>32.000031988097454</v>
       </c>
     </row>
-    <row r="5" spans="3:14" ht="18">
+    <row r="5" spans="1:14" ht="18">
       <c r="C5" s="30" t="s">
         <v>104</v>
       </c>
@@ -3328,18 +3921,18 @@
       <c r="E5" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="54">
         <v>236.58823649999999</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="43">
         <f>F5/F15</f>
         <v>8.0000079970243636</v>
       </c>
-      <c r="K5" s="45" t="s">
+      <c r="K5" s="44" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="6" spans="3:14" ht="18">
+    <row r="6" spans="1:14" ht="18">
       <c r="C6" s="30" t="s">
         <v>101</v>
       </c>
@@ -3349,7 +3942,7 @@
       <c r="E6" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="54">
         <v>14.78676478125</v>
       </c>
       <c r="G6" s="38" t="str">
@@ -3360,9 +3953,9 @@
         <f>E5</f>
         <v>US customary cup</v>
       </c>
-      <c r="J6" s="46"/>
-    </row>
-    <row r="7" spans="3:14" ht="18">
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" spans="1:14" ht="18">
       <c r="C7" s="30" t="s">
         <v>96</v>
       </c>
@@ -3372,7 +3965,7 @@
       <c r="E7" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="54">
         <v>4.9289215937500002</v>
       </c>
       <c r="G7" s="7" t="str">
@@ -3383,16 +3976,17 @@
         <f>E5</f>
         <v>US customary cup</v>
       </c>
-      <c r="J7" s="46"/>
-    </row>
-    <row r="8" spans="3:14" ht="18">
+      <c r="J7" s="45"/>
+    </row>
+    <row r="8" spans="1:14" ht="18">
       <c r="C8" s="37"/>
       <c r="D8" s="36"/>
       <c r="E8" s="35"/>
-      <c r="F8" s="58"/>
-      <c r="J8" s="46"/>
-    </row>
-    <row r="9" spans="3:14" ht="18">
+      <c r="F8" s="56"/>
+      <c r="J8" s="45"/>
+    </row>
+    <row r="9" spans="1:14" ht="18">
+      <c r="A9" s="77"/>
       <c r="C9" s="30" t="s">
         <v>92</v>
       </c>
@@ -3402,21 +3996,22 @@
       <c r="E9" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="54">
         <v>568.26125000000002</v>
       </c>
       <c r="H9" s="34">
         <v>568.26125000000002</v>
       </c>
-      <c r="J9" s="47">
+      <c r="J9" s="46">
         <f>F9/F11</f>
         <v>2</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="47" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="3:14" ht="18">
+    <row r="10" spans="1:14" ht="18">
+      <c r="A10" s="77"/>
       <c r="C10" s="33" t="s">
         <v>89</v>
       </c>
@@ -3426,7 +4021,7 @@
       <c r="E10" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="54">
         <v>1136.5225</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -3436,15 +4031,16 @@
         <f>2*H9</f>
         <v>1136.5225</v>
       </c>
-      <c r="J10" s="44">
+      <c r="J10" s="43">
         <f>F10/F9</f>
         <v>2</v>
       </c>
-      <c r="K10" s="45" t="s">
+      <c r="K10" s="44" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="3:14" ht="18">
+    <row r="11" spans="1:14" ht="18">
+      <c r="A11" s="77"/>
       <c r="C11" s="30" t="s">
         <v>82</v>
       </c>
@@ -3454,21 +4050,24 @@
       <c r="E11" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="54">
         <v>284.13062500000001</v>
       </c>
       <c r="H11" s="34">
         <v>284.13062500000001</v>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="46">
         <f>F11/F16</f>
         <v>9.9999868018625211</v>
       </c>
-      <c r="K11" s="48" t="s">
+      <c r="K11" s="47" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="3:14" ht="18">
+    <row r="12" spans="1:14" ht="18">
+      <c r="A12" s="77" t="s">
+        <v>216</v>
+      </c>
       <c r="C12" s="30" t="s">
         <v>79</v>
       </c>
@@ -3478,7 +4077,7 @@
       <c r="E12" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="54">
         <v>17.758164062500001</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -3487,9 +4086,12 @@
       <c r="H12" s="34">
         <v>177.58164062500001</v>
       </c>
-      <c r="J12" s="46"/>
-    </row>
-    <row r="13" spans="3:14" ht="19" thickBot="1">
+      <c r="J12" s="45"/>
+    </row>
+    <row r="13" spans="1:14" ht="19" thickBot="1">
+      <c r="A13" s="77" t="s">
+        <v>225</v>
+      </c>
       <c r="C13" s="27" t="s">
         <v>73</v>
       </c>
@@ -3499,15 +4101,18 @@
       <c r="E13" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="54">
         <v>5.9193880208333001</v>
       </c>
       <c r="H13" s="34">
         <v>5.9193880208333001</v>
       </c>
-      <c r="J13" s="46"/>
-    </row>
-    <row r="14" spans="3:14">
+      <c r="J13" s="45"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="77" t="s">
+        <v>226</v>
+      </c>
       <c r="C14" s="24" t="s">
         <v>76</v>
       </c>
@@ -3517,12 +4122,15 @@
       <c r="E14" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="57">
         <v>1</v>
       </c>
-      <c r="J14" s="46"/>
-    </row>
-    <row r="15" spans="3:14">
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="77" t="s">
+        <v>111</v>
+      </c>
       <c r="C15" s="22" t="s">
         <v>95</v>
       </c>
@@ -3530,15 +4138,16 @@
       <c r="E15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="58">
         <v>29.573499999999999</v>
       </c>
-      <c r="J15" s="46"/>
+      <c r="J15" s="45"/>
       <c r="N15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="3:14">
+    <row r="16" spans="1:14">
+      <c r="A16" s="77"/>
       <c r="C16" s="22" t="s">
         <v>72</v>
       </c>
@@ -3546,10 +4155,10 @@
       <c r="E16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="58">
         <v>28.4131</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="N16" t="s">
         <v>185</v>
       </c>
@@ -3561,14 +4170,14 @@
       <c r="E17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="53">
         <v>3785.51</v>
       </c>
-      <c r="J17" s="44">
+      <c r="J17" s="43">
         <f>F17/F4</f>
         <v>4.0001037836891777</v>
       </c>
-      <c r="K17" s="45" t="s">
+      <c r="K17" s="44" t="s">
         <v>188</v>
       </c>
       <c r="N17" t="s">
@@ -3582,14 +4191,14 @@
       <c r="E18" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="53">
         <v>4545.09</v>
       </c>
-      <c r="J18" s="44">
+      <c r="J18" s="43">
         <f>F18/F10</f>
         <v>3.9991201230068039</v>
       </c>
-      <c r="K18" s="45" t="s">
+      <c r="K18" s="44" t="s">
         <v>192</v>
       </c>
       <c r="N18" t="s">
@@ -3597,486 +4206,337 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="F19" s="55"/>
+      <c r="C19" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="53">
+        <f>2.54^3</f>
+        <v>16.387063999999999</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="J19" s="43"/>
+      <c r="K19" s="44"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="F20" s="55"/>
-    </row>
-    <row r="21" spans="1:14" ht="17" thickBot="1">
-      <c r="F21" s="61" t="s">
+      <c r="C20" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="F20" s="78">
+        <f>(12*2.54)^3</f>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J20" s="43"/>
+      <c r="K20" s="44"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="C21" s="77" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="53">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="J21" s="43"/>
+      <c r="K21" s="44"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="C22" s="77"/>
+      <c r="F22" s="53"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="44"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="F23" s="53"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="F24" s="53"/>
+    </row>
+    <row r="25" spans="1:14" ht="17" thickBot="1">
+      <c r="F25" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H25" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I25" s="21" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="18">
-      <c r="A22" s="13" t="s">
+    <row r="26" spans="1:14" ht="18">
+      <c r="A26" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B26" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C26" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D26" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E26" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="62">
-        <f>H22/I22</f>
+      <c r="F26" s="60">
+        <f>H26/I26</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="G22" s="64">
-        <f>IF(M22="multiply",F22,F23)</f>
+      <c r="G26" s="62">
+        <f>IF(M26="multiply",F26,F27)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="H22" s="9">
-        <f xml:space="preserve"> VLOOKUP(B22,units,4,0)</f>
+      <c r="H26" s="9">
+        <f xml:space="preserve"> VLOOKUP(B26,units,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="I22" s="9">
-        <f t="shared" ref="I22:I37" si="0" xml:space="preserve"> VLOOKUP(C22,units,4,0)</f>
+      <c r="I26" s="9">
+        <f t="shared" ref="I26:I41" si="0" xml:space="preserve"> VLOOKUP(C26,units,4,0)</f>
         <v>1</v>
       </c>
-      <c r="J22" s="67" t="str">
-        <f>PROPER(B22)&amp;PROPER(C22)</f>
+      <c r="J26" t="str">
+        <f>PROPER(B26)&amp;PROPER(C26)</f>
         <v>PintlqMl</v>
       </c>
-      <c r="K22" t="str">
-        <f>"constFactor"&amp;J22</f>
+      <c r="K26" t="str">
+        <f>"constFactor"&amp;J26</f>
         <v>constFactorPintlqMl</v>
       </c>
-      <c r="M22" s="64" t="str">
-        <f>IF(H22&gt;I22,"multiply","  divide")</f>
+      <c r="M26" s="62" t="str">
+        <f>IF(H26&gt;I26,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N22" s="64" t="str">
-        <f>IF(M22="multiply",PROPER(B22)&amp;PROPER(C22),J23)</f>
+      <c r="N26" s="62" t="str">
+        <f>IF(M26="multiply",PROPER(B26)&amp;PROPER(C26),J27)</f>
         <v>PintlqMl</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="18">
-      <c r="A23" s="13" t="s">
+    <row r="27" spans="1:14" ht="18">
+      <c r="A27" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B27" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C27" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D27" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E27" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F23" s="62">
-        <f t="shared" ref="F23:F55" si="1">H23/I23</f>
+      <c r="F27" s="60">
+        <f t="shared" ref="F27:F67" si="1">H27/I27</f>
         <v>2.1133764188651875E-3</v>
       </c>
-      <c r="G23" s="64">
-        <f>IF(M23="multiply",F23,F22)</f>
+      <c r="G27" s="62">
+        <f>IF(M27="multiply",F27,F26)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="H23" s="9">
-        <f t="shared" ref="H22:H37" si="2" xml:space="preserve"> VLOOKUP(B23,units,4,0)</f>
+      <c r="H27" s="9">
+        <f t="shared" ref="H27:H41" si="2" xml:space="preserve"> VLOOKUP(B27,units,4,0)</f>
         <v>1</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I27" s="9">
         <f t="shared" si="0"/>
         <v>473.17647299999999</v>
       </c>
-      <c r="J23" s="67" t="str">
-        <f t="shared" ref="J23:J55" si="3">PROPER(B23)&amp;PROPER(C23)</f>
+      <c r="J27" t="str">
+        <f t="shared" ref="J27:J59" si="3">PROPER(B27)&amp;PROPER(C27)</f>
         <v>MlPintlq</v>
       </c>
-      <c r="K23" t="str">
-        <f t="shared" ref="K23:K55" si="4">"constFactor"&amp;J23</f>
+      <c r="K27" t="str">
+        <f t="shared" ref="K27:K51" si="4">"constFactor"&amp;J27</f>
         <v>constFactorMlPintlq</v>
       </c>
-      <c r="M23" s="64" t="str">
-        <f>IF(M22="multiply","  divide","multiply")</f>
+      <c r="M27" s="62" t="str">
+        <f>IF(M26="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N23" s="64" t="str">
-        <f>IF(M23="multiply",PROPER(B23)&amp;PROPER(C23),J22)</f>
+      <c r="N27" s="62" t="str">
+        <f>IF(M27="multiply",PROPER(B27)&amp;PROPER(C27),J26)</f>
         <v>PintlqMl</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18">
-      <c r="A24" s="13" t="s">
+    <row r="28" spans="1:14" ht="18">
+      <c r="A28" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B28" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D28" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E28" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F28" s="60">
         <f t="shared" si="1"/>
         <v>946.35294599999997</v>
       </c>
-      <c r="G24" s="65">
-        <f>IF(M24="multiply",F24,F25)</f>
+      <c r="G28" s="63">
+        <f>IF(M28="multiply",F28,F29)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H28" s="9">
         <f t="shared" si="2"/>
         <v>946.35294599999997</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I28" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J24" s="67" t="str">
+      <c r="J28" t="str">
         <f t="shared" si="3"/>
         <v>QtusMl</v>
       </c>
-      <c r="K24" t="str">
-        <f>"constFactor"&amp;J24</f>
+      <c r="K28" t="str">
+        <f>"constFactor"&amp;J28</f>
         <v>constFactorQtusMl</v>
       </c>
-      <c r="M24" s="65" t="str">
-        <f>IF(H24&gt;I24,"multiply","  divide")</f>
+      <c r="M28" s="63" t="str">
+        <f>IF(H28&gt;I28,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N24" s="65" t="str">
-        <f>IF(M24="multiply",PROPER(B24)&amp;PROPER(C24),J25)</f>
+      <c r="N28" s="63" t="str">
+        <f>IF(M28="multiply",PROPER(B28)&amp;PROPER(C28),J29)</f>
         <v>QtusMl</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="18">
-      <c r="A25" s="13" t="s">
+    <row r="29" spans="1:14" ht="18">
+      <c r="A29" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B29" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C29" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E29" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F29" s="60">
         <f t="shared" si="1"/>
         <v>1.0566882094325937E-3</v>
       </c>
-      <c r="G25" s="65">
-        <f>IF(M25="multiply",F25,F24)</f>
+      <c r="G29" s="63">
+        <f>IF(M29="multiply",F29,F28)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H29" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I29" s="9">
         <f t="shared" si="0"/>
         <v>946.35294599999997</v>
       </c>
-      <c r="J25" s="67" t="str">
+      <c r="J29" t="str">
         <f t="shared" si="3"/>
         <v>MlQtus</v>
       </c>
-      <c r="K25" t="str">
-        <f t="shared" ref="K25" si="5">"constFactor"&amp;J25</f>
+      <c r="K29" t="str">
+        <f t="shared" ref="K29" si="5">"constFactor"&amp;J29</f>
         <v>constFactorMlQtus</v>
       </c>
-      <c r="M25" s="65" t="str">
-        <f>IF(M24="multiply","  divide","multiply")</f>
+      <c r="M29" s="63" t="str">
+        <f>IF(M28="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N25" s="65" t="str">
-        <f>IF(M25="multiply",PROPER(B25)&amp;PROPER(C25),J24)</f>
+      <c r="N29" s="63" t="str">
+        <f>IF(M29="multiply",PROPER(B29)&amp;PROPER(C29),J28)</f>
         <v>QtusMl</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="18">
-      <c r="A26" s="13" t="s">
+    <row r="30" spans="1:14" ht="18">
+      <c r="A30" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B30" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C30" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E30" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="62">
+      <c r="F30" s="60">
         <f t="shared" si="1"/>
         <v>0.12499987504661923</v>
       </c>
-      <c r="G26" s="64">
-        <f>IF(M26="multiply",F26,F27)</f>
+      <c r="G30" s="62">
+        <f>IF(M30="multiply",F30,F31)</f>
         <v>8.0000079970243636</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H30" s="9">
         <f t="shared" si="2"/>
         <v>29.573499999999999</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" si="0"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="J26" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>FzusCupc</v>
-      </c>
-      <c r="K26" t="str">
-        <f>"constFactor"&amp;J26</f>
-        <v>constFactorFzusCupc</v>
-      </c>
-      <c r="M26" s="64" t="str">
-        <f>IF(H26&gt;I26,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N26" s="64" t="str">
-        <f>IF(M26="multiply",PROPER(B26)&amp;PROPER(C26),J27)</f>
-        <v>CupcFzus</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="18">
-      <c r="A27" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="62">
-        <f t="shared" si="1"/>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="G27" s="64">
-        <f>IF(M27="multiply",F27,F26)</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="2"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="0"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="J27" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>CupcFzus</v>
-      </c>
-      <c r="K27" t="str">
-        <f t="shared" ref="K27:K29" si="6">"constFactor"&amp;J27</f>
-        <v>constFactorCupcFzus</v>
-      </c>
-      <c r="M27" s="64" t="str">
-        <f>IF(M26="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N27" s="64" t="str">
-        <f>IF(M27="multiply",PROPER(B27)&amp;PROPER(C27),J26)</f>
-        <v>CupcFzus</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="18">
-      <c r="A28" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="62">
-        <f t="shared" si="1"/>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="G28" s="65">
-        <f>IF(M28="multiply",F28,F29)</f>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="2"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" si="0"/>
-        <v>14.78676478125</v>
-      </c>
-      <c r="J28" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>FzusTbspc</v>
-      </c>
-      <c r="K28" t="str">
-        <f>"constFactor"&amp;J28</f>
-        <v>constFactorFzusTbspc</v>
-      </c>
-      <c r="M28" s="65" t="str">
-        <f>IF(H28&gt;I28,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N28" s="65" t="str">
-        <f>IF(M28="multiply",PROPER(B28)&amp;PROPER(C28),J29)</f>
-        <v>FzusTbspc</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="18">
-      <c r="A29" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="62">
-        <f t="shared" si="1"/>
-        <v>0.50000049981402273</v>
-      </c>
-      <c r="G29" s="65">
-        <f>IF(M29="multiply",F29,F28)</f>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="H29" s="9">
-        <f t="shared" si="2"/>
-        <v>14.78676478125</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" si="0"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="J29" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspcFzus</v>
-      </c>
-      <c r="K29" t="str">
-        <f t="shared" ref="K29" si="7">"constFactor"&amp;J29</f>
-        <v>constFactorTbspcFzus</v>
-      </c>
-      <c r="M29" s="65" t="str">
-        <f>IF(M28="multiply","  divide","multiply")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N29" s="65" t="str">
-        <f>IF(M29="multiply",PROPER(B29)&amp;PROPER(C29),J28)</f>
-        <v>FzusTbspc</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="18">
-      <c r="A30" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="62">
-        <f t="shared" si="1"/>
-        <v>4.2267528377303749E-3</v>
-      </c>
-      <c r="G30" s="64">
-        <f>IF(M30="multiply",F30,F31)</f>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" si="2"/>
-        <v>1</v>
       </c>
       <c r="I30" s="9">
         <f t="shared" si="0"/>
         <v>236.58823649999999</v>
       </c>
-      <c r="J30" s="67" t="str">
+      <c r="J30" t="str">
         <f t="shared" si="3"/>
-        <v>MlCupc</v>
+        <v>FzusCupc</v>
       </c>
       <c r="K30" t="str">
         <f>"constFactor"&amp;J30</f>
-        <v>constFactorMlCupc</v>
-      </c>
-      <c r="M30" s="64" t="str">
+        <v>constFactorFzusCupc</v>
+      </c>
+      <c r="M30" s="62" t="str">
         <f>IF(H30&gt;I30,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N30" s="64" t="str">
+      <c r="N30" s="62" t="str">
         <f>IF(M30="multiply",PROPER(B30)&amp;PROPER(C30),J31)</f>
-        <v>CupcMl</v>
+        <v>CupcFzus</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="18">
       <c r="A31" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>104</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="62">
-        <f t="shared" si="1"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="G31" s="64">
+        <v>11</v>
+      </c>
+      <c r="F31" s="60">
+        <f t="shared" si="1"/>
+        <v>8.0000079970243636</v>
+      </c>
+      <c r="G31" s="62">
         <f>IF(M31="multiply",F31,F30)</f>
-        <v>236.58823649999999</v>
+        <v>8.0000079970243636</v>
       </c>
       <c r="H31" s="9">
         <f t="shared" si="2"/>
@@ -4084,97 +4544,97 @@
       </c>
       <c r="I31" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J31" s="67" t="str">
+        <v>29.573499999999999</v>
+      </c>
+      <c r="J31" t="str">
         <f t="shared" si="3"/>
-        <v>CupcMl</v>
+        <v>CupcFzus</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" ref="K31:K33" si="8">"constFactor"&amp;J31</f>
-        <v>constFactorCupcMl</v>
-      </c>
-      <c r="M31" s="64" t="str">
+        <f t="shared" ref="K31" si="6">"constFactor"&amp;J31</f>
+        <v>constFactorCupcFzus</v>
+      </c>
+      <c r="M31" s="62" t="str">
         <f>IF(M30="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N31" s="64" t="str">
+      <c r="N31" s="62" t="str">
         <f>IF(M31="multiply",PROPER(B31)&amp;PROPER(C31),J30)</f>
-        <v>CupcMl</v>
+        <v>CupcFzus</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="18">
       <c r="A32" s="13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>101</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="62">
-        <f t="shared" si="1"/>
-        <v>6.7628045403685999E-2</v>
-      </c>
-      <c r="G32" s="65">
+        <v>13</v>
+      </c>
+      <c r="F32" s="60">
+        <f t="shared" si="1"/>
+        <v>1.9999980007459077</v>
+      </c>
+      <c r="G32" s="63">
         <f>IF(M32="multiply",F32,F33)</f>
-        <v>14.78676478125</v>
+        <v>1.9999980007459077</v>
       </c>
       <c r="H32" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>29.573499999999999</v>
       </c>
       <c r="I32" s="9">
         <f t="shared" si="0"/>
         <v>14.78676478125</v>
       </c>
-      <c r="J32" s="67" t="str">
+      <c r="J32" t="str">
         <f t="shared" si="3"/>
-        <v>MlTbspc</v>
+        <v>FzusTbspc</v>
       </c>
       <c r="K32" t="str">
         <f>"constFactor"&amp;J32</f>
-        <v>constFactorMlTbspc</v>
-      </c>
-      <c r="M32" s="65" t="str">
+        <v>constFactorFzusTbspc</v>
+      </c>
+      <c r="M32" s="63" t="str">
         <f>IF(H32&gt;I32,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N32" s="65" t="str">
+        <v>multiply</v>
+      </c>
+      <c r="N32" s="63" t="str">
         <f>IF(M32="multiply",PROPER(B32)&amp;PROPER(C32),J33)</f>
-        <v>TbspcMl</v>
+        <v>FzusTbspc</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="18">
       <c r="A33" s="13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>101</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="62">
-        <f t="shared" si="1"/>
-        <v>14.78676478125</v>
-      </c>
-      <c r="G33" s="65">
+        <v>14</v>
+      </c>
+      <c r="E33" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="60">
+        <f t="shared" si="1"/>
+        <v>0.50000049981402273</v>
+      </c>
+      <c r="G33" s="63">
         <f>IF(M33="multiply",F33,F32)</f>
-        <v>14.78676478125</v>
+        <v>1.9999980007459077</v>
       </c>
       <c r="H33" s="9">
         <f t="shared" si="2"/>
@@ -4182,48 +4642,48 @@
       </c>
       <c r="I33" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J33" s="67" t="str">
+        <v>29.573499999999999</v>
+      </c>
+      <c r="J33" t="str">
         <f t="shared" si="3"/>
-        <v>TbspcMl</v>
+        <v>TbspcFzus</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" ref="K33" si="9">"constFactor"&amp;J33</f>
-        <v>constFactorTbspcMl</v>
-      </c>
-      <c r="M33" s="65" t="str">
+        <f t="shared" ref="K33" si="7">"constFactor"&amp;J33</f>
+        <v>constFactorTbspcFzus</v>
+      </c>
+      <c r="M33" s="63" t="str">
         <f>IF(M32="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N33" s="65" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N33" s="63" t="str">
         <f>IF(M33="multiply",PROPER(B33)&amp;PROPER(C33),J32)</f>
-        <v>TbspcMl</v>
+        <v>FzusTbspc</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="18">
       <c r="A34" s="13" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="62">
-        <f t="shared" si="1"/>
-        <v>0.20288413621105797</v>
-      </c>
-      <c r="G34" s="64">
+        <v>17</v>
+      </c>
+      <c r="F34" s="60">
+        <f t="shared" si="1"/>
+        <v>4.2267528377303749E-3</v>
+      </c>
+      <c r="G34" s="62">
         <f>IF(M34="multiply",F34,F35)</f>
-        <v>4.9289215937500002</v>
+        <v>236.58823649999999</v>
       </c>
       <c r="H34" s="9">
         <f t="shared" si="2"/>
@@ -4231,836 +4691,836 @@
       </c>
       <c r="I34" s="9">
         <f t="shared" si="0"/>
-        <v>4.9289215937500002</v>
-      </c>
-      <c r="J34" s="67" t="str">
+        <v>236.58823649999999</v>
+      </c>
+      <c r="J34" t="str">
         <f t="shared" si="3"/>
-        <v>MlTspc</v>
+        <v>MlCupc</v>
       </c>
       <c r="K34" t="str">
         <f>"constFactor"&amp;J34</f>
-        <v>constFactorMlTspc</v>
-      </c>
-      <c r="M34" s="64" t="str">
+        <v>constFactorMlCupc</v>
+      </c>
+      <c r="M34" s="62" t="str">
         <f>IF(H34&gt;I34,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N34" s="64" t="str">
+      <c r="N34" s="62" t="str">
         <f>IF(M34="multiply",PROPER(B34)&amp;PROPER(C34),J35)</f>
-        <v>TspcMl</v>
+        <v>CupcMl</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="18">
       <c r="A35" s="13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F35" s="62">
-        <f t="shared" si="1"/>
-        <v>4.9289215937500002</v>
-      </c>
-      <c r="G35" s="64">
+        <v>19</v>
+      </c>
+      <c r="F35" s="60">
+        <f t="shared" si="1"/>
+        <v>236.58823649999999</v>
+      </c>
+      <c r="G35" s="62">
         <f>IF(M35="multiply",F35,F34)</f>
-        <v>4.9289215937500002</v>
+        <v>236.58823649999999</v>
       </c>
       <c r="H35" s="9">
         <f t="shared" si="2"/>
-        <v>4.9289215937500002</v>
+        <v>236.58823649999999</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J35" s="67" t="str">
+      <c r="J35" t="str">
+        <f t="shared" si="3"/>
+        <v>CupcMl</v>
+      </c>
+      <c r="K35" t="str">
+        <f t="shared" ref="K35" si="8">"constFactor"&amp;J35</f>
+        <v>constFactorCupcMl</v>
+      </c>
+      <c r="M35" s="62" t="str">
+        <f>IF(M34="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N35" s="62" t="str">
+        <f>IF(M35="multiply",PROPER(B35)&amp;PROPER(C35),J34)</f>
+        <v>CupcMl</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="18">
+      <c r="A36" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="60">
+        <f t="shared" si="1"/>
+        <v>6.7628045403685999E-2</v>
+      </c>
+      <c r="G36" s="63">
+        <f>IF(M36="multiply",F36,F37)</f>
+        <v>14.78676478125</v>
+      </c>
+      <c r="H36" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="0"/>
+        <v>14.78676478125</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="3"/>
+        <v>MlTbspc</v>
+      </c>
+      <c r="K36" t="str">
+        <f>"constFactor"&amp;J36</f>
+        <v>constFactorMlTbspc</v>
+      </c>
+      <c r="M36" s="63" t="str">
+        <f>IF(H36&gt;I36,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N36" s="63" t="str">
+        <f>IF(M36="multiply",PROPER(B36)&amp;PROPER(C36),J37)</f>
+        <v>TbspcMl</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="18">
+      <c r="A37" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="60">
+        <f t="shared" si="1"/>
+        <v>14.78676478125</v>
+      </c>
+      <c r="G37" s="63">
+        <f>IF(M37="multiply",F37,F36)</f>
+        <v>14.78676478125</v>
+      </c>
+      <c r="H37" s="9">
+        <f t="shared" si="2"/>
+        <v>14.78676478125</v>
+      </c>
+      <c r="I37" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="3"/>
+        <v>TbspcMl</v>
+      </c>
+      <c r="K37" t="str">
+        <f t="shared" ref="K37" si="9">"constFactor"&amp;J37</f>
+        <v>constFactorTbspcMl</v>
+      </c>
+      <c r="M37" s="63" t="str">
+        <f>IF(M36="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N37" s="63" t="str">
+        <f>IF(M37="multiply",PROPER(B37)&amp;PROPER(C37),J36)</f>
+        <v>TbspcMl</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="18">
+      <c r="A38" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="60">
+        <f t="shared" si="1"/>
+        <v>0.20288413621105797</v>
+      </c>
+      <c r="G38" s="62">
+        <f>IF(M38="multiply",F38,F39)</f>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="H38" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="0"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="3"/>
+        <v>MlTspc</v>
+      </c>
+      <c r="K38" t="str">
+        <f>"constFactor"&amp;J38</f>
+        <v>constFactorMlTspc</v>
+      </c>
+      <c r="M38" s="62" t="str">
+        <f>IF(H38&gt;I38,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N38" s="62" t="str">
+        <f>IF(M38="multiply",PROPER(B38)&amp;PROPER(C38),J39)</f>
+        <v>TspcMl</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="18">
+      <c r="A39" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="60">
+        <f t="shared" si="1"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="G39" s="62">
+        <f>IF(M39="multiply",F39,F38)</f>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="H39" s="9">
+        <f t="shared" si="2"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="str">
         <f t="shared" si="3"/>
         <v>TspcMl</v>
       </c>
-      <c r="K35" t="str">
-        <f t="shared" ref="K35:K37" si="10">"constFactor"&amp;J35</f>
+      <c r="K39" t="str">
+        <f t="shared" ref="K39" si="10">"constFactor"&amp;J39</f>
         <v>constFactorTspcMl</v>
       </c>
-      <c r="M35" s="64" t="str">
-        <f>IF(M34="multiply","  divide","multiply")</f>
+      <c r="M39" s="62" t="str">
+        <f>IF(M38="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N35" s="64" t="str">
-        <f>IF(M35="multiply",PROPER(B35)&amp;PROPER(C35),J34)</f>
+      <c r="N39" s="62" t="str">
+        <f>IF(M39="multiply",PROPER(B39)&amp;PROPER(C39),J38)</f>
         <v>TspcMl</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="18">
-      <c r="A36" s="13" t="s">
+    <row r="40" spans="1:14" ht="18">
+      <c r="A40" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B40" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C40" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D40" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E40" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="62">
+      <c r="F40" s="60">
         <f t="shared" si="1"/>
         <v>5.9999940022377229</v>
       </c>
-      <c r="G36" s="65">
-        <f>IF(M36="multiply",F36,F37)</f>
+      <c r="G40" s="63">
+        <f>IF(M40="multiply",F40,F41)</f>
         <v>5.9999940022377229</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H40" s="9">
         <f t="shared" si="2"/>
         <v>29.573499999999999</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I40" s="9">
         <f t="shared" si="0"/>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J36" s="67" t="str">
+      <c r="J40" t="str">
         <f t="shared" si="3"/>
         <v>FzusTspc</v>
       </c>
-      <c r="K36" t="str">
-        <f>"constFactor"&amp;J36</f>
+      <c r="K40" t="str">
+        <f>"constFactor"&amp;J40</f>
         <v>constFactorFzusTspc</v>
       </c>
-      <c r="M36" s="65" t="str">
-        <f>IF(H36&gt;I36,"multiply","  divide")</f>
+      <c r="M40" s="63" t="str">
+        <f>IF(H40&gt;I40,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N36" s="65" t="str">
-        <f>IF(M36="multiply",PROPER(B36)&amp;PROPER(C36),J37)</f>
+      <c r="N40" s="63" t="str">
+        <f>IF(M40="multiply",PROPER(B40)&amp;PROPER(C40),J41)</f>
         <v>FzusTspc</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="19" thickBot="1">
-      <c r="A37" s="13" t="s">
+    <row r="41" spans="1:14" ht="19" thickBot="1">
+      <c r="A41" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B41" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C41" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E41" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="62">
+      <c r="F41" s="60">
         <f t="shared" si="1"/>
         <v>0.16666683327134091</v>
       </c>
-      <c r="G37" s="65">
-        <f>IF(M37="multiply",F37,F36)</f>
+      <c r="G41" s="63">
+        <f>IF(M41="multiply",F41,F40)</f>
         <v>5.9999940022377229</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H41" s="9">
         <f t="shared" si="2"/>
         <v>4.9289215937500002</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I41" s="9">
         <f t="shared" si="0"/>
         <v>29.573499999999999</v>
       </c>
-      <c r="J37" s="67" t="str">
+      <c r="J41" t="str">
         <f t="shared" si="3"/>
         <v>TspcFzus</v>
       </c>
-      <c r="K37" t="str">
-        <f t="shared" ref="K37" si="11">"constFactor"&amp;J37</f>
+      <c r="K41" t="str">
+        <f t="shared" ref="K41" si="11">"constFactor"&amp;J41</f>
         <v>constFactorTspcFzus</v>
       </c>
-      <c r="M37" s="65" t="str">
-        <f>IF(M36="multiply","  divide","multiply")</f>
+      <c r="M41" s="63" t="str">
+        <f>IF(M40="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N37" s="65" t="str">
-        <f>IF(M37="multiply",PROPER(B37)&amp;PROPER(C37),J36)</f>
+      <c r="N41" s="63" t="str">
+        <f>IF(M41="multiply",PROPER(B41)&amp;PROPER(C41),J40)</f>
         <v>FzusTspc</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="17" thickBot="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="63"/>
-      <c r="G38"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="67" t="str">
+    <row r="42" spans="1:14" ht="17" thickBot="1">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="61"/>
+      <c r="G42"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="18">
-      <c r="A39" s="13" t="s">
+    <row r="43" spans="1:14" ht="18">
+      <c r="A43" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B43" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C43" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D43" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E43" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="62">
+      <c r="F43" s="60">
         <f t="shared" si="1"/>
         <v>568.26125000000002</v>
       </c>
-      <c r="G39" s="64">
-        <f>IF(M39="multiply",F39,F40)</f>
+      <c r="G43" s="62">
+        <f>IF(M43="multiply",F43,F44)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="H39" s="9">
-        <f t="shared" ref="H39:H55" si="12" xml:space="preserve"> VLOOKUP(B39,units,4,0)</f>
+      <c r="H43" s="9">
+        <f t="shared" ref="H43:H59" si="12" xml:space="preserve"> VLOOKUP(B43,units,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="I39" s="9">
-        <f t="shared" ref="I39:I55" si="13" xml:space="preserve"> VLOOKUP(C39,units,4,0)</f>
+      <c r="I43" s="9">
+        <f t="shared" ref="I43:I59" si="13" xml:space="preserve"> VLOOKUP(C43,units,4,0)</f>
         <v>1</v>
       </c>
-      <c r="J39" s="67" t="str">
+      <c r="J43" t="str">
         <f t="shared" si="3"/>
         <v>PintukMl</v>
       </c>
-      <c r="K39" t="str">
-        <f>"constFactor"&amp;J39</f>
+      <c r="K43" t="str">
+        <f>"constFactor"&amp;J43</f>
         <v>constFactorPintukMl</v>
       </c>
-      <c r="M39" s="64" t="str">
-        <f>IF(H39&gt;I39,"multiply","  divide")</f>
+      <c r="M43" s="62" t="str">
+        <f>IF(H43&gt;I43,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N39" s="64" t="str">
-        <f>IF(M39="multiply",PROPER(B39)&amp;PROPER(C39),J40)</f>
+      <c r="N43" s="62" t="str">
+        <f>IF(M43="multiply",PROPER(B43)&amp;PROPER(C43),J44)</f>
         <v>PintukMl</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="18">
-      <c r="A40" s="13" t="s">
+    <row r="44" spans="1:14" ht="18">
+      <c r="A44" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B44" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C44" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D44" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E44" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F40" s="62">
+      <c r="F44" s="60">
         <f t="shared" si="1"/>
         <v>1.7597539863927023E-3</v>
       </c>
-      <c r="G40" s="64">
-        <f>IF(M40="multiply",F40,F39)</f>
+      <c r="G44" s="62">
+        <f>IF(M44="multiply",F44,F43)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H44" s="9">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I44" s="9">
         <f t="shared" si="13"/>
         <v>568.26125000000002</v>
       </c>
-      <c r="J40" s="67" t="str">
+      <c r="J44" t="str">
         <f t="shared" si="3"/>
         <v>MlPintuk</v>
       </c>
-      <c r="K40" t="str">
-        <f t="shared" ref="K40:K42" si="14">"constFactor"&amp;J40</f>
+      <c r="K44" t="str">
+        <f t="shared" ref="K44" si="14">"constFactor"&amp;J44</f>
         <v>constFactorMlPintuk</v>
       </c>
-      <c r="M40" s="64" t="str">
-        <f>IF(M39="multiply","  divide","multiply")</f>
+      <c r="M44" s="62" t="str">
+        <f>IF(M43="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N40" s="64" t="str">
-        <f>IF(M40="multiply",PROPER(B40)&amp;PROPER(C40),J39)</f>
+      <c r="N44" s="62" t="str">
+        <f>IF(M44="multiply",PROPER(B44)&amp;PROPER(C44),J43)</f>
         <v>PintukMl</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="18">
-      <c r="A41" s="13" t="s">
+    <row r="45" spans="1:14" ht="18">
+      <c r="A45" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B45" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C45" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E45" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="62">
+      <c r="F45" s="60">
         <f t="shared" si="1"/>
         <v>1136.5225</v>
       </c>
-      <c r="G41" s="65">
-        <f>IF(M41="multiply",F41,F42)</f>
+      <c r="G45" s="63">
+        <f>IF(M45="multiply",F45,F46)</f>
         <v>1136.5225</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H45" s="9">
         <f t="shared" si="12"/>
         <v>1136.5225</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I45" s="9">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="J41" s="67" t="str">
+      <c r="J45" t="str">
         <f t="shared" si="3"/>
         <v>QtMl</v>
       </c>
-      <c r="K41" t="str">
-        <f>"constFactor"&amp;J41</f>
+      <c r="K45" t="str">
+        <f>"constFactor"&amp;J45</f>
         <v>constFactorQtMl</v>
       </c>
-      <c r="M41" s="65" t="str">
-        <f>IF(H41&gt;I41,"multiply","  divide")</f>
+      <c r="M45" s="63" t="str">
+        <f>IF(H45&gt;I45,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N41" s="65" t="str">
-        <f>IF(M41="multiply",PROPER(B41)&amp;PROPER(C41),J42)</f>
+      <c r="N45" s="63" t="str">
+        <f>IF(M45="multiply",PROPER(B45)&amp;PROPER(C45),J46)</f>
         <v>QtMl</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="18">
-      <c r="A42" s="13" t="s">
+    <row r="46" spans="1:14" ht="18">
+      <c r="A46" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B46" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C46" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D46" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E46" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F46" s="60">
         <f t="shared" si="1"/>
         <v>8.7987699319635115E-4</v>
       </c>
-      <c r="G42" s="65">
-        <f>IF(M42="multiply",F42,F41)</f>
+      <c r="G46" s="63">
+        <f>IF(M46="multiply",F46,F45)</f>
         <v>1136.5225</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H46" s="9">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I46" s="9">
         <f t="shared" si="13"/>
         <v>1136.5225</v>
       </c>
-      <c r="J42" s="67" t="str">
+      <c r="J46" t="str">
         <f t="shared" si="3"/>
         <v>MlQt</v>
       </c>
-      <c r="K42" t="str">
-        <f t="shared" ref="K42" si="15">"constFactor"&amp;J42</f>
+      <c r="K46" t="str">
+        <f t="shared" ref="K46" si="15">"constFactor"&amp;J46</f>
         <v>constFactorMlQt</v>
       </c>
-      <c r="M42" s="65" t="str">
-        <f>IF(M41="multiply","  divide","multiply")</f>
+      <c r="M46" s="63" t="str">
+        <f>IF(M45="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N42" s="65" t="str">
-        <f>IF(M42="multiply",PROPER(B42)&amp;PROPER(C42),J41)</f>
+      <c r="N46" s="63" t="str">
+        <f>IF(M46="multiply",PROPER(B46)&amp;PROPER(C46),J45)</f>
         <v>QtMl</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="18">
-      <c r="A43" s="13" t="s">
+    <row r="47" spans="1:14" ht="18">
+      <c r="A47" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B47" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C47" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E47" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="62">
+      <c r="F47" s="60">
         <f t="shared" si="1"/>
         <v>0.10000013198154897</v>
       </c>
-      <c r="G43" s="64">
-        <f>IF(M43="multiply",F43,F44)</f>
+      <c r="G47" s="62">
+        <f>IF(M47="multiply",F47,F48)</f>
         <v>9.9999868018625211</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H47" s="9">
         <f t="shared" si="12"/>
         <v>28.4131</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I47" s="9">
         <f t="shared" si="13"/>
         <v>284.13062500000001</v>
       </c>
-      <c r="J43" s="67" t="str">
+      <c r="J47" t="str">
         <f t="shared" si="3"/>
         <v>FzukCupuk</v>
       </c>
-      <c r="K43" t="str">
-        <f>"constFactor"&amp;J43</f>
+      <c r="K47" t="str">
+        <f>"constFactor"&amp;J47</f>
         <v>constFactorFzukCupuk</v>
       </c>
-      <c r="M43" s="64" t="str">
-        <f>IF(H43&gt;I43,"multiply","  divide")</f>
+      <c r="M47" s="62" t="str">
+        <f>IF(H47&gt;I47,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N43" s="64" t="str">
-        <f>IF(M43="multiply",PROPER(B43)&amp;PROPER(C43),J44)</f>
+      <c r="N47" s="62" t="str">
+        <f>IF(M47="multiply",PROPER(B47)&amp;PROPER(C47),J48)</f>
         <v>CupukFzuk</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="18">
-      <c r="A44" s="13" t="s">
+    <row r="48" spans="1:14" ht="18">
+      <c r="A48" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B48" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C48" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D48" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E48" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F44" s="62">
+      <c r="F48" s="60">
         <f t="shared" si="1"/>
         <v>9.9999868018625211</v>
       </c>
-      <c r="G44" s="64">
-        <f>IF(M44="multiply",F44,F43)</f>
+      <c r="G48" s="62">
+        <f>IF(M48="multiply",F48,F47)</f>
         <v>9.9999868018625211</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H48" s="9">
         <f t="shared" si="12"/>
         <v>284.13062500000001</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I48" s="9">
         <f t="shared" si="13"/>
         <v>28.4131</v>
       </c>
-      <c r="J44" s="67" t="str">
+      <c r="J48" t="str">
         <f t="shared" si="3"/>
         <v>CupukFzuk</v>
       </c>
-      <c r="K44" t="str">
-        <f t="shared" ref="K44:K46" si="16">"constFactor"&amp;J44</f>
+      <c r="K48" t="str">
+        <f t="shared" ref="K48" si="16">"constFactor"&amp;J48</f>
         <v>constFactorCupukFzuk</v>
       </c>
-      <c r="M44" s="64" t="str">
-        <f>IF(M43="multiply","  divide","multiply")</f>
+      <c r="M48" s="62" t="str">
+        <f>IF(M47="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N44" s="64" t="str">
-        <f>IF(M44="multiply",PROPER(B44)&amp;PROPER(C44),J43)</f>
+      <c r="N48" s="62" t="str">
+        <f>IF(M48="multiply",PROPER(B48)&amp;PROPER(C48),J47)</f>
         <v>CupukFzuk</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="18">
-      <c r="A45" s="13" t="s">
+    <row r="49" spans="1:14" ht="18">
+      <c r="A49" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B49" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C49" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E49" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="62">
+      <c r="F49" s="60">
         <f t="shared" si="1"/>
         <v>1.6000021117047836</v>
       </c>
-      <c r="G45" s="65">
-        <f>IF(M45="multiply",F45,F46)</f>
+      <c r="G49" s="63">
+        <f>IF(M49="multiply",F49,F50)</f>
         <v>1.6000021117047836</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H49" s="9">
         <f t="shared" si="12"/>
         <v>28.4131</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I49" s="9">
         <f t="shared" si="13"/>
         <v>17.758164062500001</v>
       </c>
-      <c r="J45" s="67" t="str">
+      <c r="J49" t="str">
         <f t="shared" si="3"/>
         <v>FzukTbspuk</v>
       </c>
-      <c r="K45" t="str">
-        <f>"constFactor"&amp;J45</f>
+      <c r="K49" t="str">
+        <f>"constFactor"&amp;J49</f>
         <v>constFactorFzukTbspuk</v>
       </c>
-      <c r="M45" s="65" t="str">
-        <f>IF(H45&gt;I45,"multiply","  divide")</f>
+      <c r="M49" s="63" t="str">
+        <f>IF(H49&gt;I49,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N45" s="65" t="str">
-        <f>IF(M45="multiply",PROPER(B45)&amp;PROPER(C45),J46)</f>
+      <c r="N49" s="63" t="str">
+        <f>IF(M49="multiply",PROPER(B49)&amp;PROPER(C49),J50)</f>
         <v>FzukTbspuk</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="18">
-      <c r="A46" s="13" t="s">
+    <row r="50" spans="1:14" ht="18">
+      <c r="A50" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B50" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C50" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="49" t="s">
+      <c r="E50" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="62">
+      <c r="F50" s="60">
         <f t="shared" si="1"/>
         <v>0.62499917511640757</v>
       </c>
-      <c r="G46" s="65">
-        <f>IF(M46="multiply",F46,F45)</f>
+      <c r="G50" s="63">
+        <f>IF(M50="multiply",F50,F49)</f>
         <v>1.6000021117047836</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H50" s="9">
         <f t="shared" si="12"/>
         <v>17.758164062500001</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I50" s="9">
         <f t="shared" si="13"/>
         <v>28.4131</v>
       </c>
-      <c r="J46" s="67" t="str">
+      <c r="J50" t="str">
         <f t="shared" si="3"/>
         <v>TbspukFzuk</v>
       </c>
-      <c r="K46" t="str">
-        <f t="shared" ref="K46" si="17">"constFactor"&amp;J46</f>
+      <c r="K50" t="str">
+        <f t="shared" ref="K50" si="17">"constFactor"&amp;J50</f>
         <v>constFactorTbspukFzuk</v>
       </c>
-      <c r="M46" s="65" t="str">
-        <f>IF(M45="multiply","  divide","multiply")</f>
+      <c r="M50" s="63" t="str">
+        <f>IF(M49="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N46" s="65" t="str">
-        <f>IF(M46="multiply",PROPER(B46)&amp;PROPER(C46),J45)</f>
+      <c r="N50" s="63" t="str">
+        <f>IF(M50="multiply",PROPER(B50)&amp;PROPER(C50),J49)</f>
         <v>FzukTbspuk</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="18">
-      <c r="A47" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E47" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="F47" s="62">
-        <f t="shared" si="1"/>
-        <v>0.62499917511640757</v>
-      </c>
-      <c r="G47"/>
-      <c r="H47" s="9">
-        <f t="shared" si="12"/>
-        <v>17.758164062500001</v>
-      </c>
-      <c r="I47" s="9">
-        <f t="shared" si="13"/>
-        <v>28.4131</v>
-      </c>
-      <c r="J47" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspukFzuk</v>
-      </c>
-      <c r="K47" t="str">
-        <f t="shared" si="4"/>
-        <v>constFactorTbspukFzuk</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="18">
-      <c r="A48" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="62">
-        <f t="shared" si="1"/>
-        <v>3.5195079727854046E-3</v>
-      </c>
-      <c r="G48" s="64">
-        <f>IF(M48="multiply",F48,F49)</f>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="H48" s="9">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="I48" s="9">
-        <f t="shared" si="13"/>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="J48" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>MlCupuk</v>
-      </c>
-      <c r="K48" t="str">
-        <f>"constFactor"&amp;J48</f>
-        <v>constFactorMlCupuk</v>
-      </c>
-      <c r="M48" s="64" t="str">
-        <f>IF(H48&gt;I48,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N48" s="64" t="str">
-        <f>IF(M48="multiply",PROPER(B48)&amp;PROPER(C48),J49)</f>
-        <v>CupukMl</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="18">
-      <c r="A49" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F49" s="62">
-        <f t="shared" si="1"/>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="G49" s="64">
-        <f>IF(M49="multiply",F49,F48)</f>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="H49" s="9">
-        <f t="shared" si="12"/>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="I49" s="9">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="J49" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>CupukMl</v>
-      </c>
-      <c r="K49" t="str">
-        <f t="shared" ref="K49:K51" si="18">"constFactor"&amp;J49</f>
-        <v>constFactorCupukMl</v>
-      </c>
-      <c r="M49" s="64" t="str">
-        <f>IF(M48="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N49" s="64" t="str">
-        <f>IF(M49="multiply",PROPER(B49)&amp;PROPER(C49),J48)</f>
-        <v>CupukMl</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="18">
-      <c r="A50" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F50" s="62">
-        <f t="shared" si="1"/>
-        <v>5.6312127564566473E-2</v>
-      </c>
-      <c r="G50" s="65">
-        <f>IF(M50="multiply",F50,F51)</f>
-        <v>17.758164062500001</v>
-      </c>
-      <c r="H50" s="9">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="I50" s="9">
-        <f t="shared" si="13"/>
-        <v>17.758164062500001</v>
-      </c>
-      <c r="J50" s="67" t="str">
-        <f t="shared" si="3"/>
-        <v>MlTbspuk</v>
-      </c>
-      <c r="K50" t="str">
-        <f>"constFactor"&amp;J50</f>
-        <v>constFactorMlTbspuk</v>
-      </c>
-      <c r="M50" s="65" t="str">
-        <f>IF(H50&gt;I50,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N50" s="65" t="str">
-        <f>IF(M50="multiply",PROPER(B50)&amp;PROPER(C50),J51)</f>
-        <v>TbspukMl</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="18">
       <c r="A51" s="13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>79</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" s="62">
-        <f t="shared" si="1"/>
-        <v>17.758164062500001</v>
-      </c>
-      <c r="G51" s="65">
-        <f>IF(M51="multiply",F51,F50)</f>
-        <v>17.758164062500001</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E51" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" s="60">
+        <f t="shared" si="1"/>
+        <v>0.62499917511640757</v>
+      </c>
+      <c r="G51"/>
       <c r="H51" s="9">
         <f t="shared" si="12"/>
         <v>17.758164062500001</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="J51" s="67" t="str">
+        <v>28.4131</v>
+      </c>
+      <c r="J51" t="str">
         <f t="shared" si="3"/>
-        <v>TbspukMl</v>
+        <v>TbspukFzuk</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" ref="K51" si="19">"constFactor"&amp;J51</f>
-        <v>constFactorTbspukMl</v>
-      </c>
-      <c r="M51" s="65" t="str">
-        <f>IF(M50="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N51" s="65" t="str">
-        <f>IF(M51="multiply",PROPER(B51)&amp;PROPER(C51),J50)</f>
-        <v>TbspukMl</v>
+        <f t="shared" si="4"/>
+        <v>constFactorTbspukFzuk</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="18">
       <c r="A52" s="13" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F52" s="62">
-        <f t="shared" si="1"/>
-        <v>0.16893638269370037</v>
-      </c>
-      <c r="G52" s="64">
+        <v>45</v>
+      </c>
+      <c r="F52" s="60">
+        <f t="shared" si="1"/>
+        <v>3.5195079727854046E-3</v>
+      </c>
+      <c r="G52" s="62">
         <f>IF(M52="multiply",F52,F53)</f>
-        <v>5.9193880208333001</v>
+        <v>284.13062500000001</v>
       </c>
       <c r="H52" s="9">
         <f t="shared" si="12"/>
@@ -5068,170 +5528,775 @@
       </c>
       <c r="I52" s="9">
         <f t="shared" si="13"/>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="J52" s="67" t="str">
+        <v>284.13062500000001</v>
+      </c>
+      <c r="J52" t="str">
         <f t="shared" si="3"/>
-        <v>MlTspuk</v>
+        <v>MlCupuk</v>
       </c>
       <c r="K52" t="str">
         <f>"constFactor"&amp;J52</f>
-        <v>constFactorMlTspuk</v>
-      </c>
-      <c r="M52" s="64" t="str">
+        <v>constFactorMlCupuk</v>
+      </c>
+      <c r="M52" s="62" t="str">
         <f>IF(H52&gt;I52,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N52" s="64" t="str">
+      <c r="N52" s="62" t="str">
         <f>IF(M52="multiply",PROPER(B52)&amp;PROPER(C52),J53)</f>
-        <v>TspukMl</v>
+        <v>CupukMl</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="18">
       <c r="A53" s="13" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" s="62">
-        <f t="shared" si="1"/>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="G53" s="64">
+        <v>47</v>
+      </c>
+      <c r="F53" s="60">
+        <f t="shared" si="1"/>
+        <v>284.13062500000001</v>
+      </c>
+      <c r="G53" s="62">
         <f>IF(M53="multiply",F53,F52)</f>
-        <v>5.9193880208333001</v>
+        <v>284.13062500000001</v>
       </c>
       <c r="H53" s="9">
         <f t="shared" si="12"/>
-        <v>5.9193880208333001</v>
+        <v>284.13062500000001</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="J53" s="67" t="str">
+      <c r="J53" t="str">
+        <f t="shared" si="3"/>
+        <v>CupukMl</v>
+      </c>
+      <c r="K53" t="str">
+        <f t="shared" ref="K53" si="18">"constFactor"&amp;J53</f>
+        <v>constFactorCupukMl</v>
+      </c>
+      <c r="M53" s="62" t="str">
+        <f>IF(M52="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N53" s="62" t="str">
+        <f>IF(M53="multiply",PROPER(B53)&amp;PROPER(C53),J52)</f>
+        <v>CupukMl</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="18">
+      <c r="A54" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="60">
+        <f t="shared" si="1"/>
+        <v>5.6312127564566473E-2</v>
+      </c>
+      <c r="G54" s="63">
+        <f>IF(M54="multiply",F54,F55)</f>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="H54" s="9">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="9">
+        <f t="shared" si="13"/>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="3"/>
+        <v>MlTbspuk</v>
+      </c>
+      <c r="K54" t="str">
+        <f>"constFactor"&amp;J54</f>
+        <v>constFactorMlTbspuk</v>
+      </c>
+      <c r="M54" s="63" t="str">
+        <f>IF(H54&gt;I54,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N54" s="63" t="str">
+        <f>IF(M54="multiply",PROPER(B54)&amp;PROPER(C54),J55)</f>
+        <v>TbspukMl</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="18">
+      <c r="A55" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" s="60">
+        <f t="shared" si="1"/>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="G55" s="63">
+        <f>IF(M55="multiply",F55,F54)</f>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="H55" s="9">
+        <f t="shared" si="12"/>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="I55" s="9">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="str">
+        <f t="shared" si="3"/>
+        <v>TbspukMl</v>
+      </c>
+      <c r="K55" t="str">
+        <f t="shared" ref="K55" si="19">"constFactor"&amp;J55</f>
+        <v>constFactorTbspukMl</v>
+      </c>
+      <c r="M55" s="63" t="str">
+        <f>IF(M54="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N55" s="63" t="str">
+        <f>IF(M55="multiply",PROPER(B55)&amp;PROPER(C55),J54)</f>
+        <v>TbspukMl</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="18">
+      <c r="A56" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="60">
+        <f t="shared" si="1"/>
+        <v>0.16893638269370037</v>
+      </c>
+      <c r="G56" s="62">
+        <f>IF(M56="multiply",F56,F57)</f>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="H56" s="9">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="9">
+        <f t="shared" si="13"/>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="3"/>
+        <v>MlTspuk</v>
+      </c>
+      <c r="K56" t="str">
+        <f>"constFactor"&amp;J56</f>
+        <v>constFactorMlTspuk</v>
+      </c>
+      <c r="M56" s="62" t="str">
+        <f>IF(H56&gt;I56,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N56" s="62" t="str">
+        <f>IF(M56="multiply",PROPER(B56)&amp;PROPER(C56),J57)</f>
+        <v>TspukMl</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="18">
+      <c r="A57" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="60">
+        <f t="shared" si="1"/>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="G57" s="62">
+        <f>IF(M57="multiply",F57,F56)</f>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="H57" s="9">
+        <f t="shared" si="12"/>
+        <v>5.9193880208333001</v>
+      </c>
+      <c r="I57" s="9">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="str">
         <f t="shared" si="3"/>
         <v>TspukMl</v>
       </c>
-      <c r="K53" t="str">
-        <f t="shared" ref="K53:K55" si="20">"constFactor"&amp;J53</f>
+      <c r="K57" t="str">
+        <f t="shared" ref="K57" si="20">"constFactor"&amp;J57</f>
         <v>constFactorTspukMl</v>
       </c>
-      <c r="M53" s="64" t="str">
-        <f>IF(M52="multiply","  divide","multiply")</f>
+      <c r="M57" s="62" t="str">
+        <f>IF(M56="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N53" s="64" t="str">
-        <f>IF(M53="multiply",PROPER(B53)&amp;PROPER(C53),J52)</f>
+      <c r="N57" s="62" t="str">
+        <f>IF(M57="multiply",PROPER(B57)&amp;PROPER(C57),J56)</f>
         <v>TspukMl</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="18">
-      <c r="A54" s="13" t="s">
+    <row r="58" spans="1:14" ht="18">
+      <c r="A58" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B58" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C58" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D58" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E58" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="62">
+      <c r="F58" s="60">
         <f t="shared" si="1"/>
         <v>4.8000063351143778</v>
       </c>
-      <c r="G54" s="65">
-        <f>IF(M54="multiply",F54,F55)</f>
+      <c r="G58" s="63">
+        <f>IF(M58="multiply",F58,F67)</f>
         <v>4.8000063351143778</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H58" s="9">
         <f t="shared" si="12"/>
         <v>28.4131</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I58" s="9">
         <f t="shared" si="13"/>
         <v>5.9193880208333001</v>
       </c>
-      <c r="J54" s="67" t="str">
+      <c r="J58" t="str">
         <f t="shared" si="3"/>
         <v>FzukTspuk</v>
       </c>
-      <c r="K54" t="str">
-        <f>"constFactor"&amp;J54</f>
+      <c r="K58" t="str">
+        <f>"constFactor"&amp;J58</f>
         <v>constFactorFzukTspuk</v>
       </c>
-      <c r="M54" s="65" t="str">
-        <f>IF(H54&gt;I54,"multiply","  divide")</f>
+      <c r="M58" s="63" t="str">
+        <f>IF(H58&gt;I58,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N54" s="65" t="str">
-        <f>IF(M54="multiply",PROPER(B54)&amp;PROPER(C54),J55)</f>
+      <c r="N58" s="63" t="str">
+        <f>IF(M58="multiply",PROPER(B58)&amp;PROPER(C58),J59)</f>
         <v>FzukTspuk</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="19" thickBot="1">
-      <c r="A55" s="13" t="s">
+    <row r="59" spans="1:14" ht="18">
+      <c r="A59" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B59" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C59" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D59" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E59" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F59" s="60">
         <f t="shared" si="1"/>
         <v>0.2083330583721347</v>
       </c>
-      <c r="G55" s="65">
-        <f>IF(M55="multiply",F55,F54)</f>
-        <v>4.8000063351143778</v>
-      </c>
-      <c r="H55" s="9">
+      <c r="G59" s="63">
+        <f>IF(M59="multiply",F59,F68)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
         <f t="shared" si="12"/>
         <v>5.9193880208333001</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I59" s="9">
         <f t="shared" si="13"/>
         <v>28.4131</v>
       </c>
-      <c r="J55" s="67" t="str">
+      <c r="J59" t="str">
         <f t="shared" si="3"/>
         <v>TspukFzuk</v>
       </c>
-      <c r="K55" t="str">
-        <f t="shared" ref="K55" si="21">"constFactor"&amp;J55</f>
+      <c r="K59" t="str">
+        <f>"constFactor"&amp;J59</f>
         <v>constFactorTspukFzuk</v>
       </c>
-      <c r="M55" s="65" t="str">
-        <f>IF(M54="multiply","  divide","multiply")</f>
+      <c r="M59" s="63" t="str">
+        <f>IF(M58="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N55" s="65" t="str">
-        <f>IF(M55="multiply",PROPER(B55)&amp;PROPER(C55),J54)</f>
+      <c r="N59" s="63" t="str">
+        <f>IF(M59="multiply",PROPER(B59)&amp;PROPER(C59),J58)</f>
         <v>FzukTspuk</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="18">
+      <c r="A60" s="76" t="str">
+        <f>MID(D60,5,99)</f>
+        <v>MLtoIN3</v>
+      </c>
+      <c r="B60" s="77" t="str">
+        <f>MID(A60,1,SEARCH("to",A60)-1)</f>
+        <v>ML</v>
+      </c>
+      <c r="C60" s="77" t="str">
+        <f>MID(A60,SEARCH("to",A60)+2,99)</f>
+        <v>IN3</v>
+      </c>
+      <c r="D60" s="72" t="s">
+        <v>200</v>
+      </c>
+      <c r="E60" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="60">
+        <f t="shared" si="1"/>
+        <v>6.1023744094732289E-2</v>
+      </c>
+      <c r="G60" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H60" s="9">
+        <f xml:space="preserve"> VLOOKUP(B60,units,4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I60" s="9">
+        <f t="shared" ref="I60:I67" si="21" xml:space="preserve"> VLOOKUP(C60,units,4,0)</f>
+        <v>16.387063999999999</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" ref="J60:J67" si="22">PROPER(B60)&amp;PROPER(C60)</f>
+        <v>MlIn3</v>
+      </c>
+      <c r="K60" t="str">
+        <f t="shared" ref="K60:K67" si="23">"constFactor"&amp;J60</f>
+        <v>constFactorMlIn3</v>
+      </c>
+      <c r="M60" s="62" t="str">
+        <f>IF(H60&gt;I60,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N60" s="62" t="str">
+        <f>IF(M60="multiply",PROPER(B60)&amp;PROPER(C60),J61)</f>
+        <v>In3Ml</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="18">
+      <c r="A61" s="76" t="str">
+        <f t="shared" ref="A61:A67" si="24">MID(D61,5,99)</f>
+        <v>IN3toML</v>
+      </c>
+      <c r="B61" s="77" t="str">
+        <f t="shared" ref="B61:B67" si="25">MID(A61,1,SEARCH("to",A61)-1)</f>
+        <v>IN3</v>
+      </c>
+      <c r="C61" s="77" t="str">
+        <f t="shared" ref="C61:C67" si="26">MID(A61,SEARCH("to",A61)+2,99)</f>
+        <v>ML</v>
+      </c>
+      <c r="D61" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="F61" s="60">
+        <f t="shared" si="1"/>
+        <v>16.387063999999999</v>
+      </c>
+      <c r="G61" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H61" s="9">
+        <f t="shared" ref="H60:H67" si="27" xml:space="preserve"> VLOOKUP(B61,units,4,0)</f>
+        <v>16.387063999999999</v>
+      </c>
+      <c r="I61" s="9">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="22"/>
+        <v>In3Ml</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorIn3Ml</v>
+      </c>
+      <c r="M61" s="62" t="str">
+        <f>IF(M60="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N61" s="62" t="str">
+        <f>IF(M61="multiply",PROPER(B61)&amp;PROPER(C61),J60)</f>
+        <v>In3Ml</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="18">
+      <c r="A62" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>FT3toGLUK</v>
+      </c>
+      <c r="B62" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>FT3</v>
+      </c>
+      <c r="C62" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>GLUK</v>
+      </c>
+      <c r="D62" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="E62" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" s="60">
+        <f t="shared" si="1"/>
+        <v>6.2302059127542027</v>
+      </c>
+      <c r="G62" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H62" s="9">
+        <f t="shared" si="27"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="I62" s="9">
+        <f t="shared" si="21"/>
+        <v>4545.09</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="22"/>
+        <v>Ft3Gluk</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorFt3Gluk</v>
+      </c>
+      <c r="M62" s="63" t="str">
+        <f>IF(H62&gt;I62,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N62" s="63" t="str">
+        <f>IF(M62="multiply",PROPER(B62)&amp;PROPER(C62),J63)</f>
+        <v>Ft3Gluk</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="18">
+      <c r="A63" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>GLUKtoFT3</v>
+      </c>
+      <c r="B63" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>GLUK</v>
+      </c>
+      <c r="C63" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>FT3</v>
+      </c>
+      <c r="D63" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="E63" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="60">
+        <f t="shared" si="1"/>
+        <v>0.16050833856917057</v>
+      </c>
+      <c r="G63" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H63" s="9">
+        <f t="shared" si="27"/>
+        <v>4545.09</v>
+      </c>
+      <c r="I63" s="9">
+        <f t="shared" si="21"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="22"/>
+        <v>GlukFt3</v>
+      </c>
+      <c r="K63" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorGlukFt3</v>
+      </c>
+      <c r="M63" s="63" t="str">
+        <f>IF(M62="multiply","  divide","multiply")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N63" s="63" t="str">
+        <f>IF(M63="multiply",PROPER(B63)&amp;PROPER(C63),J62)</f>
+        <v>Ft3Gluk</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="18">
+      <c r="A64" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>LtoFT3</v>
+      </c>
+      <c r="B64" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>L</v>
+      </c>
+      <c r="C64" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>FT3</v>
+      </c>
+      <c r="D64" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="60">
+        <f t="shared" si="1"/>
+        <v>3.5314666721488586E-2</v>
+      </c>
+      <c r="G64" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H64" s="9">
+        <f t="shared" si="27"/>
+        <v>1000</v>
+      </c>
+      <c r="I64" s="9">
+        <f t="shared" si="21"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="22"/>
+        <v>LFt3</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorLFt3</v>
+      </c>
+      <c r="M64" s="62" t="str">
+        <f>IF(H64&gt;I64,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N64" s="62" t="str">
+        <f>IF(M64="multiply",PROPER(B64)&amp;PROPER(C64),J65)</f>
+        <v>Ft3L</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="18">
+      <c r="A65" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>FT3toL</v>
+      </c>
+      <c r="B65" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>FT3</v>
+      </c>
+      <c r="C65" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>L</v>
+      </c>
+      <c r="D65" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="E65" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="60">
+        <f t="shared" si="1"/>
+        <v>28.316846592000001</v>
+      </c>
+      <c r="G65" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H65" s="9">
+        <f t="shared" si="27"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="I65" s="9">
+        <f t="shared" si="21"/>
+        <v>1000</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="22"/>
+        <v>Ft3L</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorFt3L</v>
+      </c>
+      <c r="M65" s="62" t="str">
+        <f>IF(M64="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N65" s="62" t="str">
+        <f>IF(M65="multiply",PROPER(B65)&amp;PROPER(C65),J64)</f>
+        <v>Ft3L</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="18">
+      <c r="A66" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>LtoQTUS</v>
+      </c>
+      <c r="B66" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>L</v>
+      </c>
+      <c r="C66" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>QTUS</v>
+      </c>
+      <c r="D66" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="F66" s="60">
+        <f t="shared" si="1"/>
+        <v>1.0566882094325938</v>
+      </c>
+      <c r="G66" s="63">
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H66" s="9">
+        <f t="shared" si="27"/>
+        <v>1000</v>
+      </c>
+      <c r="I66" s="9">
+        <f t="shared" si="21"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="22"/>
+        <v>LQtus</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorLQtus</v>
+      </c>
+      <c r="M66" s="63" t="str">
+        <f>IF(H66&gt;I66,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N66" s="63" t="str">
+        <f>IF(M66="multiply",PROPER(B66)&amp;PROPER(C66),J67)</f>
+        <v>LQtus</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="19" thickBot="1">
+      <c r="A67" s="76" t="str">
+        <f t="shared" si="24"/>
+        <v>QTUStoL</v>
+      </c>
+      <c r="B67" s="77" t="str">
+        <f t="shared" si="25"/>
+        <v>QTUS</v>
+      </c>
+      <c r="C67" s="77" t="str">
+        <f t="shared" si="26"/>
+        <v>L</v>
+      </c>
+      <c r="D67" s="74" t="s">
+        <v>207</v>
+      </c>
+      <c r="E67" s="75" t="s">
+        <v>215</v>
+      </c>
+      <c r="F67" s="60">
+        <f t="shared" si="1"/>
+        <v>0.94635294599999997</v>
+      </c>
+      <c r="G67" s="63">
+        <f>IF(M67="multiply",F67,F58)</f>
+        <v>4.8000063351143778</v>
+      </c>
+      <c r="H67" s="9">
+        <f t="shared" si="27"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="I67" s="9">
+        <f t="shared" si="21"/>
+        <v>1000</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="22"/>
+        <v>QtusL</v>
+      </c>
+      <c r="K67" t="str">
+        <f t="shared" si="23"/>
+        <v>constFactorQtusL</v>
+      </c>
+      <c r="M67" s="63" t="str">
+        <f>IF(M66="multiply","  divide","multiply")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N67" s="63" t="str">
+        <f>IF(M67="multiply",PROPER(B67)&amp;PROPER(C67),J66)</f>
+        <v>LQtus</v>
       </c>
     </row>
   </sheetData>
@@ -5242,7 +6307,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF49E5-C5CF-EF45-BD21-7588D88F54A2}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -5513,6 +6578,70 @@
         <v>175</v>
       </c>
     </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>206</v>
+      </c>
+      <c r="B42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14234EB1-98E8-3E44-B1AF-037F6CB95FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69650D8-B696-0746-A9BE-43274DB0E2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="33600" windowHeight="20520" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
+    <workbookView xWindow="5380" yWindow="600" windowWidth="32800" windowHeight="20500" activeTab="2" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
   <sheets>
     <sheet name="Items and code" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="230">
   <si>
     <t>ITM_PINTLQtoML</t>
   </si>
@@ -694,18 +694,9 @@
     <t>IN3</t>
   </si>
   <si>
-    <t xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</t>
-  </si>
-  <si>
     <t>"m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3</t>
   </si>
   <si>
-    <t>"ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK</t>
-  </si>
-  <si>
-    <t>"GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</t>
-  </si>
-  <si>
     <t>STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3</t>
   </si>
   <si>
@@ -731,6 +722,15 @@
   </si>
   <si>
     <t>ml x 1000</t>
+  </si>
+  <si>
+    <t>"ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK</t>
+  </si>
+  <si>
+    <t>"gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</t>
+  </si>
+  <si>
+    <t>"in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</t>
   </si>
 </sst>
 </file>
@@ -3362,15 +3362,15 @@
         <v>multiply</v>
       </c>
       <c r="F35" s="81" t="str">
-        <f t="shared" ref="F35:F43" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
+        <f t="shared" ref="F35:F42" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
       <c r="G35" s="81" t="str">
-        <f t="shared" ref="G35:G43" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
+        <f t="shared" ref="G35:G42" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
       <c r="H35" s="49" t="str">
-        <f t="shared" ref="H35:H43" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
+        <f t="shared" ref="H35:H42" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
       <c r="I35" s="79">
@@ -3378,7 +3378,7 @@
         <v>5.9193880208333001</v>
       </c>
       <c r="J35" s="79" t="str">
-        <f t="shared" ref="J35:J43" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+        <f t="shared" ref="J35:J42" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K35" s="82" t="str">
@@ -3386,11 +3386,11 @@
         <v>TspukMl</v>
       </c>
       <c r="L35" s="50" t="str">
-        <f t="shared" ref="L35:L43" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
+        <f t="shared" ref="L35:L42" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833300000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N35" s="65" t="str">
-        <f t="shared" ref="N35:N43" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
+        <f t="shared" ref="N35:N42" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
         <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
       </c>
     </row>
@@ -3465,15 +3465,15 @@
       </c>
       <c r="F37" s="81" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</v>
+        <v>"in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</v>
       </c>
       <c r="G37" s="81" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve"> "in" STD_SUP_3 STD_RIGHT_ARROW</v>
+        <v>"in" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
       <c r="H37" s="49" t="str">
         <f t="shared" si="8"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorIn3Ml,         multiply,       "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre,                "in" STD_SUP_3 STD_RIGHT_ARROW                             ),</v>
+        <v>/* NNNN */  UNIT_CONV(constFactorIn3Ml,         multiply,      "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre,                "in" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
       <c r="I37" s="79">
         <f>VLOOKUP(A37,Factors!D:G,4,0)</f>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="F38" s="81" t="str">
         <f t="shared" si="6"/>
-        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK</v>
+        <v>"ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK</v>
       </c>
       <c r="G38" s="81" t="str">
         <f t="shared" si="7"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H38" s="49" t="str">
         <f t="shared" si="8"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorFt3Gluk,       multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW "GL" STD_UK,                  "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
+        <v>/* NNNN */  UNIT_CONV(constFactorFt3Gluk,       multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK,                 "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
       <c r="I38" s="79">
         <f>VLOOKUP(A38,Factors!D:G,4,0)</f>
@@ -3567,15 +3567,15 @@
       </c>
       <c r="F39" s="81" t="str">
         <f t="shared" si="6"/>
-        <v>"GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</v>
+        <v>"gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</v>
       </c>
       <c r="G39" s="81" t="str">
         <f t="shared" si="7"/>
-        <v>"GL" STD_UK STD_RIGHT_ARROW</v>
+        <v>"gal" STD_UK STD_RIGHT_ARROW</v>
       </c>
       <c r="H39" s="49" t="str">
         <f t="shared" si="8"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorGlukFt3,         divide,      "GL" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3,                  "GL" STD_UK STD_RIGHT_ARROW                                 ),</v>
+        <v>/* NNNN */  UNIT_CONV(constFactorGlukFt3,         divide,      "gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3,                 "gal" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
       <c r="I39" s="79">
         <f>VLOOKUP(A39,Factors!D:G,4,0)</f>
@@ -3843,7 +3843,7 @@
     <col min="3" max="3" width="7.83203125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="8" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="13" spans="1:14" ht="19" thickBot="1">
       <c r="A13" s="77" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>73</v>
@@ -4111,7 +4111,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="77" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>76</v>
@@ -4214,34 +4214,34 @@
         <v>16.387063999999999</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J19" s="43"/>
       <c r="K19" s="44"/>
     </row>
     <row r="20" spans="1:14">
       <c r="C20" s="77" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F20" s="78">
         <f>(12*2.54)^3</f>
         <v>28316.846592000002</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J20" s="43"/>
       <c r="K20" s="44"/>
     </row>
     <row r="21" spans="1:14">
       <c r="C21" s="77" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F21" s="53">
         <v>1000</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J21" s="43"/>
       <c r="K21" s="44"/>
@@ -5968,7 +5968,7 @@
         <v>4.8000063351143778</v>
       </c>
       <c r="H61" s="9">
-        <f t="shared" ref="H60:H67" si="27" xml:space="preserve"> VLOOKUP(B61,units,4,0)</f>
+        <f t="shared" ref="H61:H67" si="27" xml:space="preserve"> VLOOKUP(B61,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
       <c r="I61" s="9">
@@ -6307,7 +6307,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF49E5-C5CF-EF45-BD21-7588D88F54A2}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -6562,7 +6562,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -6578,68 +6578,92 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:3" ht="18">
       <c r="A36" t="s">
         <v>200</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>217</v>
+      </c>
+      <c r="C36" s="69" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18">
       <c r="A37" t="s">
         <v>201</v>
       </c>
       <c r="B37" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>229</v>
+      </c>
+      <c r="C37" s="69" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18">
       <c r="A38" t="s">
         <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>227</v>
+      </c>
+      <c r="C38" s="69" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18">
       <c r="A39" t="s">
         <v>203</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>228</v>
+      </c>
+      <c r="C39" s="69" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18">
       <c r="A40" t="s">
         <v>204</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>218</v>
+      </c>
+      <c r="C40" s="69" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18">
       <c r="A41" t="s">
         <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>219</v>
+      </c>
+      <c r="C41" s="69" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18">
       <c r="A42" t="s">
         <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>220</v>
+      </c>
+      <c r="C42" s="69" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18">
       <c r="A43" t="s">
         <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="C43" s="69" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69650D8-B696-0746-A9BE-43274DB0E2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C493F16-73EA-3F4D-917E-7165F241C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5380" yWindow="600" windowWidth="32800" windowHeight="20500" activeTab="2" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="20500" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
   <sheets>
     <sheet name="Items and code" sheetId="1" r:id="rId1"/>
@@ -1700,8 +1700,9 @@
     <col min="6" max="6" width="58.83203125" style="79" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="58.83203125" style="79" customWidth="1"/>
     <col min="8" max="8" width="225" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5" style="79" customWidth="1"/>
-    <col min="10" max="11" width="10.83203125" style="79"/>
+    <col min="9" max="9" width="12.1640625" style="79" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="79" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="79" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="144.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -3324,11 +3325,11 @@
       </c>
       <c r="I34" s="79">
         <f>VLOOKUP(A34,Factors!D:G,4,0)</f>
-        <v>0</v>
+        <v>4.8000063351143778</v>
       </c>
       <c r="J34" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>0.000000000000000000000000000000000000000000000000000000e+00</v>
+        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K34" s="82" t="str">
         <f>VLOOKUP(A34,Factors!D:N,11,0)</f>
@@ -3426,11 +3427,11 @@
       </c>
       <c r="I36" s="79">
         <f>VLOOKUP(A36,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>16.387063999999999</v>
       </c>
       <c r="J36" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
       <c r="K36" s="82" t="str">
         <f>VLOOKUP(A36,Factors!D:N,11,0)</f>
@@ -3477,11 +3478,11 @@
       </c>
       <c r="I37" s="79">
         <f>VLOOKUP(A37,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>16.387063999999999</v>
       </c>
       <c r="J37" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
       <c r="K37" s="82" t="str">
         <f>VLOOKUP(A37,Factors!D:N,11,0)</f>
@@ -3489,7 +3490,7 @@
       </c>
       <c r="L37" s="50" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  generateConstantArray("In3Ml",         "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+        <v xml:space="preserve">  generateConstantArray("In3Ml",         "+1.638706400000000000000000000000000000000000000000000000e+01");</v>
       </c>
       <c r="N37" s="65" t="str">
         <f t="shared" si="11"/>
@@ -3528,11 +3529,11 @@
       </c>
       <c r="I38" s="79">
         <f>VLOOKUP(A38,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>6.2302059127542027</v>
       </c>
       <c r="J38" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>6.230205912754200000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K38" s="82" t="str">
         <f>VLOOKUP(A38,Factors!D:N,11,0)</f>
@@ -3540,7 +3541,7 @@
       </c>
       <c r="L38" s="50" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  generateConstantArray("Ft3Gluk",       "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+        <v xml:space="preserve">  generateConstantArray("Ft3Gluk",       "+6.230205912754200000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N38" s="65" t="str">
         <f t="shared" si="11"/>
@@ -3579,11 +3580,11 @@
       </c>
       <c r="I39" s="79">
         <f>VLOOKUP(A39,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>6.2302059127542027</v>
       </c>
       <c r="J39" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>6.230205912754200000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K39" s="82" t="str">
         <f>VLOOKUP(A39,Factors!D:N,11,0)</f>
@@ -3630,11 +3631,11 @@
       </c>
       <c r="I40" s="79">
         <f>VLOOKUP(A40,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>28.316846592000001</v>
       </c>
       <c r="J40" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
       <c r="K40" s="82" t="str">
         <f>VLOOKUP(A40,Factors!D:N,11,0)</f>
@@ -3681,11 +3682,11 @@
       </c>
       <c r="I41" s="79">
         <f>VLOOKUP(A41,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>28.316846592000001</v>
       </c>
       <c r="J41" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
       <c r="K41" s="82" t="str">
         <f>VLOOKUP(A41,Factors!D:N,11,0)</f>
@@ -3693,7 +3694,7 @@
       </c>
       <c r="L41" s="50" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  generateConstantArray("Ft3L",          "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+        <v xml:space="preserve">  generateConstantArray("Ft3L",          "+2.831684659200000000000000000000000000000000000000000000e+01");</v>
       </c>
       <c r="N41" s="65" t="str">
         <f t="shared" si="11"/>
@@ -3732,11 +3733,11 @@
       </c>
       <c r="I42" s="79">
         <f>VLOOKUP(A42,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>1.0566882094325938</v>
       </c>
       <c r="J42" s="79" t="str">
         <f t="shared" si="9"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K42" s="82" t="str">
         <f>VLOOKUP(A42,Factors!D:N,11,0)</f>
@@ -3744,7 +3745,7 @@
       </c>
       <c r="L42" s="50" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  generateConstantArray("LQtus",         "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
+        <v xml:space="preserve">  generateConstantArray("LQtus",         "+1.056688209432590000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N42" s="65" t="str">
         <f t="shared" si="11"/>
@@ -3783,11 +3784,11 @@
       </c>
       <c r="I43" s="79">
         <f>VLOOKUP(A43,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
+        <v>1.0566882094325938</v>
       </c>
       <c r="J43" s="79" t="str">
         <f t="shared" si="3"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
+        <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K43" s="82" t="str">
         <f>VLOOKUP(A43,Factors!D:N,11,0)</f>
@@ -5813,7 +5814,7 @@
         <v>4.8000063351143778</v>
       </c>
       <c r="G58" s="63">
-        <f>IF(M58="multiply",F58,F67)</f>
+        <f>IF(M58="multiply",F58,F59)</f>
         <v>4.8000063351143778</v>
       </c>
       <c r="H58" s="9">
@@ -5862,8 +5863,8 @@
         <v>0.2083330583721347</v>
       </c>
       <c r="G59" s="63">
-        <f>IF(M59="multiply",F59,F68)</f>
-        <v>0</v>
+        <f>IF(M59="multiply",F59,F58)</f>
+        <v>4.8000063351143778</v>
       </c>
       <c r="H59" s="9">
         <f t="shared" si="12"/>
@@ -5913,8 +5914,9 @@
         <f t="shared" si="1"/>
         <v>6.1023744094732289E-2</v>
       </c>
-      <c r="G60" s="63">
-        <v>4.8000063351143778</v>
+      <c r="G60" s="62">
+        <f>IF(M60="multiply",F60,F61)</f>
+        <v>16.387063999999999</v>
       </c>
       <c r="H60" s="9">
         <f xml:space="preserve"> VLOOKUP(B60,units,4,0)</f>
@@ -5964,8 +5966,9 @@
         <f t="shared" si="1"/>
         <v>16.387063999999999</v>
       </c>
-      <c r="G61" s="63">
-        <v>4.8000063351143778</v>
+      <c r="G61" s="62">
+        <f>IF(M61="multiply",F61,F60)</f>
+        <v>16.387063999999999</v>
       </c>
       <c r="H61" s="9">
         <f t="shared" ref="H61:H67" si="27" xml:space="preserve"> VLOOKUP(B61,units,4,0)</f>
@@ -6016,7 +6019,8 @@
         <v>6.2302059127542027</v>
       </c>
       <c r="G62" s="63">
-        <v>4.8000063351143778</v>
+        <f>IF(M62="multiply",F62,F63)</f>
+        <v>6.2302059127542027</v>
       </c>
       <c r="H62" s="9">
         <f t="shared" si="27"/>
@@ -6067,7 +6071,8 @@
         <v>0.16050833856917057</v>
       </c>
       <c r="G63" s="63">
-        <v>4.8000063351143778</v>
+        <f>IF(M63="multiply",F63,F62)</f>
+        <v>6.2302059127542027</v>
       </c>
       <c r="H63" s="9">
         <f t="shared" si="27"/>
@@ -6117,8 +6122,9 @@
         <f t="shared" si="1"/>
         <v>3.5314666721488586E-2</v>
       </c>
-      <c r="G64" s="63">
-        <v>4.8000063351143778</v>
+      <c r="G64" s="62">
+        <f>IF(M64="multiply",F64,F65)</f>
+        <v>28.316846592000001</v>
       </c>
       <c r="H64" s="9">
         <f t="shared" si="27"/>
@@ -6168,8 +6174,9 @@
         <f t="shared" si="1"/>
         <v>28.316846592000001</v>
       </c>
-      <c r="G65" s="63">
-        <v>4.8000063351143778</v>
+      <c r="G65" s="62">
+        <f>IF(M65="multiply",F65,F64)</f>
+        <v>28.316846592000001</v>
       </c>
       <c r="H65" s="9">
         <f t="shared" si="27"/>
@@ -6220,7 +6227,8 @@
         <v>1.0566882094325938</v>
       </c>
       <c r="G66" s="63">
-        <v>4.8000063351143778</v>
+        <f>IF(M66="multiply",F66,F67)</f>
+        <v>1.0566882094325938</v>
       </c>
       <c r="H66" s="9">
         <f t="shared" si="27"/>
@@ -6271,8 +6279,8 @@
         <v>0.94635294599999997</v>
       </c>
       <c r="G67" s="63">
-        <f>IF(M67="multiply",F67,F58)</f>
-        <v>4.8000063351143778</v>
+        <f>IF(M67="multiply",F67,F66)</f>
+        <v>1.0566882094325938</v>
       </c>
       <c r="H67" s="9">
         <f t="shared" si="27"/>

--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C493F16-73EA-3F4D-917E-7165F241C196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14D795B-DB59-2B4E-9AA5-C58D6E9605F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="20500" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="20500" activeTab="1" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
   <sheets>
     <sheet name="Items and code" sheetId="1" r:id="rId1"/>
     <sheet name="Factors" sheetId="3" r:id="rId2"/>
-    <sheet name="STD" sheetId="2" r:id="rId3"/>
+    <sheet name="US Cutomary System" sheetId="4" r:id="rId3"/>
+    <sheet name="UK" sheetId="5" r:id="rId4"/>
+    <sheet name="STD" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="stdform">STD!$A:$B</definedName>
-    <definedName name="units">Factors!$C$3:$F$24</definedName>
+    <definedName name="units">Factors!$C$6:$F$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="262">
   <si>
     <t>ITM_PINTLQtoML</t>
   </si>
@@ -433,9 +435,6 @@
     <t>cup␭</t>
   </si>
   <si>
-    <t>1136,523?</t>
-  </si>
-  <si>
     <t>UK quart</t>
   </si>
   <si>
@@ -481,12 +480,6 @@
     <t>"ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q</t>
   </si>
   <si>
-    <t>"qt." STD_US STD_RIGHT_ARROW "ml"</t>
-  </si>
-  <si>
-    <t>"ml" STD_RIGHT_ARROW "qt." STD_US</t>
-  </si>
-  <si>
     <t>"floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</t>
   </si>
   <si>
@@ -529,12 +522,6 @@
     <t>"ml" STD_RIGHT_ARROW "pint" STD_UK</t>
   </si>
   <si>
-    <t>"qt." STD_UK STD_RIGHT_ARROW "ml"</t>
-  </si>
-  <si>
-    <t>"ml" STD_RIGHT_ARROW "qt." STD_UK</t>
-  </si>
-  <si>
     <t>"floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK</t>
   </si>
   <si>
@@ -571,30 +558,6 @@
     <t>"tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</t>
   </si>
   <si>
-    <t>cup US</t>
-  </si>
-  <si>
-    <t>pint US</t>
-  </si>
-  <si>
-    <t>liquid</t>
-  </si>
-  <si>
-    <t>floz US</t>
-  </si>
-  <si>
-    <t>cup UK</t>
-  </si>
-  <si>
-    <t>pint UK</t>
-  </si>
-  <si>
-    <t>floz UK</t>
-  </si>
-  <si>
-    <t>Ben: 15?</t>
-  </si>
-  <si>
     <t>ml     = pintuk × 568.26125</t>
   </si>
   <si>
@@ -607,9 +570,6 @@
     <t>US gallon</t>
   </si>
   <si>
-    <t>quart US</t>
-  </si>
-  <si>
     <t>ml     = tbspuk × 17.7581640625</t>
   </si>
   <si>
@@ -619,9 +579,6 @@
     <t>UK gallon</t>
   </si>
   <si>
-    <t>quart UK</t>
-  </si>
-  <si>
     <t>ml     = tspuk   × 5.9193880208333...</t>
   </si>
   <si>
@@ -715,15 +672,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>(ft × 12 × 2.54)^3</t>
-  </si>
-  <si>
-    <t>(in x 2.54) ^ 3</t>
-  </si>
-  <si>
-    <t>ml x 1000</t>
-  </si>
-  <si>
     <t>"ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK</t>
   </si>
   <si>
@@ -731,18 +679,328 @@
   </si>
   <si>
     <t>"in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 pint = 2 cup = 32 tbsp = 96 tsp </t>
+  </si>
+  <si>
+    <t>// l      = quart × 4.54609e-3 / 4 × 1000</t>
+  </si>
+  <si>
+    <t>// ml     = flozus × 231 × 0.0254³ / 128 × 1000000</t>
+  </si>
+  <si>
+    <t>updated from Martin's .c file and C47 constants</t>
+  </si>
+  <si>
+    <t>Checked and ok</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
+    <t>Pay attention repeating fraction</t>
+  </si>
+  <si>
+    <r>
+      <t>A tablespoon is a unit of volume equal to three </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>teaspoons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t> or ½ </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>fluid ounce</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>.[1] One tablespoon is equal to 14.7868 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>milliliters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>, but for nutrition labeling, one tablespoon is rounded to 15 milliliters.[2]</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.inchcalculator.com/convert/pint-to-tablespoon/</t>
+  </si>
+  <si>
+    <r>
+      <t>The tablespoon is a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> US customary uni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>t of volume. Tablespoons can be abbreviated as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>tbsp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>, and are also sometimes abbreviated as </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tbls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>, or </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444444"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>. For example, 1 tablespoon can be written as 1 tbsp, 1 T, 1 Tbls, or 1 Tb.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tbsn = pints × 32</t>
+  </si>
+  <si>
+    <t>1 Tbsn = 3 x tsp = 1/2 floz us</t>
+  </si>
+  <si>
+    <t>The US liquid pint is a unit of fluid volume equal to one-eighth of a gallon, one-half of a quart, or two cups. The liquid pint should not be confused with the dry pint (US) or the imperial pint, which are different units.</t>
+  </si>
+  <si>
+    <t>1 pint = 1/8 Gal us = 1/2 quart = 2 cups</t>
+  </si>
+  <si>
+    <t>All are precice to all digits shown here</t>
+  </si>
+  <si>
+    <t>// 1 lq pint = 32 Tbsns = (231 * 0.0254^3 / 128 * 1000000) / 2 * 32</t>
+  </si>
+  <si>
+    <t>// quart = 2 pint =(231*0.0254^3/128*1000000)/2*32*2</t>
+  </si>
+  <si>
+    <t>// ml      = galus × 231 × 0.0254³ × 1000000</t>
+  </si>
+  <si>
+    <t>// 1 cup = 1/2 pint = =(231*0.0254^3/128*1000000)/2*32/2</t>
+  </si>
+  <si>
+    <t>// 1 Tspn = 1/2 floz us = =(231 * 0.0254^3 / 128 * 1000000) / 2</t>
+  </si>
+  <si>
+    <t>// 1 tsp = 1/2/3 floz us = =(231 * 0.0254^3 / 128 * 1000000) / 2 / 3</t>
+  </si>
+  <si>
+    <t>GALLON	=	4.54609 cubic decimetres.</t>
+  </si>
+  <si>
+    <t>Quart	=	¼ gallon.</t>
+  </si>
+  <si>
+    <t>Fluid ounce = 1/20 pint.</t>
+  </si>
+  <si>
+    <t>Sch. 1 Pt. VI: definition of “fluid ounce” inserted (1.1.2000) by S.I. 1994/2867, reg. 7(3)(c)(i)</t>
+  </si>
+  <si>
+    <t>https://www.legislation.gov.uk/ukpga/1985/72</t>
+  </si>
+  <si>
+    <t>PINT = 0.568 261 25 cubic decimetre.</t>
+  </si>
+  <si>
+    <t>https://www.legislation.gov.uk/uksi/1994/2867/regulation/6/made#regulation-6-5-b-i</t>
+  </si>
+  <si>
+    <t>// ml     = flozuk × 4.54609e-3 / 160 × 1000000 // = 1/20 defined pint. = 568.26125 / 20</t>
+  </si>
+  <si>
+    <t>// ml      = galuk × 4.54609e-3 × 1000000, definition UK</t>
+  </si>
+  <si>
+    <t>// PINT = 0.568 261 25 dm^3 = 568.26125 cm^3, definition UK</t>
+  </si>
+  <si>
+    <t>The British imperial gallon (frequently called simply "gallon") is defined as exactly 4.54609 dm3 (4.54609 litres).[4] It is used in some Commonwealth countries, and until 1976 was defined as the volume of water at 62 °F (16.67 °C)[5][6] whose mass is 10 pounds (4.5359237 kg). There are four imperial quarts in a gallon, two imperial pints in a quart, and there are 20 imperial fluid ounces in an imperial pint,[4] yielding 160 fluid ounces in an imperial gallon.</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Gallon#Imperial_gallon</t>
+  </si>
+  <si>
+    <t>Thus, both gallons are equal to four quarts, eight pints, sixteen cups, or thirty-two gills.</t>
+  </si>
+  <si>
+    <t>1 gallon = 4 quarts = 8 pints = 16 cups = 160 floz</t>
+  </si>
+  <si>
+    <t>// (in x 2.54) ^ 3</t>
+  </si>
+  <si>
+    <t>// (ft × 12 × 2.54)^3</t>
+  </si>
+  <si>
+    <t>// ml x 1000</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Cooking_weights_and_measures</t>
+  </si>
+  <si>
+    <t>In the UK, teaspoons and tablespoons are formally 1⁄96 and 1⁄32 of an imperial pint (5.92 mL and 17.76 mL), respectively.</t>
+  </si>
+  <si>
+    <t>// 1 cup =  gallon /16 = =0.00454609 / 16 * 1000000</t>
+  </si>
+  <si>
+    <t>// 1 tbsp = pint /32 =568.26125/32</t>
+  </si>
+  <si>
+    <t>//1 tsp = pint / 96 =568.26125/96</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Mult. Of tsp</t>
+  </si>
+  <si>
+    <t>"qt" STD_US STD_RIGHT_ARROW "ml"</t>
+  </si>
+  <si>
+    <t>"ml" STD_RIGHT_ARROW "qt" STD_US</t>
+  </si>
+  <si>
+    <t>"qt" STD_UK STD_RIGHT_ARROW "ml"</t>
+  </si>
+  <si>
+    <t>"ml" STD_RIGHT_ARROW "qt" STD_UK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0000000000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0000000000000"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000"/>
+    <numFmt numFmtId="169" formatCode="0.00000000000"/>
+    <numFmt numFmtId="170" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="172" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -799,23 +1057,6 @@
       <name val="Calibri (Body)"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="C43__StandardFont StandardFont"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="C43__StandardFont StandardFont"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Consolas"/>
@@ -865,8 +1106,81 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="C47__StandardFont StandardFont"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="C47__StandardFont StandardFont"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -882,12 +1196,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,8 +1259,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1079,49 +1411,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1147,11 +1436,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1212,95 +1527,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1312,49 +1557,138 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="10" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1694,15 +2028,11 @@
   <cols>
     <col min="1" max="1" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" style="79" customWidth="1"/>
-    <col min="6" max="6" width="58.83203125" style="79" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.83203125" style="79" customWidth="1"/>
+    <col min="5" max="7" width="10.5" style="53" customWidth="1"/>
     <col min="8" max="8" width="225" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="79" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="79" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="79" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="5.83203125" style="53" customWidth="1"/>
     <col min="12" max="12" width="144.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,7 +2040,7 @@
     <row r="1" spans="1:14" ht="16">
       <c r="A1"/>
       <c r="B1"/>
-      <c r="F1" s="79">
+      <c r="F1" s="53">
         <f>LEN(F24)</f>
         <v>57</v>
       </c>
@@ -1723,8 +2053,8 @@
       <c r="B2"/>
     </row>
     <row r="3" spans="1:14" ht="16">
-      <c r="A3" s="51" t="s">
-        <v>197</v>
+      <c r="A3" s="32" t="s">
+        <v>182</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>64</v>
@@ -1732,2073 +2062,2073 @@
       <c r="C3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="G3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="I3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="J3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" s="80" t="s">
-        <v>199</v>
-      </c>
-      <c r="L3" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="N3" s="52" t="s">
-        <v>194</v>
+      <c r="D3" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="J3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="L3" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="64" t="str">
+      <c r="D4" s="40" t="str">
         <f>VLOOKUP(A4,Factors!D:K,8,0)</f>
         <v>constFactorCupcFzus</v>
       </c>
-      <c r="E4" s="79" t="str">
+      <c r="E4" s="53" t="str">
         <f>VLOOKUP(A4,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F4" s="81" t="str">
+      <c r="F4" s="55" t="str">
         <f t="shared" ref="F4:F43" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G4" s="81" t="str">
+      <c r="G4" s="55" t="str">
         <f>MID(F4,1,SEARCH("STD_RIGHT_ARROW",F4)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H4" s="49" t="str">
+      <c r="H4" s="30" t="str">
         <f>"/* NNNN */  UNIT_CONV("&amp;D4&amp;","&amp;REPT(CHAR(32),21-LEN(D4))&amp;"    "&amp;E4&amp;",      "&amp;F4&amp;","&amp;REPT(CHAR(32),60-LEN(F4))&amp;G4&amp;REPT(CHAR(32),60-LEN(G4))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcFzus,      multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I4" s="82">
+      <c r="I4" s="56">
         <f>VLOOKUP(A4,Factors!D:G,4,0)</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="J4" s="79" t="str">
+        <v>8</v>
+      </c>
+      <c r="J4" s="53" t="str">
         <f>SUBSTITUTE(TEXT(I4,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
-        <v>8.000007997024360000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K4" s="82" t="str">
+        <v>8.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K4" s="56" t="str">
         <f>VLOOKUP(A4,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
-      <c r="L4" s="50" t="str">
+      <c r="L4" s="31" t="str">
         <f>IF(E4="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K4&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K4))&amp;CHAR(34)&amp;"+"&amp;J4&amp;CHAR(34)&amp;");","")</f>
-        <v xml:space="preserve">  generateConstantArray("CupcFzus",      "+8.000007997024360000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N4" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("CupcFzus",      "+8.000000000000000000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N4" s="41" t="str">
         <f>"    ["&amp;D4&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K4&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcFzus] = &amp;const_CupcFzus,</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="64" t="str">
+      <c r="D5" s="40" t="str">
         <f>VLOOKUP(A5,Factors!D:K,8,0)</f>
         <v>constFactorCupcMl</v>
       </c>
-      <c r="E5" s="79" t="str">
+      <c r="E5" s="53" t="str">
         <f>VLOOKUP(A5,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F5" s="81" t="str">
+      <c r="F5" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G5" s="81" t="str">
+      <c r="G5" s="55" t="str">
         <f t="shared" ref="G5:G43" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H5" s="49" t="str">
+      <c r="H5" s="30" t="str">
         <f t="shared" ref="H5:H43" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcMl,        multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="53">
         <f>VLOOKUP(A5,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J5" s="79" t="str">
+      <c r="J5" s="53" t="str">
         <f t="shared" ref="J5:J43" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K5" s="82" t="str">
+      <c r="K5" s="56" t="str">
         <f>VLOOKUP(A5,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
-      <c r="L5" s="50" t="str">
+      <c r="L5" s="31" t="str">
         <f t="shared" ref="L5:L43" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("CupcMl",        "+2.365882365000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N5" s="65" t="str">
+      <c r="N5" s="41" t="str">
         <f t="shared" ref="N5:N43" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcMl] = &amp;const_CupcMl,</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="40" t="str">
         <f>VLOOKUP(A6,Factors!D:K,8,0)</f>
         <v>constFactorCupukFzuk</v>
       </c>
-      <c r="E6" s="79" t="str">
+      <c r="E6" s="53" t="str">
         <f>VLOOKUP(A6,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F6" s="81" t="str">
+      <c r="F6" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G6" s="81" t="str">
+      <c r="G6" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H6" s="49" t="str">
+      <c r="H6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukFzuk,     multiply,      "cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I6" s="79">
+      <c r="I6" s="53">
         <f>VLOOKUP(A6,Factors!D:G,4,0)</f>
-        <v>9.9999868018625211</v>
-      </c>
-      <c r="J6" s="79" t="str">
+        <v>10</v>
+      </c>
+      <c r="J6" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>9.999986801862520000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K6" s="82" t="str">
+        <v>1.000000000000000000000000000000000000000000000000000000e+01</v>
+      </c>
+      <c r="K6" s="56" t="str">
         <f>VLOOKUP(A6,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
-      <c r="L6" s="50" t="str">
+      <c r="L6" s="31" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("CupukFzuk",     "+9.999986801862520000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N6" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("CupukFzuk",     "+1.000000000000000000000000000000000000000000000000000000e+01");</v>
+      </c>
+      <c r="N6" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorCupukFzuk] = &amp;const_CupukFzuk,</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="64" t="str">
+      <c r="D7" s="40" t="str">
         <f>VLOOKUP(A7,Factors!D:K,8,0)</f>
         <v>constFactorCupukMl</v>
       </c>
-      <c r="E7" s="79" t="str">
+      <c r="E7" s="53" t="str">
         <f>VLOOKUP(A7,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F7" s="81" t="str">
+      <c r="F7" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G7" s="81" t="str">
+      <c r="G7" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H7" s="49" t="str">
+      <c r="H7" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukMl,       multiply,      "cup" STD_UK STD_RIGHT_ARROW "ml",                           "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="53">
         <f>VLOOKUP(A7,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J7" s="79" t="str">
+      <c r="J7" s="53" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K7" s="82" t="str">
+      <c r="K7" s="56" t="str">
         <f>VLOOKUP(A7,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
-      <c r="L7" s="50" t="str">
+      <c r="L7" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("CupukMl",       "+2.841306250000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N7" s="65" t="str">
+      <c r="N7" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorCupukMl] = &amp;const_CupukMl,</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="64" t="str">
+      <c r="D8" s="40" t="str">
         <f>VLOOKUP(A8,Factors!D:K,8,0)</f>
         <v>constFactorFzukCupuk</v>
       </c>
-      <c r="E8" s="79" t="str">
+      <c r="E8" s="53" t="str">
         <f>VLOOKUP(A8,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F8" s="81" t="str">
+      <c r="F8" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G8" s="81" t="str">
+      <c r="G8" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H8" s="49" t="str">
+      <c r="H8" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukCupuk,       divide,      "floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="53">
         <f>VLOOKUP(A8,Factors!D:G,4,0)</f>
-        <v>9.9999868018625211</v>
-      </c>
-      <c r="J8" s="79" t="str">
+        <v>10</v>
+      </c>
+      <c r="J8" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>9.999986801862520000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K8" s="82" t="str">
+        <v>1.000000000000000000000000000000000000000000000000000000e+01</v>
+      </c>
+      <c r="K8" s="56" t="str">
         <f>VLOOKUP(A8,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
-      <c r="L8" s="50" t="str">
+      <c r="L8" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="65" t="str">
+      <c r="N8" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukCupuk] = &amp;const_CupukFzuk,</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="64" t="str">
+      <c r="D9" s="40" t="str">
         <f>VLOOKUP(A9,Factors!D:K,8,0)</f>
         <v>constFactorFzukTbspuk</v>
       </c>
-      <c r="E9" s="79" t="str">
+      <c r="E9" s="53" t="str">
         <f>VLOOKUP(A9,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F9" s="81" t="str">
+      <c r="F9" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G9" s="81" t="str">
+      <c r="G9" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H9" s="49" t="str">
+      <c r="H9" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTbspuk,    multiply,      "floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK,                 "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I9" s="79">
+      <c r="I9" s="53">
         <f>VLOOKUP(A9,Factors!D:G,4,0)</f>
-        <v>1.6000021117047836</v>
-      </c>
-      <c r="J9" s="79" t="str">
+        <v>1.6</v>
+      </c>
+      <c r="J9" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>1.600002111704780000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K9" s="82" t="str">
+        <v>1.600000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K9" s="56" t="str">
         <f>VLOOKUP(A9,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
-      <c r="L9" s="50" t="str">
+      <c r="L9" s="31" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("FzukTbspuk",    "+1.600002111704780000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N9" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("FzukTbspuk",    "+1.600000000000000000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N9" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukTbspuk] = &amp;const_FzukTbspuk,</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="64" t="str">
+      <c r="D10" s="40" t="str">
         <f>VLOOKUP(A10,Factors!D:K,8,0)</f>
         <v>constFactorFzukTspuk</v>
       </c>
-      <c r="E10" s="79" t="str">
+      <c r="E10" s="53" t="str">
         <f>VLOOKUP(A10,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F10" s="81" t="str">
+      <c r="F10" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G10" s="81" t="str">
+      <c r="G10" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H10" s="49" t="str">
+      <c r="H10" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTspuk,     multiply,      "floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="53">
         <f>VLOOKUP(A10,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
-      </c>
-      <c r="J10" s="79" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="J10" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K10" s="82" t="str">
+        <v>4.800000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K10" s="56" t="str">
         <f>VLOOKUP(A10,Factors!D:N,11,0)</f>
         <v>FzukTspuk</v>
       </c>
-      <c r="L10" s="50" t="str">
+      <c r="L10" s="31" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("FzukTspuk",     "+4.800006335114380000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N10" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("FzukTspuk",     "+4.800000000000000000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N10" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzukTspuk] = &amp;const_FzukTspuk,</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="64" t="str">
+      <c r="D11" s="40" t="str">
         <f>VLOOKUP(A11,Factors!D:K,8,0)</f>
         <v>constFactorFzusCupc</v>
       </c>
-      <c r="E11" s="79" t="str">
+      <c r="E11" s="53" t="str">
         <f>VLOOKUP(A11,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F11" s="81" t="str">
+      <c r="F11" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G11" s="81" t="str">
+      <c r="G11" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H11" s="49" t="str">
+      <c r="H11" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusCupc,        divide,      "floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I11" s="79">
+      <c r="I11" s="53">
         <f>VLOOKUP(A11,Factors!D:G,4,0)</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="J11" s="79" t="str">
+        <v>8</v>
+      </c>
+      <c r="J11" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>8.000007997024360000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K11" s="82" t="str">
+        <v>8.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K11" s="56" t="str">
         <f>VLOOKUP(A11,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
-      <c r="L11" s="50" t="str">
+      <c r="L11" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N11" s="65" t="str">
+      <c r="N11" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusCupc] = &amp;const_CupcFzus,</v>
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="64" t="str">
+      <c r="D12" s="40" t="str">
         <f>VLOOKUP(A12,Factors!D:K,8,0)</f>
         <v>constFactorFzusTbspc</v>
       </c>
-      <c r="E12" s="79" t="str">
+      <c r="E12" s="53" t="str">
         <f>VLOOKUP(A12,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F12" s="81" t="str">
+      <c r="F12" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G12" s="81" t="str">
+      <c r="G12" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H12" s="49" t="str">
+      <c r="H12" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTbspc,     multiply,      "floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,       "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I12" s="79">
+      <c r="I12" s="53">
         <f>VLOOKUP(A12,Factors!D:G,4,0)</f>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="J12" s="79" t="str">
+        <v>2</v>
+      </c>
+      <c r="J12" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>1.999998000745910000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K12" s="82" t="str">
+        <v>2.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K12" s="56" t="str">
         <f>VLOOKUP(A12,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
-      <c r="L12" s="50" t="str">
+      <c r="L12" s="31" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("FzusTbspc",     "+1.999998000745910000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N12" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("FzusTbspc",     "+2.000000000000000000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N12" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusTbspc] = &amp;const_FzusTbspc,</v>
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="64" t="str">
+      <c r="D13" s="40" t="str">
         <f>VLOOKUP(A13,Factors!D:K,8,0)</f>
         <v>constFactorFzusTspc</v>
       </c>
-      <c r="E13" s="79" t="str">
+      <c r="E13" s="53" t="str">
         <f>VLOOKUP(A13,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F13" s="81" t="str">
+      <c r="F13" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G13" s="81" t="str">
+      <c r="G13" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H13" s="49" t="str">
+      <c r="H13" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTspc,      multiply,      "floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I13" s="79">
+      <c r="I13" s="53">
         <f>VLOOKUP(A13,Factors!D:G,4,0)</f>
-        <v>5.9999940022377229</v>
-      </c>
-      <c r="J13" s="79" t="str">
+        <v>6</v>
+      </c>
+      <c r="J13" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>5.999994002237720000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K13" s="82" t="str">
+        <v>6.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K13" s="56" t="str">
         <f>VLOOKUP(A13,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
-      <c r="L13" s="50" t="str">
+      <c r="L13" s="31" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">  generateConstantArray("FzusTspc",      "+5.999994002237720000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N13" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("FzusTspc",      "+6.000000000000000000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N13" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorFzusTspc] = &amp;const_FzusTspc,</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="64" t="str">
+      <c r="D14" s="40" t="str">
         <f>VLOOKUP(A14,Factors!D:K,8,0)</f>
         <v>constFactorMlCupc</v>
       </c>
-      <c r="E14" s="79" t="str">
+      <c r="E14" s="53" t="str">
         <f>VLOOKUP(A14,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F14" s="81" t="str">
+      <c r="F14" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G14" s="81" t="str">
+      <c r="G14" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H14" s="49" t="str">
+      <c r="H14" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupc,          divide,      "ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I14" s="79">
+      <c r="I14" s="53">
         <f>VLOOKUP(A14,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J14" s="79" t="str">
+      <c r="J14" s="53" t="str">
         <f t="shared" si="3"/>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K14" s="82" t="str">
+      <c r="K14" s="56" t="str">
         <f>VLOOKUP(A14,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
-      <c r="L14" s="50" t="str">
+      <c r="L14" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N14" s="65" t="str">
+      <c r="N14" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlCupc] = &amp;const_CupcMl,</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="64" t="str">
+      <c r="D15" s="40" t="str">
         <f>VLOOKUP(A15,Factors!D:K,8,0)</f>
         <v>constFactorMlCupuk</v>
       </c>
-      <c r="E15" s="79" t="str">
+      <c r="E15" s="53" t="str">
         <f>VLOOKUP(A15,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F15" s="81" t="str">
+      <c r="F15" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G15" s="81" t="str">
+      <c r="G15" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H15" s="49" t="str">
+      <c r="H15" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupuk,         divide,      "ml" STD_RIGHT_ARROW "cup" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I15" s="79">
+      <c r="I15" s="53">
         <f>VLOOKUP(A15,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J15" s="79" t="str">
+      <c r="J15" s="53" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K15" s="82" t="str">
+      <c r="K15" s="56" t="str">
         <f>VLOOKUP(A15,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
-      <c r="L15" s="50" t="str">
+      <c r="L15" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N15" s="65" t="str">
+      <c r="N15" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlCupuk] = &amp;const_CupukMl,</v>
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="64" t="str">
+      <c r="D16" s="40" t="str">
         <f>VLOOKUP(A16,Factors!D:K,8,0)</f>
         <v>constFactorMlPintlq</v>
       </c>
-      <c r="E16" s="79" t="str">
+      <c r="E16" s="53" t="str">
         <f>VLOOKUP(A16,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F16" s="81" t="str">
+      <c r="F16" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q</v>
       </c>
-      <c r="G16" s="81" t="str">
+      <c r="G16" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H16" s="49" t="str">
+      <c r="H16" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintlq,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q,   "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I16" s="79">
+      <c r="I16" s="53">
         <f>VLOOKUP(A16,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J16" s="79" t="str">
+      <c r="J16" s="53" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K16" s="82" t="str">
+      <c r="K16" s="56" t="str">
         <f>VLOOKUP(A16,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
-      <c r="L16" s="50" t="str">
+      <c r="L16" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N16" s="65" t="str">
+      <c r="N16" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlPintlq] = &amp;const_PintlqMl,</v>
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="64" t="str">
+      <c r="D17" s="40" t="str">
         <f>VLOOKUP(A17,Factors!D:K,8,0)</f>
         <v>constFactorMlPintuk</v>
       </c>
-      <c r="E17" s="79" t="str">
+      <c r="E17" s="53" t="str">
         <f>VLOOKUP(A17,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F17" s="81" t="str">
+      <c r="F17" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_UK</v>
       </c>
-      <c r="G17" s="81" t="str">
+      <c r="G17" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H17" s="49" t="str">
+      <c r="H17" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintuk,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I17" s="79">
+      <c r="I17" s="53">
         <f>VLOOKUP(A17,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J17" s="79" t="str">
+      <c r="J17" s="53" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K17" s="82" t="str">
+      <c r="K17" s="56" t="str">
         <f>VLOOKUP(A17,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
-      <c r="L17" s="50" t="str">
+      <c r="L17" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N17" s="65" t="str">
+      <c r="N17" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlPintuk] = &amp;const_PintukMl,</v>
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="66" t="s">
+      <c r="C18" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="64" t="str">
+      <c r="D18" s="40" t="str">
         <f>VLOOKUP(A18,Factors!D:K,8,0)</f>
         <v>constFactorMlQt</v>
       </c>
-      <c r="E18" s="79" t="str">
+      <c r="E18" s="53" t="str">
         <f>VLOOKUP(A18,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F18" s="81" t="str">
+      <c r="F18" s="55" t="str">
         <f t="shared" si="0"/>
-        <v>"ml" STD_RIGHT_ARROW "qt." STD_UK</v>
-      </c>
-      <c r="G18" s="81" t="str">
+        <v>"ml" STD_RIGHT_ARROW "qt" STD_UK</v>
+      </c>
+      <c r="G18" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H18" s="49" t="str">
+      <c r="H18" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorMlQt,            divide,      "ml" STD_RIGHT_ARROW "qt." STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
-      </c>
-      <c r="I18" s="79">
+        <v>/* NNNN */  UNIT_CONV(constFactorMlQt,            divide,      "ml" STD_RIGHT_ARROW "qt" STD_UK,                            "ml" STD_RIGHT_ARROW                                        ),</v>
+      </c>
+      <c r="I18" s="53">
         <f>VLOOKUP(A18,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J18" s="79" t="str">
+      <c r="J18" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K18" s="82" t="str">
+      <c r="K18" s="56" t="str">
         <f>VLOOKUP(A18,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
-      <c r="L18" s="50" t="str">
+      <c r="L18" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N18" s="65" t="str">
+      <c r="N18" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlQt] = &amp;const_QtMl,</v>
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="64" t="str">
+      <c r="D19" s="40" t="str">
         <f>VLOOKUP(A19,Factors!D:K,8,0)</f>
         <v>constFactorMlQtus</v>
       </c>
-      <c r="E19" s="79" t="str">
+      <c r="E19" s="53" t="str">
         <f>VLOOKUP(A19,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F19" s="81" t="str">
+      <c r="F19" s="55" t="str">
         <f t="shared" si="0"/>
-        <v>"ml" STD_RIGHT_ARROW "qt." STD_US</v>
-      </c>
-      <c r="G19" s="81" t="str">
+        <v>"ml" STD_RIGHT_ARROW "qt" STD_US</v>
+      </c>
+      <c r="G19" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H19" s="49" t="str">
+      <c r="H19" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorMlQtus,          divide,      "ml" STD_RIGHT_ARROW "qt." STD_US,                           "ml" STD_RIGHT_ARROW                                        ),</v>
-      </c>
-      <c r="I19" s="79">
+        <v>/* NNNN */  UNIT_CONV(constFactorMlQtus,          divide,      "ml" STD_RIGHT_ARROW "qt" STD_US,                            "ml" STD_RIGHT_ARROW                                        ),</v>
+      </c>
+      <c r="I19" s="53">
         <f>VLOOKUP(A19,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J19" s="79" t="str">
+      <c r="J19" s="53" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K19" s="82" t="str">
+      <c r="K19" s="56" t="str">
         <f>VLOOKUP(A19,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
-      <c r="L19" s="50" t="str">
+      <c r="L19" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N19" s="65" t="str">
+      <c r="N19" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlQtus] = &amp;const_QtusMl,</v>
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B20" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="64" t="str">
+      <c r="D20" s="40" t="str">
         <f>VLOOKUP(A20,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspc</v>
       </c>
-      <c r="E20" s="79" t="str">
+      <c r="E20" s="53" t="str">
         <f>VLOOKUP(A20,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F20" s="81" t="str">
+      <c r="F20" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G20" s="81" t="str">
+      <c r="G20" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H20" s="49" t="str">
+      <c r="H20" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspc,         divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,                "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I20" s="79">
+      <c r="I20" s="53">
         <f>VLOOKUP(A20,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J20" s="79" t="str">
+      <c r="J20" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K20" s="82" t="str">
+      <c r="K20" s="56" t="str">
         <f>VLOOKUP(A20,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
-      <c r="L20" s="50" t="str">
+      <c r="L20" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N20" s="65" t="str">
+      <c r="N20" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTbspc] = &amp;const_TbspcMl,</v>
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="64" t="str">
+      <c r="D21" s="40" t="str">
         <f>VLOOKUP(A21,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspuk</v>
       </c>
-      <c r="E21" s="79" t="str">
+      <c r="E21" s="53" t="str">
         <f>VLOOKUP(A21,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F21" s="81" t="str">
+      <c r="F21" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G21" s="81" t="str">
+      <c r="G21" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H21" s="49" t="str">
+      <c r="H21" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspuk,        divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I21" s="79">
+      <c r="I21" s="53">
         <f>VLOOKUP(A21,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J21" s="79" t="str">
+      <c r="J21" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K21" s="82" t="str">
+      <c r="K21" s="56" t="str">
         <f>VLOOKUP(A21,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
-      <c r="L21" s="50" t="str">
+      <c r="L21" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N21" s="65" t="str">
+      <c r="N21" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTbspuk] = &amp;const_TbspukMl,</v>
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="64" t="str">
+      <c r="D22" s="40" t="str">
         <f>VLOOKUP(A22,Factors!D:K,8,0)</f>
         <v>constFactorMlTspc</v>
       </c>
-      <c r="E22" s="79" t="str">
+      <c r="E22" s="53" t="str">
         <f>VLOOKUP(A22,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F22" s="81" t="str">
+      <c r="F22" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G22" s="81" t="str">
+      <c r="G22" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H22" s="49" t="str">
+      <c r="H22" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspc,          divide,      "ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I22" s="79">
+      <c r="I22" s="53">
         <f>VLOOKUP(A22,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J22" s="79" t="str">
+      <c r="J22" s="53" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K22" s="82" t="str">
+      <c r="K22" s="56" t="str">
         <f>VLOOKUP(A22,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
-      <c r="L22" s="50" t="str">
+      <c r="L22" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N22" s="65" t="str">
+      <c r="N22" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTspc] = &amp;const_TspcMl,</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="64" t="str">
+      <c r="D23" s="40" t="str">
         <f>VLOOKUP(A23,Factors!D:K,8,0)</f>
         <v>constFactorMlTspuk</v>
       </c>
-      <c r="E23" s="79" t="str">
+      <c r="E23" s="53" t="str">
         <f>VLOOKUP(A23,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F23" s="81" t="str">
+      <c r="F23" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G23" s="81" t="str">
+      <c r="G23" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
-      <c r="H23" s="49" t="str">
+      <c r="H23" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspuk,         divide,      "ml" STD_RIGHT_ARROW "tsp" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I23" s="79">
+      <c r="I23" s="53">
         <f>VLOOKUP(A23,Factors!D:G,4,0)</f>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="J23" s="79" t="str">
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="J23" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K23" s="82" t="str">
+        <v>5.919388020833330000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K23" s="56" t="str">
         <f>VLOOKUP(A23,Factors!D:N,11,0)</f>
         <v>TspukMl</v>
       </c>
-      <c r="L23" s="50" t="str">
+      <c r="L23" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N23" s="65" t="str">
+      <c r="N23" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorMlTspuk] = &amp;const_TspukMl,</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="64" t="str">
+      <c r="D24" s="40" t="str">
         <f>VLOOKUP(A24,Factors!D:K,8,0)</f>
         <v>constFactorPintlqMl</v>
       </c>
-      <c r="E24" s="79" t="str">
+      <c r="E24" s="53" t="str">
         <f>VLOOKUP(A24,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F24" s="81" t="str">
+      <c r="F24" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G24" s="81" t="str">
+      <c r="G24" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW</v>
       </c>
-      <c r="H24" s="49" t="str">
+      <c r="H24" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintlqMl,      multiply,      "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml",   "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW        ),</v>
       </c>
-      <c r="I24" s="79">
+      <c r="I24" s="53">
         <f>VLOOKUP(A24,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J24" s="79" t="str">
+      <c r="J24" s="53" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K24" s="82" t="str">
+      <c r="K24" s="56" t="str">
         <f>VLOOKUP(A24,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
-      <c r="L24" s="50" t="str">
+      <c r="L24" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("PintlqMl",      "+4.731764730000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N24" s="65" t="str">
+      <c r="N24" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorPintlqMl] = &amp;const_PintlqMl,</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="64" t="str">
+      <c r="D25" s="40" t="str">
         <f>VLOOKUP(A25,Factors!D:K,8,0)</f>
         <v>constFactorPintukMl</v>
       </c>
-      <c r="E25" s="79" t="str">
+      <c r="E25" s="53" t="str">
         <f>VLOOKUP(A25,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F25" s="81" t="str">
+      <c r="F25" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G25" s="81" t="str">
+      <c r="G25" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H25" s="49" t="str">
+      <c r="H25" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintukMl,      multiply,      "pint" STD_UK STD_RIGHT_ARROW "ml",                          "pint" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I25" s="79">
+      <c r="I25" s="53">
         <f>VLOOKUP(A25,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J25" s="79" t="str">
+      <c r="J25" s="53" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K25" s="82" t="str">
+      <c r="K25" s="56" t="str">
         <f>VLOOKUP(A25,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
-      <c r="L25" s="50" t="str">
+      <c r="L25" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("PintukMl",      "+5.682612500000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N25" s="65" t="str">
+      <c r="N25" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorPintukMl] = &amp;const_PintukMl,</v>
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="64" t="str">
+      <c r="D26" s="40" t="str">
         <f>VLOOKUP(A26,Factors!D:K,8,0)</f>
         <v>constFactorQtMl</v>
       </c>
-      <c r="E26" s="79" t="str">
+      <c r="E26" s="53" t="str">
         <f>VLOOKUP(A26,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F26" s="81" t="str">
+      <c r="F26" s="55" t="str">
         <f t="shared" si="0"/>
-        <v>"qt." STD_UK STD_RIGHT_ARROW "ml"</v>
-      </c>
-      <c r="G26" s="81" t="str">
+        <v>"qt" STD_UK STD_RIGHT_ARROW "ml"</v>
+      </c>
+      <c r="G26" s="55" t="str">
         <f t="shared" si="1"/>
-        <v>"qt." STD_UK STD_RIGHT_ARROW</v>
-      </c>
-      <c r="H26" s="49" t="str">
+        <v>"qt" STD_UK STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H26" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorQtMl,          multiply,      "qt." STD_UK STD_RIGHT_ARROW "ml",                           "qt." STD_UK STD_RIGHT_ARROW                                ),</v>
-      </c>
-      <c r="I26" s="79">
+        <v>/* NNNN */  UNIT_CONV(constFactorQtMl,          multiply,      "qt" STD_UK STD_RIGHT_ARROW "ml",                            "qt" STD_UK STD_RIGHT_ARROW                                 ),</v>
+      </c>
+      <c r="I26" s="53">
         <f>VLOOKUP(A26,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J26" s="79" t="str">
+      <c r="J26" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K26" s="82" t="str">
+      <c r="K26" s="56" t="str">
         <f>VLOOKUP(A26,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
-      <c r="L26" s="50" t="str">
+      <c r="L26" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("QtMl",          "+1.136522500000000000000000000000000000000000000000000000e+03");</v>
       </c>
-      <c r="N26" s="65" t="str">
+      <c r="N26" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorQtMl] = &amp;const_QtMl,</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C27" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="64" t="str">
+      <c r="D27" s="40" t="str">
         <f>VLOOKUP(A27,Factors!D:K,8,0)</f>
         <v>constFactorQtusMl</v>
       </c>
-      <c r="E27" s="79" t="str">
+      <c r="E27" s="53" t="str">
         <f>VLOOKUP(A27,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F27" s="81" t="str">
+      <c r="F27" s="55" t="str">
         <f t="shared" si="0"/>
-        <v>"qt." STD_US STD_RIGHT_ARROW "ml"</v>
-      </c>
-      <c r="G27" s="81" t="str">
+        <v>"qt" STD_US STD_RIGHT_ARROW "ml"</v>
+      </c>
+      <c r="G27" s="55" t="str">
         <f t="shared" si="1"/>
-        <v>"qt." STD_US STD_RIGHT_ARROW</v>
-      </c>
-      <c r="H27" s="49" t="str">
+        <v>"qt" STD_US STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H27" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>/* NNNN */  UNIT_CONV(constFactorQtusMl,        multiply,      "qt." STD_US STD_RIGHT_ARROW "ml",                           "qt." STD_US STD_RIGHT_ARROW                                ),</v>
-      </c>
-      <c r="I27" s="79">
+        <v>/* NNNN */  UNIT_CONV(constFactorQtusMl,        multiply,      "qt" STD_US STD_RIGHT_ARROW "ml",                            "qt" STD_US STD_RIGHT_ARROW                                 ),</v>
+      </c>
+      <c r="I27" s="53">
         <f>VLOOKUP(A27,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J27" s="79" t="str">
+      <c r="J27" s="53" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K27" s="82" t="str">
+      <c r="K27" s="56" t="str">
         <f>VLOOKUP(A27,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
-      <c r="L27" s="50" t="str">
+      <c r="L27" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("QtusMl",        "+9.463529460000000000000000000000000000000000000000000000e+02");</v>
       </c>
-      <c r="N27" s="65" t="str">
+      <c r="N27" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorQtusMl] = &amp;const_QtusMl,</v>
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="64" t="str">
+      <c r="D28" s="40" t="str">
         <f>VLOOKUP(A28,Factors!D:K,8,0)</f>
         <v>constFactorTbspcFzus</v>
       </c>
-      <c r="E28" s="79" t="str">
+      <c r="E28" s="53" t="str">
         <f>VLOOKUP(A28,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F28" s="81" t="str">
+      <c r="F28" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G28" s="81" t="str">
+      <c r="G28" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H28" s="49" t="str">
+      <c r="H28" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcFzus,       divide,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,       "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I28" s="79">
+      <c r="I28" s="53">
         <f>VLOOKUP(A28,Factors!D:G,4,0)</f>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="J28" s="79" t="str">
+        <v>2</v>
+      </c>
+      <c r="J28" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>1.999998000745910000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K28" s="82" t="str">
+        <v>2.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K28" s="56" t="str">
         <f>VLOOKUP(A28,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
-      <c r="L28" s="50" t="str">
+      <c r="L28" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N28" s="65" t="str">
+      <c r="N28" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspcFzus] = &amp;const_FzusTbspc,</v>
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="64" t="str">
+      <c r="D29" s="40" t="str">
         <f>VLOOKUP(A29,Factors!D:K,8,0)</f>
         <v>constFactorTbspcMl</v>
       </c>
-      <c r="E29" s="79" t="str">
+      <c r="E29" s="53" t="str">
         <f>VLOOKUP(A29,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F29" s="81" t="str">
+      <c r="F29" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G29" s="81" t="str">
+      <c r="G29" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H29" s="49" t="str">
+      <c r="H29" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcMl,       multiply,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I29" s="79">
+      <c r="I29" s="53">
         <f>VLOOKUP(A29,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J29" s="79" t="str">
+      <c r="J29" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K29" s="82" t="str">
+      <c r="K29" s="56" t="str">
         <f>VLOOKUP(A29,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
-      <c r="L29" s="50" t="str">
+      <c r="L29" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TbspcMl",       "+1.478676478125000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N29" s="65" t="str">
+      <c r="N29" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspcMl] = &amp;const_TbspcMl,</v>
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="64" t="str">
+      <c r="D30" s="40" t="str">
         <f>VLOOKUP(A30,Factors!D:K,8,0)</f>
         <v>constFactorTbspukFzuk</v>
       </c>
-      <c r="E30" s="79" t="str">
+      <c r="E30" s="53" t="str">
         <f>VLOOKUP(A30,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F30" s="81" t="str">
+      <c r="F30" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G30" s="81" t="str">
+      <c r="G30" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H30" s="49" t="str">
+      <c r="H30" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukFzuk,      divide,      "Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                 "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I30" s="79">
+      <c r="I30" s="53">
         <f>VLOOKUP(A30,Factors!D:G,4,0)</f>
-        <v>1.6000021117047836</v>
-      </c>
-      <c r="J30" s="79" t="str">
+        <v>1.6</v>
+      </c>
+      <c r="J30" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>1.600002111704780000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K30" s="82" t="str">
+        <v>1.600000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K30" s="56" t="str">
         <f>VLOOKUP(A30,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
-      <c r="L30" s="50" t="str">
+      <c r="L30" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N30" s="65" t="str">
+      <c r="N30" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspukFzuk] = &amp;const_FzukTbspuk,</v>
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="64" t="str">
+      <c r="D31" s="40" t="str">
         <f>VLOOKUP(A31,Factors!D:K,8,0)</f>
         <v>constFactorTbspukMl</v>
       </c>
-      <c r="E31" s="79" t="str">
+      <c r="E31" s="53" t="str">
         <f>VLOOKUP(A31,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F31" s="81" t="str">
+      <c r="F31" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G31" s="81" t="str">
+      <c r="G31" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H31" s="49" t="str">
+      <c r="H31" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukMl,      multiply,      "Tbsp" STD_UK STD_RIGHT_ARROW "ml",                          "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I31" s="79">
+      <c r="I31" s="53">
         <f>VLOOKUP(A31,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J31" s="79" t="str">
+      <c r="J31" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K31" s="82" t="str">
+      <c r="K31" s="56" t="str">
         <f>VLOOKUP(A31,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
-      <c r="L31" s="50" t="str">
+      <c r="L31" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TbspukMl",      "+1.775816406250000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N31" s="65" t="str">
+      <c r="N31" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTbspukMl] = &amp;const_TbspukMl,</v>
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="64" t="str">
+      <c r="D32" s="40" t="str">
         <f>VLOOKUP(A32,Factors!D:K,8,0)</f>
         <v>constFactorTspcFzus</v>
       </c>
-      <c r="E32" s="79" t="str">
+      <c r="E32" s="53" t="str">
         <f>VLOOKUP(A32,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F32" s="81" t="str">
+      <c r="F32" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G32" s="81" t="str">
+      <c r="G32" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H32" s="49" t="str">
+      <c r="H32" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcFzus,        divide,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I32" s="79">
+      <c r="I32" s="53">
         <f>VLOOKUP(A32,Factors!D:G,4,0)</f>
-        <v>5.9999940022377229</v>
-      </c>
-      <c r="J32" s="79" t="str">
+        <v>6</v>
+      </c>
+      <c r="J32" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>5.999994002237720000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K32" s="82" t="str">
+        <v>6.000000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K32" s="56" t="str">
         <f>VLOOKUP(A32,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
-      <c r="L32" s="50" t="str">
+      <c r="L32" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N32" s="65" t="str">
+      <c r="N32" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTspcFzus] = &amp;const_FzusTspc,</v>
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="66" t="s">
+      <c r="C33" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="64" t="str">
+      <c r="D33" s="40" t="str">
         <f>VLOOKUP(A33,Factors!D:K,8,0)</f>
         <v>constFactorTspcMl</v>
       </c>
-      <c r="E33" s="79" t="str">
+      <c r="E33" s="53" t="str">
         <f>VLOOKUP(A33,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F33" s="81" t="str">
+      <c r="F33" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G33" s="81" t="str">
+      <c r="G33" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
-      <c r="H33" s="49" t="str">
+      <c r="H33" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcMl,        multiply,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I33" s="79">
+      <c r="I33" s="53">
         <f>VLOOKUP(A33,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J33" s="79" t="str">
+      <c r="J33" s="53" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K33" s="82" t="str">
+      <c r="K33" s="56" t="str">
         <f>VLOOKUP(A33,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
-      <c r="L33" s="50" t="str">
+      <c r="L33" s="31" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">  generateConstantArray("TspcMl",        "+4.928921593750000000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N33" s="65" t="str">
+      <c r="N33" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTspcMl] = &amp;const_TspcMl,</v>
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="64" t="str">
+      <c r="D34" s="40" t="str">
         <f>VLOOKUP(A34,Factors!D:K,8,0)</f>
         <v>constFactorTspukFzuk</v>
       </c>
-      <c r="E34" s="79" t="str">
+      <c r="E34" s="53" t="str">
         <f>VLOOKUP(A34,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F34" s="81" t="str">
+      <c r="F34" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G34" s="81" t="str">
+      <c r="G34" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H34" s="49" t="str">
+      <c r="H34" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukFzuk,       divide,      "tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I34" s="79">
+      <c r="I34" s="53">
         <f>VLOOKUP(A34,Factors!D:G,4,0)</f>
-        <v>4.8000063351143778</v>
-      </c>
-      <c r="J34" s="79" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="J34" s="53" t="str">
         <f t="shared" si="3"/>
-        <v>4.800006335114380000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K34" s="82" t="str">
+        <v>4.800000000000000000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K34" s="56" t="str">
         <f>VLOOKUP(A34,Factors!D:N,11,0)</f>
         <v>FzukTspuk</v>
       </c>
-      <c r="L34" s="50" t="str">
+      <c r="L34" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N34" s="65" t="str">
+      <c r="N34" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorTspukFzuk] = &amp;const_FzukTspuk,</v>
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="64" t="str">
+      <c r="D35" s="40" t="str">
         <f>VLOOKUP(A35,Factors!D:K,8,0)</f>
         <v>constFactorTspukMl</v>
       </c>
-      <c r="E35" s="79" t="str">
+      <c r="E35" s="53" t="str">
         <f>VLOOKUP(A35,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F35" s="81" t="str">
+      <c r="F35" s="55" t="str">
         <f t="shared" ref="F35:F42" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G35" s="81" t="str">
+      <c r="G35" s="55" t="str">
         <f t="shared" ref="G35:G42" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H35" s="49" t="str">
+      <c r="H35" s="30" t="str">
         <f t="shared" ref="H35:H42" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I35" s="79">
+      <c r="I35" s="53">
         <f>VLOOKUP(A35,Factors!D:G,4,0)</f>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="J35" s="79" t="str">
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="J35" s="53" t="str">
         <f t="shared" ref="J35:J42" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
-        <v>5.919388020833300000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K35" s="82" t="str">
+        <v>5.919388020833330000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K35" s="56" t="str">
         <f>VLOOKUP(A35,Factors!D:N,11,0)</f>
         <v>TspukMl</v>
       </c>
-      <c r="L35" s="50" t="str">
+      <c r="L35" s="31" t="str">
         <f t="shared" ref="L35:L42" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
-        <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833300000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N35" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833330000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N35" s="41" t="str">
         <f t="shared" ref="N35:N42" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
         <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="C36" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="64" t="str">
+      <c r="D36" s="40" t="str">
         <f>VLOOKUP(A36,Factors!D:K,8,0)</f>
         <v>constFactorMlIn3</v>
       </c>
-      <c r="E36" s="79" t="str">
+      <c r="E36" s="53" t="str">
         <f>VLOOKUP(A36,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F36" s="81" t="str">
+      <c r="F36" s="55" t="str">
         <f t="shared" si="6"/>
         <v>"m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3</v>
       </c>
-      <c r="G36" s="81" t="str">
+      <c r="G36" s="55" t="str">
         <f t="shared" si="7"/>
         <v>"m" STD_litre STD_RIGHT_ARROW</v>
       </c>
-      <c r="H36" s="49" t="str">
+      <c r="H36" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlIn3,           divide,      "m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3,                "m" STD_litre STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I36" s="79">
+      <c r="I36" s="53">
         <f>VLOOKUP(A36,Factors!D:G,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="J36" s="79" t="str">
+      <c r="J36" s="53" t="str">
         <f t="shared" si="9"/>
         <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K36" s="82" t="str">
+      <c r="K36" s="56" t="str">
         <f>VLOOKUP(A36,Factors!D:N,11,0)</f>
         <v>In3Ml</v>
       </c>
-      <c r="L36" s="50" t="str">
+      <c r="L36" s="31" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N36" s="65" t="str">
+      <c r="N36" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorMlIn3] = &amp;const_In3Ml,</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>201</v>
-      </c>
-      <c r="B37" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="C37" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="64" t="str">
+      <c r="D37" s="40" t="str">
         <f>VLOOKUP(A37,Factors!D:K,8,0)</f>
         <v>constFactorIn3Ml</v>
       </c>
-      <c r="E37" s="79" t="str">
+      <c r="E37" s="53" t="str">
         <f>VLOOKUP(A37,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F37" s="81" t="str">
+      <c r="F37" s="55" t="str">
         <f t="shared" si="6"/>
         <v>"in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</v>
       </c>
-      <c r="G37" s="81" t="str">
+      <c r="G37" s="55" t="str">
         <f t="shared" si="7"/>
         <v>"in" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
-      <c r="H37" s="49" t="str">
+      <c r="H37" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorIn3Ml,         multiply,      "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre,                "in" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I37" s="79">
+      <c r="I37" s="53">
         <f>VLOOKUP(A37,Factors!D:G,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="J37" s="79" t="str">
+      <c r="J37" s="53" t="str">
         <f t="shared" si="9"/>
         <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K37" s="82" t="str">
+      <c r="K37" s="56" t="str">
         <f>VLOOKUP(A37,Factors!D:N,11,0)</f>
         <v>In3Ml</v>
       </c>
-      <c r="L37" s="50" t="str">
+      <c r="L37" s="31" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">  generateConstantArray("In3Ml",         "+1.638706400000000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N37" s="65" t="str">
+      <c r="N37" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorIn3Ml] = &amp;const_In3Ml,</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="69" t="s">
-        <v>210</v>
-      </c>
-      <c r="C38" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="64" t="str">
+      <c r="D38" s="40" t="str">
         <f>VLOOKUP(A38,Factors!D:K,8,0)</f>
         <v>constFactorFt3Gluk</v>
       </c>
-      <c r="E38" s="79" t="str">
+      <c r="E38" s="53" t="str">
         <f>VLOOKUP(A38,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F38" s="81" t="str">
+      <c r="F38" s="55" t="str">
         <f t="shared" si="6"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK</v>
       </c>
-      <c r="G38" s="81" t="str">
+      <c r="G38" s="55" t="str">
         <f t="shared" si="7"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
-      <c r="H38" s="49" t="str">
+      <c r="H38" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFt3Gluk,       multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK,                 "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I38" s="79">
+      <c r="I38" s="53">
         <f>VLOOKUP(A38,Factors!D:G,4,0)</f>
-        <v>6.2302059127542027</v>
-      </c>
-      <c r="J38" s="79" t="str">
+        <v>6.2288354590428261</v>
+      </c>
+      <c r="J38" s="53" t="str">
         <f t="shared" si="9"/>
-        <v>6.230205912754200000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K38" s="82" t="str">
+        <v>6.228835459042830000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K38" s="56" t="str">
         <f>VLOOKUP(A38,Factors!D:N,11,0)</f>
         <v>Ft3Gluk</v>
       </c>
-      <c r="L38" s="50" t="str">
+      <c r="L38" s="31" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  generateConstantArray("Ft3Gluk",       "+6.230205912754200000000000000000000000000000000000000000e+00");</v>
-      </c>
-      <c r="N38" s="65" t="str">
+        <v xml:space="preserve">  generateConstantArray("Ft3Gluk",       "+6.228835459042830000000000000000000000000000000000000000e+00");</v>
+      </c>
+      <c r="N38" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorFt3Gluk] = &amp;const_Ft3Gluk,</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>203</v>
-      </c>
-      <c r="B39" s="69" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="64" t="str">
+      <c r="D39" s="40" t="str">
         <f>VLOOKUP(A39,Factors!D:K,8,0)</f>
         <v>constFactorGlukFt3</v>
       </c>
-      <c r="E39" s="79" t="str">
+      <c r="E39" s="53" t="str">
         <f>VLOOKUP(A39,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F39" s="81" t="str">
+      <c r="F39" s="55" t="str">
         <f t="shared" si="6"/>
         <v>"gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</v>
       </c>
-      <c r="G39" s="81" t="str">
+      <c r="G39" s="55" t="str">
         <f t="shared" si="7"/>
         <v>"gal" STD_UK STD_RIGHT_ARROW</v>
       </c>
-      <c r="H39" s="49" t="str">
+      <c r="H39" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorGlukFt3,         divide,      "gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3,                 "gal" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I39" s="79">
+      <c r="I39" s="53">
         <f>VLOOKUP(A39,Factors!D:G,4,0)</f>
-        <v>6.2302059127542027</v>
-      </c>
-      <c r="J39" s="79" t="str">
+        <v>6.2288354590428261</v>
+      </c>
+      <c r="J39" s="53" t="str">
         <f t="shared" si="9"/>
-        <v>6.230205912754200000000000000000000000000000000000000000e+00</v>
-      </c>
-      <c r="K39" s="82" t="str">
+        <v>6.228835459042830000000000000000000000000000000000000000e+00</v>
+      </c>
+      <c r="K39" s="56" t="str">
         <f>VLOOKUP(A39,Factors!D:N,11,0)</f>
         <v>Ft3Gluk</v>
       </c>
-      <c r="L39" s="50" t="str">
+      <c r="L39" s="31" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N39" s="65" t="str">
+      <c r="N39" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorGlukFt3] = &amp;const_Ft3Gluk,</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>204</v>
-      </c>
-      <c r="B40" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="C40" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="64" t="str">
+      <c r="D40" s="40" t="str">
         <f>VLOOKUP(A40,Factors!D:K,8,0)</f>
         <v>constFactorLFt3</v>
       </c>
-      <c r="E40" s="79" t="str">
+      <c r="E40" s="53" t="str">
         <f>VLOOKUP(A40,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F40" s="81" t="str">
+      <c r="F40" s="55" t="str">
         <f t="shared" si="6"/>
         <v>STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3</v>
       </c>
-      <c r="G40" s="81" t="str">
+      <c r="G40" s="55" t="str">
         <f t="shared" si="7"/>
         <v>STD_litre STD_RIGHT_ARROW</v>
       </c>
-      <c r="H40" s="49" t="str">
+      <c r="H40" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorLFt3,            divide,      STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3,                    STD_litre STD_RIGHT_ARROW                                   ),</v>
       </c>
-      <c r="I40" s="79">
+      <c r="I40" s="53">
         <f>VLOOKUP(A40,Factors!D:G,4,0)</f>
         <v>28.316846592000001</v>
       </c>
-      <c r="J40" s="79" t="str">
+      <c r="J40" s="53" t="str">
         <f t="shared" si="9"/>
         <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K40" s="82" t="str">
+      <c r="K40" s="56" t="str">
         <f>VLOOKUP(A40,Factors!D:N,11,0)</f>
         <v>Ft3L</v>
       </c>
-      <c r="L40" s="50" t="str">
+      <c r="L40" s="31" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N40" s="65" t="str">
+      <c r="N40" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorLFt3] = &amp;const_Ft3L,</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>205</v>
-      </c>
-      <c r="B41" s="69" t="s">
-        <v>213</v>
-      </c>
-      <c r="C41" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="64" t="str">
+      <c r="D41" s="40" t="str">
         <f>VLOOKUP(A41,Factors!D:K,8,0)</f>
         <v>constFactorFt3L</v>
       </c>
-      <c r="E41" s="79" t="str">
+      <c r="E41" s="53" t="str">
         <f>VLOOKUP(A41,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F41" s="81" t="str">
+      <c r="F41" s="55" t="str">
         <f t="shared" si="6"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre</v>
       </c>
-      <c r="G41" s="81" t="str">
+      <c r="G41" s="55" t="str">
         <f t="shared" si="7"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
-      <c r="H41" s="49" t="str">
+      <c r="H41" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFt3L,          multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre,                    "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I41" s="79">
+      <c r="I41" s="53">
         <f>VLOOKUP(A41,Factors!D:G,4,0)</f>
         <v>28.316846592000001</v>
       </c>
-      <c r="J41" s="79" t="str">
+      <c r="J41" s="53" t="str">
         <f t="shared" si="9"/>
         <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K41" s="82" t="str">
+      <c r="K41" s="56" t="str">
         <f>VLOOKUP(A41,Factors!D:N,11,0)</f>
         <v>Ft3L</v>
       </c>
-      <c r="L41" s="50" t="str">
+      <c r="L41" s="31" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">  generateConstantArray("Ft3L",          "+2.831684659200000000000000000000000000000000000000000000e+01");</v>
       </c>
-      <c r="N41" s="65" t="str">
+      <c r="N41" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorFt3L] = &amp;const_Ft3L,</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>206</v>
-      </c>
-      <c r="B42" s="69" t="s">
-        <v>214</v>
-      </c>
-      <c r="C42" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="64" t="str">
+      <c r="D42" s="40" t="str">
         <f>VLOOKUP(A42,Factors!D:K,8,0)</f>
         <v>constFactorLQtus</v>
       </c>
-      <c r="E42" s="79" t="str">
+      <c r="E42" s="53" t="str">
         <f>VLOOKUP(A42,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F42" s="81" t="str">
+      <c r="F42" s="55" t="str">
         <f t="shared" si="6"/>
         <v>STD_litre STD_RIGHT_ARROW "qt" STD_US</v>
       </c>
-      <c r="G42" s="81" t="str">
+      <c r="G42" s="55" t="str">
         <f t="shared" si="7"/>
         <v>STD_litre STD_RIGHT_ARROW</v>
       </c>
-      <c r="H42" s="49" t="str">
+      <c r="H42" s="30" t="str">
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorLQtus,         multiply,      STD_litre STD_RIGHT_ARROW "qt" STD_US,                       STD_litre STD_RIGHT_ARROW                                   ),</v>
       </c>
-      <c r="I42" s="79">
+      <c r="I42" s="53">
         <f>VLOOKUP(A42,Factors!D:G,4,0)</f>
         <v>1.0566882094325938</v>
       </c>
-      <c r="J42" s="79" t="str">
+      <c r="J42" s="53" t="str">
         <f t="shared" si="9"/>
         <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K42" s="82" t="str">
+      <c r="K42" s="56" t="str">
         <f>VLOOKUP(A42,Factors!D:N,11,0)</f>
         <v>LQtus</v>
       </c>
-      <c r="L42" s="50" t="str">
+      <c r="L42" s="31" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">  generateConstantArray("LQtus",         "+1.056688209432590000000000000000000000000000000000000000e+00");</v>
       </c>
-      <c r="N42" s="65" t="str">
+      <c r="N42" s="41" t="str">
         <f t="shared" si="11"/>
         <v xml:space="preserve">    [constFactorLQtus] = &amp;const_LQtus,</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>207</v>
-      </c>
-      <c r="B43" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="C43" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="64" t="str">
+      <c r="D43" s="40" t="str">
         <f>VLOOKUP(A43,Factors!D:K,8,0)</f>
         <v>constFactorQtusL</v>
       </c>
-      <c r="E43" s="79" t="str">
+      <c r="E43" s="53" t="str">
         <f>VLOOKUP(A43,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F43" s="81" t="str">
+      <c r="F43" s="55" t="str">
         <f t="shared" si="0"/>
         <v>"qt" STD_US STD_RIGHT_ARROW STD_litre</v>
       </c>
-      <c r="G43" s="81" t="str">
+      <c r="G43" s="55" t="str">
         <f t="shared" si="1"/>
         <v>"qt" STD_US STD_RIGHT_ARROW</v>
       </c>
-      <c r="H43" s="49" t="str">
+      <c r="H43" s="30" t="str">
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtusL,           divide,      "qt" STD_US STD_RIGHT_ARROW STD_litre,                       "qt" STD_US STD_RIGHT_ARROW                                 ),</v>
       </c>
-      <c r="I43" s="79">
+      <c r="I43" s="53">
         <f>VLOOKUP(A43,Factors!D:G,4,0)</f>
         <v>1.0566882094325938</v>
       </c>
-      <c r="J43" s="79" t="str">
+      <c r="J43" s="53" t="str">
         <f t="shared" si="3"/>
         <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K43" s="82" t="str">
+      <c r="K43" s="56" t="str">
         <f>VLOOKUP(A43,Factors!D:N,11,0)</f>
         <v>LQtus</v>
       </c>
-      <c r="L43" s="50" t="str">
+      <c r="L43" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N43" s="65" t="str">
+      <c r="N43" s="41" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">    [constFactorQtusL] = &amp;const_LQtus,</v>
       </c>
@@ -3836,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAAB5F5-5A0E-F540-8CD7-68987B744E5F}">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -3844,2466 +4174,2745 @@
     <col min="3" max="3" width="7.83203125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="8" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="57.1640625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="F1" s="53"/>
-    </row>
-    <row r="2" spans="1:14" ht="17" thickBot="1">
-      <c r="F2" s="53" t="s">
+    <row r="1" spans="1:18" ht="17" thickBot="1">
+      <c r="F1" s="69" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="F2" s="60" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="17" thickBot="1">
+      <c r="F3" s="61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="F4" s="34"/>
+      <c r="H4" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="F5" s="34" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="18">
-      <c r="C3" s="42" t="s">
+      <c r="G5" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="C6" s="70" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="71"/>
+      <c r="E6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F6" s="74">
+        <v>3785.4117839999999</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="82">
+        <f>231 * 0.0254^3 * 1000000</f>
+        <v>3785.4117839999999</v>
+      </c>
+      <c r="I6" s="83">
+        <f>H6/$H$12</f>
+        <v>768</v>
+      </c>
+      <c r="J6" t="s">
+        <v>255</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:K11" si="0">$H$6/$I$6*I6</f>
+        <v>3785.4117839999999</v>
+      </c>
+      <c r="L6" t="b">
+        <f t="shared" ref="L6:L11" si="1">K6=F6</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="25"/>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="C7" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="95">
+        <f>H7</f>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="84">
+        <f>(231*0.0254^3/128*1000000)/2*32*2</f>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="I7" s="83">
+        <f t="shared" ref="I7:I11" si="2">H7/$H$12</f>
+        <v>192</v>
+      </c>
+      <c r="J7" t="s">
+        <v>255</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="L7" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="C8" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="40" t="s">
+      <c r="D8" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="54">
+      <c r="E8" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="59">
         <v>473.17647299999999</v>
       </c>
-      <c r="J3" s="43">
-        <f>F3/F5</f>
-        <v>2</v>
-      </c>
-      <c r="K3" s="44" t="s">
+      <c r="G8" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="84">
+        <f>(231 * 0.0254^3 / 128 * 1000000) / 2 * 32</f>
+        <v>473.17647299999999</v>
+      </c>
+      <c r="I8" s="83">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="J8" t="s">
+        <v>255</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>473.17647299999999</v>
+      </c>
+      <c r="L8" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="C9" s="72" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="59">
+        <v>236.58823649999999</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="85">
+        <f>(231*0.0254^3/128*1000000)/2*32/2</f>
+        <v>236.58823649999999</v>
+      </c>
+      <c r="I9" s="83">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>236.58823649999999</v>
+      </c>
+      <c r="L9" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="25"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="74">
+        <v>29.573529562499999</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="H10" s="82">
+        <f>231 * 0.0254^3 / 128 * 1000000</f>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="I10" s="96">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>255</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="L10" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="P10" s="26"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="C11" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="59">
+        <v>14.78676478125</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="H11" s="86">
+        <f>(231 * 0.0254^3 / 128 * 1000000) / 2</f>
+        <v>14.78676478125</v>
+      </c>
+      <c r="I11" s="83">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J11" t="s">
+        <v>255</v>
+      </c>
+      <c r="K11" s="93">
+        <f t="shared" si="0"/>
+        <v>14.78676478125</v>
+      </c>
+      <c r="L11" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="P11" s="26"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="C12" s="72" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="59">
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="H12" s="86">
+        <f>(231 * 0.0254^3 / 128 * 1000000) / 2 / 3</f>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="I12" s="83">
+        <f>H12/$H$12</f>
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="93">
+        <f>$H$6/$I$6*I12</f>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="L12" t="b">
+        <f>K12=F12</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="P12" s="26"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="C13" s="70" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="18">
-      <c r="C4" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="D13" s="71"/>
+      <c r="E13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="95">
+        <f>H13</f>
+        <v>4546.09</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>241</v>
+      </c>
+      <c r="H13" s="82">
+        <f>0.00454609 * 1000000</f>
+        <v>4546.09</v>
+      </c>
+      <c r="I13" s="87">
+        <f t="shared" ref="I13:I19" si="3">H13/$H$19</f>
+        <v>768</v>
+      </c>
+      <c r="J13" t="s">
+        <v>256</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ref="K13:K18" si="4">$H$13/$I$13*I13</f>
+        <v>4546.09</v>
+      </c>
+      <c r="L13" t="b">
+        <f t="shared" ref="L13:L18" si="5">K13=F13</f>
+        <v>1</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="52"/>
+      <c r="C14" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="81" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="59">
+        <v>1136.5225</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="82">
+        <f>0.00454609 / 4 * 1000000</f>
+        <v>1136.5225</v>
+      </c>
+      <c r="I14" s="87">
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="J14" t="s">
+        <v>256</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="4"/>
+        <v>1136.5225</v>
+      </c>
+      <c r="L14" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="22"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="25"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="52"/>
+      <c r="C15" s="72" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="E4" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="55">
-        <f xml:space="preserve"> 2 * F3</f>
-        <v>946.35294599999997</v>
-      </c>
-      <c r="J4" s="43">
-        <f>F4/F3</f>
-        <v>2</v>
-      </c>
-      <c r="K4" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="M4">
-        <f>F4/F5</f>
-        <v>4</v>
-      </c>
-      <c r="N4">
-        <f>F4/F15</f>
-        <v>32.000031988097454</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="18">
-      <c r="C5" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="54">
-        <v>236.58823649999999</v>
-      </c>
-      <c r="J5" s="43">
-        <f>F5/F15</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="18">
-      <c r="C6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6" s="54">
-        <v>14.78676478125</v>
-      </c>
-      <c r="G6" s="38" t="str">
-        <f xml:space="preserve"> "1/16"</f>
-        <v>1/16</v>
-      </c>
-      <c r="H6" t="str">
-        <f>E5</f>
-        <v>US customary cup</v>
-      </c>
-      <c r="J6" s="45"/>
-    </row>
-    <row r="7" spans="1:14" ht="18">
-      <c r="C7" s="30" t="s">
+      <c r="F15" s="59">
+        <v>568.26125000000002</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>242</v>
+      </c>
+      <c r="H15" s="82">
+        <v>568.26125000000002</v>
+      </c>
+      <c r="I15" s="87">
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="54">
-        <v>4.9289215937500002</v>
-      </c>
-      <c r="G7" s="7" t="str">
-        <f xml:space="preserve"> "1/48"</f>
-        <v>1/48</v>
-      </c>
-      <c r="H7" t="str">
-        <f>E5</f>
-        <v>US customary cup</v>
-      </c>
-      <c r="J7" s="45"/>
-    </row>
-    <row r="8" spans="1:14" ht="18">
-      <c r="C8" s="37"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="56"/>
-      <c r="J8" s="45"/>
-    </row>
-    <row r="9" spans="1:14" ht="18">
-      <c r="A9" s="77"/>
-      <c r="C9" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="54">
+      <c r="J15" t="s">
+        <v>256</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="4"/>
         <v>568.26125000000002</v>
       </c>
-      <c r="H9" s="34">
-        <v>568.26125000000002</v>
-      </c>
-      <c r="J9" s="46">
-        <f>F9/F11</f>
-        <v>2</v>
-      </c>
-      <c r="K9" s="47" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="18">
-      <c r="A10" s="77"/>
-      <c r="C10" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="54">
-        <v>1136.5225</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10" s="34">
-        <f>2*H9</f>
-        <v>1136.5225</v>
-      </c>
-      <c r="J10" s="43">
-        <f>F10/F9</f>
-        <v>2</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18">
-      <c r="A11" s="77"/>
-      <c r="C11" s="30" t="s">
+      <c r="L15" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="22"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="28"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="52"/>
+      <c r="C16" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D16" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E16" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F16" s="59">
         <v>284.13062500000001</v>
       </c>
-      <c r="H11" s="34">
+      <c r="G16" s="58" t="s">
+        <v>252</v>
+      </c>
+      <c r="H16" s="82">
+        <f>0.00454609 / 16 * 1000000</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J11" s="46">
-        <f>F11/F16</f>
-        <v>9.9999868018625211</v>
-      </c>
-      <c r="K11" s="47" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="18">
-      <c r="A12" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="30" t="s">
+      <c r="I16" s="87">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="J16" t="s">
+        <v>256</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="4"/>
+        <v>284.13062500000001</v>
+      </c>
+      <c r="L16" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M16" s="7"/>
+      <c r="N16" s="22"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="28"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="52"/>
+      <c r="C17" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="74">
+        <v>28.413062500000002</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="82">
+        <f xml:space="preserve"> 0.00454609 / 160 * 1000000</f>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="I17" s="97">
+        <f t="shared" si="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>256</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="4"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="L17" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M17" s="7"/>
+      <c r="P17" s="26"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D18" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E18" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F18" s="59">
         <v>17.758164062500001</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="34">
-        <v>177.58164062500001</v>
-      </c>
-      <c r="J12" s="45"/>
-    </row>
-    <row r="13" spans="1:14" ht="19" thickBot="1">
-      <c r="A13" s="77" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="G18" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="H18" s="88">
+        <f>568.26125/32</f>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="I18" s="87">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J18" t="s">
+        <v>256</v>
+      </c>
+      <c r="K18" s="22">
+        <f t="shared" si="4"/>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="L18" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="7"/>
+      <c r="N18" s="22"/>
+      <c r="P18" s="26"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D19" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E19" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="F13" s="54">
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="H13" s="34">
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="J13" s="45"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="24" t="s">
+      <c r="F19" s="75">
+        <f>H19</f>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" s="89">
+        <f>568.26125/96</f>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="I19" s="87">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>256</v>
+      </c>
+      <c r="K19" s="94">
+        <f>$H$13/$I$13*I19</f>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="L19" t="b">
+        <f>K19=F19</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="7"/>
+      <c r="N19" s="22"/>
+      <c r="P19" s="26"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D20" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F20" s="59">
         <v>1</v>
       </c>
-      <c r="J14" s="45"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="77" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" s="58">
-        <v>29.573499999999999</v>
-      </c>
-      <c r="J15" s="45"/>
-      <c r="N15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="77"/>
-      <c r="C16" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="58">
-        <v>28.4131</v>
-      </c>
-      <c r="J16" s="45"/>
-      <c r="N16" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="C17" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" s="53">
-        <v>3785.51</v>
-      </c>
-      <c r="J17" s="43">
-        <f>F17/F4</f>
-        <v>4.0001037836891777</v>
-      </c>
-      <c r="K17" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="C18" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18" s="53">
-        <v>4545.09</v>
-      </c>
-      <c r="J18" s="43">
-        <f>F18/F10</f>
-        <v>3.9991201230068039</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="C19" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="53">
+      <c r="G20" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="H20" s="82">
+        <v>1</v>
+      </c>
+      <c r="I20" s="90"/>
+      <c r="M20" s="7"/>
+      <c r="P20" s="26"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="C21" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="59">
         <f>2.54^3</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="44"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="C20" s="77" t="s">
-        <v>222</v>
-      </c>
-      <c r="F20" s="78">
+      <c r="G21" s="58" t="s">
+        <v>247</v>
+      </c>
+      <c r="H21" s="82">
+        <f>2.54^3</f>
+        <v>16.387063999999999</v>
+      </c>
+      <c r="I21" s="90"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="C22" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="76">
         <f>(12*2.54)^3</f>
         <v>28316.846592000002</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="J20" s="43"/>
-      <c r="K20" s="44"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="C21" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="F21" s="53">
+      <c r="G22" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="H22" s="84">
+        <f>(12*2.54)^3</f>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="I22" s="90"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="C23" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="59">
         <v>1000</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="J21" s="43"/>
-      <c r="K21" s="44"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="C22" s="77"/>
-      <c r="F22" s="53"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="F23" s="53"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="F24" s="53"/>
-    </row>
-    <row r="25" spans="1:14" ht="17" thickBot="1">
-      <c r="F25" s="59" t="s">
+      <c r="G23" s="58" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="C24" s="52"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="66"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="25"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="F25" s="1"/>
+      <c r="H25" s="62">
+        <f xml:space="preserve"> 568.26125 / 20</f>
+        <v>28.413062500000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" ht="17" thickBot="1">
+      <c r="F27" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H27" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I27" s="21" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="18">
-      <c r="A26" s="13" t="s">
+    <row r="28" spans="1:16" ht="18">
+      <c r="A28" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B28" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="60">
-        <f>H26/I26</f>
-        <v>473.17647299999999</v>
-      </c>
-      <c r="G26" s="62">
-        <f>IF(M26="multiply",F26,F27)</f>
-        <v>473.17647299999999</v>
-      </c>
-      <c r="H26" s="9">
-        <f xml:space="preserve"> VLOOKUP(B26,units,4,0)</f>
-        <v>473.17647299999999</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" ref="I26:I41" si="0" xml:space="preserve"> VLOOKUP(C26,units,4,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J26" t="str">
-        <f>PROPER(B26)&amp;PROPER(C26)</f>
-        <v>PintlqMl</v>
-      </c>
-      <c r="K26" t="str">
-        <f>"constFactor"&amp;J26</f>
-        <v>constFactorPintlqMl</v>
-      </c>
-      <c r="M26" s="62" t="str">
-        <f>IF(H26&gt;I26,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N26" s="62" t="str">
-        <f>IF(M26="multiply",PROPER(B26)&amp;PROPER(C26),J27)</f>
-        <v>PintlqMl</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="18">
-      <c r="A27" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" s="60">
-        <f t="shared" ref="F27:F67" si="1">H27/I27</f>
-        <v>2.1133764188651875E-3</v>
-      </c>
-      <c r="G27" s="62">
-        <f>IF(M27="multiply",F27,F26)</f>
-        <v>473.17647299999999</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" ref="H27:H41" si="2" xml:space="preserve"> VLOOKUP(B27,units,4,0)</f>
-        <v>1</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="0"/>
-        <v>473.17647299999999</v>
-      </c>
-      <c r="J27" t="str">
-        <f t="shared" ref="J27:J59" si="3">PROPER(B27)&amp;PROPER(C27)</f>
-        <v>MlPintlq</v>
-      </c>
-      <c r="K27" t="str">
-        <f t="shared" ref="K27:K51" si="4">"constFactor"&amp;J27</f>
-        <v>constFactorMlPintlq</v>
-      </c>
-      <c r="M27" s="62" t="str">
-        <f>IF(M26="multiply","  divide","multiply")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N27" s="62" t="str">
-        <f>IF(M27="multiply",PROPER(B27)&amp;PROPER(C27),J26)</f>
-        <v>PintlqMl</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="18">
-      <c r="A28" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>111</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="60">
-        <f t="shared" si="1"/>
-        <v>946.35294599999997</v>
-      </c>
-      <c r="G28" s="63">
+      <c r="D28" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="36">
+        <f>H28/I28</f>
+        <v>473.17647299999999</v>
+      </c>
+      <c r="G28" s="38">
         <f>IF(M28="multiply",F28,F29)</f>
-        <v>946.35294599999997</v>
+        <v>473.17647299999999</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="2"/>
-        <v>946.35294599999997</v>
+        <f xml:space="preserve"> VLOOKUP(B28,units,4,0)</f>
+        <v>473.17647299999999</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I28:I43" si="6" xml:space="preserve"> VLOOKUP(C28,units,4,0)</f>
         <v>1</v>
       </c>
       <c r="J28" t="str">
-        <f t="shared" si="3"/>
-        <v>QtusMl</v>
+        <f>PROPER(B28)&amp;PROPER(C28)</f>
+        <v>PintlqMl</v>
       </c>
       <c r="K28" t="str">
         <f>"constFactor"&amp;J28</f>
-        <v>constFactorQtusMl</v>
-      </c>
-      <c r="M28" s="63" t="str">
+        <v>constFactorPintlqMl</v>
+      </c>
+      <c r="M28" s="38" t="str">
         <f>IF(H28&gt;I28,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N28" s="63" t="str">
+      <c r="N28" s="38" t="str">
         <f>IF(M28="multiply",PROPER(B28)&amp;PROPER(C28),J29)</f>
-        <v>QtusMl</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="18">
+        <v>PintlqMl</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="18">
       <c r="A29" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="60">
-        <f t="shared" si="1"/>
-        <v>1.0566882094325937E-3</v>
-      </c>
-      <c r="G29" s="63">
+        <v>3</v>
+      </c>
+      <c r="F29" s="36">
+        <f t="shared" ref="F29:F69" si="7">H29/I29</f>
+        <v>2.1133764188651875E-3</v>
+      </c>
+      <c r="G29" s="38">
         <f>IF(M29="multiply",F29,F28)</f>
-        <v>946.35294599999997</v>
+        <v>473.17647299999999</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H29:H43" si="8" xml:space="preserve"> VLOOKUP(B29,units,4,0)</f>
         <v>1</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="0"/>
-        <v>946.35294599999997</v>
+        <f t="shared" si="6"/>
+        <v>473.17647299999999</v>
       </c>
       <c r="J29" t="str">
-        <f t="shared" si="3"/>
-        <v>MlQtus</v>
+        <f t="shared" ref="J29:J61" si="9">PROPER(B29)&amp;PROPER(C29)</f>
+        <v>MlPintlq</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" ref="K29" si="5">"constFactor"&amp;J29</f>
-        <v>constFactorMlQtus</v>
-      </c>
-      <c r="M29" s="63" t="str">
+        <f t="shared" ref="K29:K53" si="10">"constFactor"&amp;J29</f>
+        <v>constFactorMlPintlq</v>
+      </c>
+      <c r="M29" s="38" t="str">
         <f>IF(M28="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N29" s="63" t="str">
+      <c r="N29" s="38" t="str">
         <f>IF(M29="multiply",PROPER(B29)&amp;PROPER(C29),J28)</f>
+        <v>PintlqMl</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="18">
+      <c r="A30" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="36">
+        <f t="shared" si="7"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="G30" s="39">
+        <f>IF(M30="multiply",F30,F31)</f>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="8"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="9"/>
         <v>QtusMl</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="18">
-      <c r="A30" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="60">
-        <f t="shared" si="1"/>
-        <v>0.12499987504661923</v>
-      </c>
-      <c r="G30" s="62">
-        <f>IF(M30="multiply",F30,F31)</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" si="2"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="I30" s="9">
-        <f t="shared" si="0"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="J30" t="str">
-        <f t="shared" si="3"/>
-        <v>FzusCupc</v>
       </c>
       <c r="K30" t="str">
         <f>"constFactor"&amp;J30</f>
-        <v>constFactorFzusCupc</v>
-      </c>
-      <c r="M30" s="62" t="str">
+        <v>constFactorQtusMl</v>
+      </c>
+      <c r="M30" s="39" t="str">
         <f>IF(H30&gt;I30,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N30" s="39" t="str">
+        <f>IF(M30="multiply",PROPER(B30)&amp;PROPER(C30),J31)</f>
+        <v>QtusMl</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="18">
+      <c r="A31" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="36">
+        <f t="shared" si="7"/>
+        <v>1.0566882094325937E-3</v>
+      </c>
+      <c r="G31" s="39">
+        <f>IF(M31="multiply",F31,F30)</f>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="H31" s="9">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="9">
+        <f t="shared" si="6"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="9"/>
+        <v>MlQtus</v>
+      </c>
+      <c r="K31" t="str">
+        <f t="shared" ref="K31" si="11">"constFactor"&amp;J31</f>
+        <v>constFactorMlQtus</v>
+      </c>
+      <c r="M31" s="39" t="str">
+        <f>IF(M30="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N30" s="62" t="str">
-        <f>IF(M30="multiply",PROPER(B30)&amp;PROPER(C30),J31)</f>
-        <v>CupcFzus</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="18">
-      <c r="A31" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="60">
-        <f t="shared" si="1"/>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="G31" s="62">
-        <f>IF(M31="multiply",F31,F30)</f>
-        <v>8.0000079970243636</v>
-      </c>
-      <c r="H31" s="9">
-        <f t="shared" si="2"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="I31" s="9">
-        <f t="shared" si="0"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="J31" t="str">
-        <f t="shared" si="3"/>
-        <v>CupcFzus</v>
-      </c>
-      <c r="K31" t="str">
-        <f t="shared" ref="K31" si="6">"constFactor"&amp;J31</f>
-        <v>constFactorCupcFzus</v>
-      </c>
-      <c r="M31" s="62" t="str">
-        <f>IF(M30="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N31" s="62" t="str">
+      <c r="N31" s="39" t="str">
         <f>IF(M31="multiply",PROPER(B31)&amp;PROPER(C31),J30)</f>
-        <v>CupcFzus</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="18">
+        <v>QtusMl</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="18">
       <c r="A32" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>95</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="60">
-        <f t="shared" si="1"/>
-        <v>1.9999980007459077</v>
-      </c>
-      <c r="G32" s="63">
+        <v>9</v>
+      </c>
+      <c r="F32" s="36">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+      <c r="G32" s="38">
         <f>IF(M32="multiply",F32,F33)</f>
-        <v>1.9999980007459077</v>
+        <v>8</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="2"/>
-        <v>29.573499999999999</v>
+        <f t="shared" si="8"/>
+        <v>29.573529562499999</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="0"/>
-        <v>14.78676478125</v>
+        <f t="shared" si="6"/>
+        <v>236.58823649999999</v>
       </c>
       <c r="J32" t="str">
-        <f t="shared" si="3"/>
-        <v>FzusTbspc</v>
+        <f t="shared" si="9"/>
+        <v>FzusCupc</v>
       </c>
       <c r="K32" t="str">
         <f>"constFactor"&amp;J32</f>
-        <v>constFactorFzusTbspc</v>
-      </c>
-      <c r="M32" s="63" t="str">
+        <v>constFactorFzusCupc</v>
+      </c>
+      <c r="M32" s="38" t="str">
         <f>IF(H32&gt;I32,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N32" s="63" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N32" s="38" t="str">
         <f>IF(M32="multiply",PROPER(B32)&amp;PROPER(C32),J33)</f>
-        <v>FzusTbspc</v>
+        <v>CupcFzus</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="18">
       <c r="A33" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>95</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="60">
-        <f t="shared" si="1"/>
-        <v>0.50000049981402273</v>
-      </c>
-      <c r="G33" s="63">
+        <v>10</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="36">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="G33" s="38">
         <f>IF(M33="multiply",F33,F32)</f>
-        <v>1.9999980007459077</v>
+        <v>8</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="2"/>
-        <v>14.78676478125</v>
+        <f t="shared" si="8"/>
+        <v>236.58823649999999</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="0"/>
-        <v>29.573499999999999</v>
+        <f t="shared" si="6"/>
+        <v>29.573529562499999</v>
       </c>
       <c r="J33" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspcFzus</v>
+        <f t="shared" si="9"/>
+        <v>CupcFzus</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" ref="K33" si="7">"constFactor"&amp;J33</f>
-        <v>constFactorTbspcFzus</v>
-      </c>
-      <c r="M33" s="63" t="str">
+        <f t="shared" ref="K33" si="12">"constFactor"&amp;J33</f>
+        <v>constFactorCupcFzus</v>
+      </c>
+      <c r="M33" s="38" t="str">
         <f>IF(M32="multiply","  divide","multiply")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N33" s="63" t="str">
+        <v>multiply</v>
+      </c>
+      <c r="N33" s="38" t="str">
         <f>IF(M33="multiply",PROPER(B33)&amp;PROPER(C33),J32)</f>
-        <v>FzusTbspc</v>
+        <v>CupcFzus</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="18">
       <c r="A34" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="60">
-        <f t="shared" si="1"/>
-        <v>4.2267528377303749E-3</v>
-      </c>
-      <c r="G34" s="62">
+        <v>13</v>
+      </c>
+      <c r="F34" s="36">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="G34" s="39">
         <f>IF(M34="multiply",F34,F35)</f>
-        <v>236.58823649999999</v>
+        <v>2</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>29.573529562499999</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="0"/>
-        <v>236.58823649999999</v>
+        <f t="shared" si="6"/>
+        <v>14.78676478125</v>
       </c>
       <c r="J34" t="str">
-        <f t="shared" si="3"/>
-        <v>MlCupc</v>
+        <f t="shared" si="9"/>
+        <v>FzusTbspc</v>
       </c>
       <c r="K34" t="str">
         <f>"constFactor"&amp;J34</f>
-        <v>constFactorMlCupc</v>
-      </c>
-      <c r="M34" s="62" t="str">
+        <v>constFactorFzusTbspc</v>
+      </c>
+      <c r="M34" s="39" t="str">
         <f>IF(H34&gt;I34,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N34" s="62" t="str">
+        <v>multiply</v>
+      </c>
+      <c r="N34" s="39" t="str">
         <f>IF(M34="multiply",PROPER(B34)&amp;PROPER(C34),J35)</f>
-        <v>CupcMl</v>
+        <v>FzusTbspc</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="18">
       <c r="A35" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="60">
-        <f t="shared" si="1"/>
-        <v>236.58823649999999</v>
-      </c>
-      <c r="G35" s="62">
+        <v>14</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="36">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="39">
         <f>IF(M35="multiply",F35,F34)</f>
-        <v>236.58823649999999</v>
+        <v>2</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="2"/>
-        <v>236.58823649999999</v>
+        <f t="shared" si="8"/>
+        <v>14.78676478125</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>29.573529562499999</v>
       </c>
       <c r="J35" t="str">
-        <f t="shared" si="3"/>
-        <v>CupcMl</v>
+        <f t="shared" si="9"/>
+        <v>TbspcFzus</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" ref="K35" si="8">"constFactor"&amp;J35</f>
-        <v>constFactorCupcMl</v>
-      </c>
-      <c r="M35" s="62" t="str">
+        <f t="shared" ref="K35" si="13">"constFactor"&amp;J35</f>
+        <v>constFactorTbspcFzus</v>
+      </c>
+      <c r="M35" s="39" t="str">
         <f>IF(M34="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N35" s="62" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N35" s="39" t="str">
         <f>IF(M35="multiply",PROPER(B35)&amp;PROPER(C35),J34)</f>
-        <v>CupcMl</v>
+        <v>FzusTbspc</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="18">
       <c r="A36" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" s="60">
-        <f t="shared" si="1"/>
-        <v>6.7628045403685999E-2</v>
-      </c>
-      <c r="G36" s="63">
+        <v>17</v>
+      </c>
+      <c r="F36" s="36">
+        <f t="shared" si="7"/>
+        <v>4.2267528377303749E-3</v>
+      </c>
+      <c r="G36" s="38">
         <f>IF(M36="multiply",F36,F37)</f>
-        <v>14.78676478125</v>
+        <v>236.58823649999999</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="0"/>
-        <v>14.78676478125</v>
+        <f t="shared" si="6"/>
+        <v>236.58823649999999</v>
       </c>
       <c r="J36" t="str">
-        <f t="shared" si="3"/>
-        <v>MlTbspc</v>
+        <f t="shared" si="9"/>
+        <v>MlCupc</v>
       </c>
       <c r="K36" t="str">
         <f>"constFactor"&amp;J36</f>
-        <v>constFactorMlTbspc</v>
-      </c>
-      <c r="M36" s="63" t="str">
+        <v>constFactorMlCupc</v>
+      </c>
+      <c r="M36" s="38" t="str">
         <f>IF(H36&gt;I36,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N36" s="63" t="str">
+      <c r="N36" s="38" t="str">
         <f>IF(M36="multiply",PROPER(B36)&amp;PROPER(C36),J37)</f>
-        <v>TbspcMl</v>
+        <v>CupcMl</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="18">
       <c r="A37" s="13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="60">
-        <f t="shared" si="1"/>
-        <v>14.78676478125</v>
-      </c>
-      <c r="G37" s="63">
+        <v>18</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="36">
+        <f t="shared" si="7"/>
+        <v>236.58823649999999</v>
+      </c>
+      <c r="G37" s="38">
         <f>IF(M37="multiply",F37,F36)</f>
-        <v>14.78676478125</v>
+        <v>236.58823649999999</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="2"/>
-        <v>14.78676478125</v>
+        <f t="shared" si="8"/>
+        <v>236.58823649999999</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J37" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspcMl</v>
+        <f t="shared" si="9"/>
+        <v>CupcMl</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" ref="K37" si="9">"constFactor"&amp;J37</f>
-        <v>constFactorTbspcMl</v>
-      </c>
-      <c r="M37" s="63" t="str">
+        <f t="shared" ref="K37" si="14">"constFactor"&amp;J37</f>
+        <v>constFactorCupcMl</v>
+      </c>
+      <c r="M37" s="38" t="str">
         <f>IF(M36="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N37" s="63" t="str">
+      <c r="N37" s="38" t="str">
         <f>IF(M37="multiply",PROPER(B37)&amp;PROPER(C37),J36)</f>
-        <v>TbspcMl</v>
+        <v>CupcMl</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="18">
       <c r="A38" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="60">
-        <f t="shared" si="1"/>
-        <v>0.20288413621105797</v>
-      </c>
-      <c r="G38" s="62">
+        <v>21</v>
+      </c>
+      <c r="F38" s="36">
+        <f t="shared" si="7"/>
+        <v>6.7628045403685999E-2</v>
+      </c>
+      <c r="G38" s="39">
         <f>IF(M38="multiply",F38,F39)</f>
-        <v>4.9289215937500002</v>
+        <v>14.78676478125</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="0"/>
-        <v>4.9289215937500002</v>
+        <f t="shared" si="6"/>
+        <v>14.78676478125</v>
       </c>
       <c r="J38" t="str">
-        <f t="shared" si="3"/>
-        <v>MlTspc</v>
+        <f t="shared" si="9"/>
+        <v>MlTbspc</v>
       </c>
       <c r="K38" t="str">
         <f>"constFactor"&amp;J38</f>
-        <v>constFactorMlTspc</v>
-      </c>
-      <c r="M38" s="62" t="str">
+        <v>constFactorMlTbspc</v>
+      </c>
+      <c r="M38" s="39" t="str">
         <f>IF(H38&gt;I38,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N38" s="62" t="str">
+      <c r="N38" s="39" t="str">
         <f>IF(M38="multiply",PROPER(B38)&amp;PROPER(C38),J39)</f>
-        <v>TspcMl</v>
+        <v>TbspcMl</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="18">
       <c r="A39" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="60">
-        <f t="shared" si="1"/>
-        <v>4.9289215937500002</v>
-      </c>
-      <c r="G39" s="62">
+        <v>22</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="36">
+        <f t="shared" si="7"/>
+        <v>14.78676478125</v>
+      </c>
+      <c r="G39" s="39">
         <f>IF(M39="multiply",F39,F38)</f>
-        <v>4.9289215937500002</v>
+        <v>14.78676478125</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="2"/>
-        <v>4.9289215937500002</v>
+        <f t="shared" si="8"/>
+        <v>14.78676478125</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J39" t="str">
-        <f t="shared" si="3"/>
-        <v>TspcMl</v>
+        <f t="shared" si="9"/>
+        <v>TbspcMl</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" ref="K39" si="10">"constFactor"&amp;J39</f>
-        <v>constFactorTspcMl</v>
-      </c>
-      <c r="M39" s="62" t="str">
+        <f t="shared" ref="K39" si="15">"constFactor"&amp;J39</f>
+        <v>constFactorTbspcMl</v>
+      </c>
+      <c r="M39" s="39" t="str">
         <f>IF(M38="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N39" s="62" t="str">
+      <c r="N39" s="39" t="str">
         <f>IF(M39="multiply",PROPER(B39)&amp;PROPER(C39),J38)</f>
-        <v>TspcMl</v>
+        <v>TbspcMl</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="18">
       <c r="A40" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F40" s="60">
-        <f t="shared" si="1"/>
-        <v>5.9999940022377229</v>
-      </c>
-      <c r="G40" s="63">
+        <v>25</v>
+      </c>
+      <c r="F40" s="36">
+        <f t="shared" si="7"/>
+        <v>0.20288413621105797</v>
+      </c>
+      <c r="G40" s="38">
         <f>IF(M40="multiply",F40,F41)</f>
-        <v>5.9999940022377229</v>
+        <v>4.9289215937500002</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" si="2"/>
-        <v>29.573499999999999</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4.9289215937500002</v>
       </c>
       <c r="J40" t="str">
-        <f t="shared" si="3"/>
-        <v>FzusTspc</v>
+        <f t="shared" si="9"/>
+        <v>MlTspc</v>
       </c>
       <c r="K40" t="str">
         <f>"constFactor"&amp;J40</f>
-        <v>constFactorFzusTspc</v>
-      </c>
-      <c r="M40" s="63" t="str">
+        <v>constFactorMlTspc</v>
+      </c>
+      <c r="M40" s="38" t="str">
         <f>IF(H40&gt;I40,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N40" s="63" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N40" s="38" t="str">
         <f>IF(M40="multiply",PROPER(B40)&amp;PROPER(C40),J41)</f>
-        <v>FzusTspc</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="19" thickBot="1">
+        <v>TspcMl</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="18">
       <c r="A41" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="36">
+        <f t="shared" si="7"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="G41" s="38">
+        <f>IF(M41="multiply",F41,F40)</f>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="H41" s="9">
+        <f t="shared" si="8"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="I41" s="9">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="9"/>
+        <v>TspcMl</v>
+      </c>
+      <c r="K41" t="str">
+        <f t="shared" ref="K41" si="16">"constFactor"&amp;J41</f>
+        <v>constFactorTspcMl</v>
+      </c>
+      <c r="M41" s="38" t="str">
+        <f>IF(M40="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N41" s="38" t="str">
+        <f>IF(M41="multiply",PROPER(B41)&amp;PROPER(C41),J40)</f>
+        <v>TspcMl</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="18">
+      <c r="A42" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="C42" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="36">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="G42" s="39">
+        <f>IF(M42="multiply",F42,F43)</f>
+        <v>6</v>
+      </c>
+      <c r="H42" s="9">
+        <f t="shared" si="8"/>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="I42" s="9">
+        <f t="shared" si="6"/>
+        <v>4.9289215937500002</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="9"/>
+        <v>FzusTspc</v>
+      </c>
+      <c r="K42" t="str">
+        <f>"constFactor"&amp;J42</f>
+        <v>constFactorFzusTspc</v>
+      </c>
+      <c r="M42" s="39" t="str">
+        <f>IF(H42&gt;I42,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N42" s="39" t="str">
+        <f>IF(M42="multiply",PROPER(B42)&amp;PROPER(C42),J43)</f>
+        <v>FzusTspc</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="19" thickBot="1">
+      <c r="A43" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E43" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F41" s="60">
-        <f t="shared" si="1"/>
-        <v>0.16666683327134091</v>
-      </c>
-      <c r="G41" s="63">
-        <f>IF(M41="multiply",F41,F40)</f>
-        <v>5.9999940022377229</v>
-      </c>
-      <c r="H41" s="9">
-        <f t="shared" si="2"/>
+      <c r="F43" s="36">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="G43" s="39">
+        <f>IF(M43="multiply",F43,F42)</f>
+        <v>6</v>
+      </c>
+      <c r="H43" s="9">
+        <f t="shared" si="8"/>
         <v>4.9289215937500002</v>
       </c>
-      <c r="I41" s="9">
-        <f t="shared" si="0"/>
-        <v>29.573499999999999</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="3"/>
+      <c r="I43" s="9">
+        <f t="shared" si="6"/>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="9"/>
         <v>TspcFzus</v>
       </c>
-      <c r="K41" t="str">
-        <f t="shared" ref="K41" si="11">"constFactor"&amp;J41</f>
+      <c r="K43" t="str">
+        <f t="shared" ref="K43" si="17">"constFactor"&amp;J43</f>
         <v>constFactorTspcFzus</v>
       </c>
-      <c r="M41" s="63" t="str">
-        <f>IF(M40="multiply","  divide","multiply")</f>
+      <c r="M43" s="39" t="str">
+        <f>IF(M42="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N41" s="63" t="str">
-        <f>IF(M41="multiply",PROPER(B41)&amp;PROPER(C41),J40)</f>
+      <c r="N43" s="39" t="str">
+        <f>IF(M43="multiply",PROPER(B43)&amp;PROPER(C43),J42)</f>
         <v>FzusTspc</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="17" thickBot="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="61"/>
-      <c r="G42"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" t="str">
-        <f t="shared" si="3"/>
+    <row r="44" spans="1:14" ht="17" thickBot="1">
+      <c r="A44" s="19"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="37"/>
+      <c r="G44"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" t="str">
+        <f t="shared" si="9"/>
         <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="18">
-      <c r="A43" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" s="60">
-        <f t="shared" si="1"/>
-        <v>568.26125000000002</v>
-      </c>
-      <c r="G43" s="62">
-        <f>IF(M43="multiply",F43,F44)</f>
-        <v>568.26125000000002</v>
-      </c>
-      <c r="H43" s="9">
-        <f t="shared" ref="H43:H59" si="12" xml:space="preserve"> VLOOKUP(B43,units,4,0)</f>
-        <v>568.26125000000002</v>
-      </c>
-      <c r="I43" s="9">
-        <f t="shared" ref="I43:I59" si="13" xml:space="preserve"> VLOOKUP(C43,units,4,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="3"/>
-        <v>PintukMl</v>
-      </c>
-      <c r="K43" t="str">
-        <f>"constFactor"&amp;J43</f>
-        <v>constFactorPintukMl</v>
-      </c>
-      <c r="M43" s="62" t="str">
-        <f>IF(H43&gt;I43,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N43" s="62" t="str">
-        <f>IF(M43="multiply",PROPER(B43)&amp;PROPER(C43),J44)</f>
-        <v>PintukMl</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="18">
-      <c r="A44" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="60">
-        <f t="shared" si="1"/>
-        <v>1.7597539863927023E-3</v>
-      </c>
-      <c r="G44" s="62">
-        <f>IF(M44="multiply",F44,F43)</f>
-        <v>568.26125000000002</v>
-      </c>
-      <c r="H44" s="9">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="I44" s="9">
-        <f t="shared" si="13"/>
-        <v>568.26125000000002</v>
-      </c>
-      <c r="J44" t="str">
-        <f t="shared" si="3"/>
-        <v>MlPintuk</v>
-      </c>
-      <c r="K44" t="str">
-        <f t="shared" ref="K44" si="14">"constFactor"&amp;J44</f>
-        <v>constFactorMlPintuk</v>
-      </c>
-      <c r="M44" s="62" t="str">
-        <f>IF(M43="multiply","  divide","multiply")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N44" s="62" t="str">
-        <f>IF(M44="multiply",PROPER(B44)&amp;PROPER(C44),J43)</f>
-        <v>PintukMl</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="18">
       <c r="A45" s="13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="60">
-        <f t="shared" si="1"/>
-        <v>1136.5225</v>
-      </c>
-      <c r="G45" s="63">
+      <c r="D45" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="36">
+        <f t="shared" si="7"/>
+        <v>568.26125000000002</v>
+      </c>
+      <c r="G45" s="38">
         <f>IF(M45="multiply",F45,F46)</f>
-        <v>1136.5225</v>
+        <v>568.26125000000002</v>
       </c>
       <c r="H45" s="9">
-        <f t="shared" si="12"/>
-        <v>1136.5225</v>
+        <f t="shared" ref="H45:H61" si="18" xml:space="preserve"> VLOOKUP(B45,units,4,0)</f>
+        <v>568.26125000000002</v>
       </c>
       <c r="I45" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="I45:I61" si="19" xml:space="preserve"> VLOOKUP(C45,units,4,0)</f>
         <v>1</v>
       </c>
       <c r="J45" t="str">
-        <f t="shared" si="3"/>
-        <v>QtMl</v>
+        <f t="shared" si="9"/>
+        <v>PintukMl</v>
       </c>
       <c r="K45" t="str">
         <f>"constFactor"&amp;J45</f>
-        <v>constFactorQtMl</v>
-      </c>
-      <c r="M45" s="63" t="str">
+        <v>constFactorPintukMl</v>
+      </c>
+      <c r="M45" s="38" t="str">
         <f>IF(H45&gt;I45,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N45" s="63" t="str">
+      <c r="N45" s="38" t="str">
         <f>IF(M45="multiply",PROPER(B45)&amp;PROPER(C45),J46)</f>
-        <v>QtMl</v>
+        <v>PintukMl</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="18">
       <c r="A46" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F46" s="60">
-        <f t="shared" si="1"/>
-        <v>8.7987699319635115E-4</v>
-      </c>
-      <c r="G46" s="63">
+        <v>31</v>
+      </c>
+      <c r="F46" s="36">
+        <f t="shared" si="7"/>
+        <v>1.7597539863927023E-3</v>
+      </c>
+      <c r="G46" s="38">
         <f>IF(M46="multiply",F46,F45)</f>
-        <v>1136.5225</v>
+        <v>568.26125000000002</v>
       </c>
       <c r="H46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I46" s="9">
-        <f t="shared" si="13"/>
-        <v>1136.5225</v>
+        <f t="shared" si="19"/>
+        <v>568.26125000000002</v>
       </c>
       <c r="J46" t="str">
-        <f t="shared" si="3"/>
-        <v>MlQt</v>
+        <f t="shared" si="9"/>
+        <v>MlPintuk</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" ref="K46" si="15">"constFactor"&amp;J46</f>
-        <v>constFactorMlQt</v>
-      </c>
-      <c r="M46" s="63" t="str">
+        <f t="shared" ref="K46" si="20">"constFactor"&amp;J46</f>
+        <v>constFactorMlPintuk</v>
+      </c>
+      <c r="M46" s="38" t="str">
         <f>IF(M45="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N46" s="63" t="str">
+      <c r="N46" s="38" t="str">
         <f>IF(M46="multiply",PROPER(B46)&amp;PROPER(C46),J45)</f>
-        <v>QtMl</v>
+        <v>PintukMl</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="18">
       <c r="A47" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F47" s="60">
-        <f t="shared" si="1"/>
-        <v>0.10000013198154897</v>
-      </c>
-      <c r="G47" s="62">
+        <v>33</v>
+      </c>
+      <c r="F47" s="36">
+        <f t="shared" si="7"/>
+        <v>1136.5225</v>
+      </c>
+      <c r="G47" s="39">
         <f>IF(M47="multiply",F47,F48)</f>
-        <v>9.9999868018625211</v>
+        <v>1136.5225</v>
       </c>
       <c r="H47" s="9">
-        <f t="shared" si="12"/>
-        <v>28.4131</v>
+        <f t="shared" si="18"/>
+        <v>1136.5225</v>
       </c>
       <c r="I47" s="9">
-        <f t="shared" si="13"/>
-        <v>284.13062500000001</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="J47" t="str">
-        <f t="shared" si="3"/>
-        <v>FzukCupuk</v>
+        <f t="shared" si="9"/>
+        <v>QtMl</v>
       </c>
       <c r="K47" t="str">
         <f>"constFactor"&amp;J47</f>
-        <v>constFactorFzukCupuk</v>
-      </c>
-      <c r="M47" s="62" t="str">
+        <v>constFactorQtMl</v>
+      </c>
+      <c r="M47" s="39" t="str">
         <f>IF(H47&gt;I47,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N47" s="62" t="str">
+        <v>multiply</v>
+      </c>
+      <c r="N47" s="39" t="str">
         <f>IF(M47="multiply",PROPER(B47)&amp;PROPER(C47),J48)</f>
-        <v>CupukFzuk</v>
+        <v>QtMl</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="18">
       <c r="A48" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F48" s="60">
-        <f t="shared" si="1"/>
-        <v>9.9999868018625211</v>
-      </c>
-      <c r="G48" s="62">
+        <v>35</v>
+      </c>
+      <c r="F48" s="36">
+        <f t="shared" si="7"/>
+        <v>8.7987699319635115E-4</v>
+      </c>
+      <c r="G48" s="39">
         <f>IF(M48="multiply",F48,F47)</f>
-        <v>9.9999868018625211</v>
+        <v>1136.5225</v>
       </c>
       <c r="H48" s="9">
-        <f t="shared" si="12"/>
-        <v>284.13062500000001</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I48" s="9">
-        <f t="shared" si="13"/>
-        <v>28.4131</v>
+        <f t="shared" si="19"/>
+        <v>1136.5225</v>
       </c>
       <c r="J48" t="str">
-        <f t="shared" si="3"/>
-        <v>CupukFzuk</v>
+        <f t="shared" si="9"/>
+        <v>MlQt</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" ref="K48" si="16">"constFactor"&amp;J48</f>
-        <v>constFactorCupukFzuk</v>
-      </c>
-      <c r="M48" s="62" t="str">
+        <f t="shared" ref="K48" si="21">"constFactor"&amp;J48</f>
+        <v>constFactorMlQt</v>
+      </c>
+      <c r="M48" s="39" t="str">
         <f>IF(M47="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N48" s="62" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N48" s="39" t="str">
         <f>IF(M48="multiply",PROPER(B48)&amp;PROPER(C48),J47)</f>
-        <v>CupukFzuk</v>
+        <v>QtMl</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="18">
       <c r="A49" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F49" s="60">
-        <f t="shared" si="1"/>
-        <v>1.6000021117047836</v>
-      </c>
-      <c r="G49" s="63">
+        <v>37</v>
+      </c>
+      <c r="F49" s="36">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
+      <c r="G49" s="38">
         <f>IF(M49="multiply",F49,F50)</f>
-        <v>1.6000021117047836</v>
+        <v>10</v>
       </c>
       <c r="H49" s="9">
-        <f t="shared" si="12"/>
-        <v>28.4131</v>
+        <f t="shared" si="18"/>
+        <v>28.413062500000002</v>
       </c>
       <c r="I49" s="9">
-        <f t="shared" si="13"/>
-        <v>17.758164062500001</v>
+        <f t="shared" si="19"/>
+        <v>284.13062500000001</v>
       </c>
       <c r="J49" t="str">
-        <f t="shared" si="3"/>
-        <v>FzukTbspuk</v>
+        <f t="shared" si="9"/>
+        <v>FzukCupuk</v>
       </c>
       <c r="K49" t="str">
         <f>"constFactor"&amp;J49</f>
-        <v>constFactorFzukTbspuk</v>
-      </c>
-      <c r="M49" s="63" t="str">
+        <v>constFactorFzukCupuk</v>
+      </c>
+      <c r="M49" s="38" t="str">
         <f>IF(H49&gt;I49,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N49" s="63" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N49" s="38" t="str">
         <f>IF(M49="multiply",PROPER(B49)&amp;PROPER(C49),J50)</f>
-        <v>FzukTbspuk</v>
+        <v>CupukFzuk</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="18">
       <c r="A50" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E50" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" s="60">
-        <f t="shared" si="1"/>
-        <v>0.62499917511640757</v>
-      </c>
-      <c r="G50" s="63">
+        <v>38</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" s="36">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="G50" s="38">
         <f>IF(M50="multiply",F50,F49)</f>
-        <v>1.6000021117047836</v>
+        <v>10</v>
       </c>
       <c r="H50" s="9">
-        <f t="shared" si="12"/>
-        <v>17.758164062500001</v>
+        <f t="shared" si="18"/>
+        <v>284.13062500000001</v>
       </c>
       <c r="I50" s="9">
-        <f t="shared" si="13"/>
-        <v>28.4131</v>
+        <f t="shared" si="19"/>
+        <v>28.413062500000002</v>
       </c>
       <c r="J50" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspukFzuk</v>
+        <f t="shared" si="9"/>
+        <v>CupukFzuk</v>
       </c>
       <c r="K50" t="str">
-        <f t="shared" ref="K50" si="17">"constFactor"&amp;J50</f>
-        <v>constFactorTbspukFzuk</v>
-      </c>
-      <c r="M50" s="63" t="str">
+        <f t="shared" ref="K50" si="22">"constFactor"&amp;J50</f>
+        <v>constFactorCupukFzuk</v>
+      </c>
+      <c r="M50" s="38" t="str">
         <f>IF(M49="multiply","  divide","multiply")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N50" s="63" t="str">
+        <v>multiply</v>
+      </c>
+      <c r="N50" s="38" t="str">
         <f>IF(M50="multiply",PROPER(B50)&amp;PROPER(C50),J49)</f>
-        <v>FzukTbspuk</v>
+        <v>CupukFzuk</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="18">
       <c r="A51" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>72</v>
-      </c>
       <c r="D51" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="60">
-        <f t="shared" si="1"/>
-        <v>0.62499917511640757</v>
-      </c>
-      <c r="G51"/>
+        <v>40</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" s="36">
+        <f t="shared" si="7"/>
+        <v>1.6</v>
+      </c>
+      <c r="G51" s="39">
+        <f>IF(M51="multiply",F51,F52)</f>
+        <v>1.6</v>
+      </c>
       <c r="H51" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="I51" s="9">
+        <f t="shared" si="19"/>
         <v>17.758164062500001</v>
       </c>
-      <c r="I51" s="9">
-        <f t="shared" si="13"/>
-        <v>28.4131</v>
-      </c>
       <c r="J51" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspukFzuk</v>
+        <f t="shared" si="9"/>
+        <v>FzukTbspuk</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="4"/>
-        <v>constFactorTbspukFzuk</v>
+        <f>"constFactor"&amp;J51</f>
+        <v>constFactorFzukTbspuk</v>
+      </c>
+      <c r="M51" s="39" t="str">
+        <f>IF(H51&gt;I51,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N51" s="39" t="str">
+        <f>IF(M51="multiply",PROPER(B51)&amp;PROPER(C51),J52)</f>
+        <v>FzukTbspuk</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="18">
       <c r="A52" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F52" s="60">
-        <f t="shared" si="1"/>
-        <v>3.5195079727854046E-3</v>
-      </c>
-      <c r="G52" s="62">
-        <f>IF(M52="multiply",F52,F53)</f>
-        <v>284.13062500000001</v>
+        <v>42</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="36">
+        <f t="shared" si="7"/>
+        <v>0.625</v>
+      </c>
+      <c r="G52" s="39">
+        <f>IF(M52="multiply",F52,F51)</f>
+        <v>1.6</v>
       </c>
       <c r="H52" s="9">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <f t="shared" si="18"/>
+        <v>17.758164062500001</v>
       </c>
       <c r="I52" s="9">
-        <f t="shared" si="13"/>
-        <v>284.13062500000001</v>
+        <f t="shared" si="19"/>
+        <v>28.413062500000002</v>
       </c>
       <c r="J52" t="str">
-        <f t="shared" si="3"/>
-        <v>MlCupuk</v>
+        <f t="shared" si="9"/>
+        <v>TbspukFzuk</v>
       </c>
       <c r="K52" t="str">
-        <f>"constFactor"&amp;J52</f>
-        <v>constFactorMlCupuk</v>
-      </c>
-      <c r="M52" s="62" t="str">
-        <f>IF(H52&gt;I52,"multiply","  divide")</f>
+        <f t="shared" ref="K52" si="23">"constFactor"&amp;J52</f>
+        <v>constFactorTbspukFzuk</v>
+      </c>
+      <c r="M52" s="39" t="str">
+        <f>IF(M51="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N52" s="62" t="str">
-        <f>IF(M52="multiply",PROPER(B52)&amp;PROPER(C52),J53)</f>
-        <v>CupukMl</v>
+      <c r="N52" s="39" t="str">
+        <f>IF(M52="multiply",PROPER(B52)&amp;PROPER(C52),J51)</f>
+        <v>FzukTbspuk</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="18">
       <c r="A53" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F53" s="60">
-        <f t="shared" si="1"/>
-        <v>284.13062500000001</v>
-      </c>
-      <c r="G53" s="62">
-        <f>IF(M53="multiply",F53,F52)</f>
-        <v>284.13062500000001</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="36">
+        <f t="shared" si="7"/>
+        <v>0.625</v>
+      </c>
+      <c r="G53"/>
       <c r="H53" s="9">
-        <f t="shared" si="12"/>
-        <v>284.13062500000001</v>
+        <f t="shared" si="18"/>
+        <v>17.758164062500001</v>
       </c>
       <c r="I53" s="9">
-        <f t="shared" si="13"/>
-        <v>1</v>
+        <f t="shared" si="19"/>
+        <v>28.413062500000002</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" si="3"/>
-        <v>CupukMl</v>
+        <f t="shared" si="9"/>
+        <v>TbspukFzuk</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" ref="K53" si="18">"constFactor"&amp;J53</f>
-        <v>constFactorCupukMl</v>
-      </c>
-      <c r="M53" s="62" t="str">
-        <f>IF(M52="multiply","  divide","multiply")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N53" s="62" t="str">
-        <f>IF(M53="multiply",PROPER(B53)&amp;PROPER(C53),J52)</f>
-        <v>CupukMl</v>
+        <f t="shared" si="10"/>
+        <v>constFactorTbspukFzuk</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="18">
       <c r="A54" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F54" s="60">
-        <f t="shared" si="1"/>
-        <v>5.6312127564566473E-2</v>
-      </c>
-      <c r="G54" s="63">
+        <v>45</v>
+      </c>
+      <c r="F54" s="36">
+        <f t="shared" si="7"/>
+        <v>3.5195079727854046E-3</v>
+      </c>
+      <c r="G54" s="38">
         <f>IF(M54="multiply",F54,F55)</f>
-        <v>17.758164062500001</v>
+        <v>284.13062500000001</v>
       </c>
       <c r="H54" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I54" s="9">
-        <f t="shared" si="13"/>
-        <v>17.758164062500001</v>
+        <f t="shared" si="19"/>
+        <v>284.13062500000001</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="3"/>
-        <v>MlTbspuk</v>
+        <f t="shared" si="9"/>
+        <v>MlCupuk</v>
       </c>
       <c r="K54" t="str">
         <f>"constFactor"&amp;J54</f>
-        <v>constFactorMlTbspuk</v>
-      </c>
-      <c r="M54" s="63" t="str">
+        <v>constFactorMlCupuk</v>
+      </c>
+      <c r="M54" s="38" t="str">
         <f>IF(H54&gt;I54,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N54" s="63" t="str">
+      <c r="N54" s="38" t="str">
         <f>IF(M54="multiply",PROPER(B54)&amp;PROPER(C54),J55)</f>
-        <v>TbspukMl</v>
+        <v>CupukMl</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="18">
       <c r="A55" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F55" s="60">
-        <f t="shared" si="1"/>
-        <v>17.758164062500001</v>
-      </c>
-      <c r="G55" s="63">
+        <v>47</v>
+      </c>
+      <c r="F55" s="36">
+        <f t="shared" si="7"/>
+        <v>284.13062500000001</v>
+      </c>
+      <c r="G55" s="38">
         <f>IF(M55="multiply",F55,F54)</f>
-        <v>17.758164062500001</v>
+        <v>284.13062500000001</v>
       </c>
       <c r="H55" s="9">
-        <f t="shared" si="12"/>
-        <v>17.758164062500001</v>
+        <f t="shared" si="18"/>
+        <v>284.13062500000001</v>
       </c>
       <c r="I55" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="3"/>
-        <v>TbspukMl</v>
+        <f t="shared" si="9"/>
+        <v>CupukMl</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" ref="K55" si="19">"constFactor"&amp;J55</f>
-        <v>constFactorTbspukMl</v>
-      </c>
-      <c r="M55" s="63" t="str">
+        <f t="shared" ref="K55" si="24">"constFactor"&amp;J55</f>
+        <v>constFactorCupukMl</v>
+      </c>
+      <c r="M55" s="38" t="str">
         <f>IF(M54="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N55" s="63" t="str">
+      <c r="N55" s="38" t="str">
         <f>IF(M55="multiply",PROPER(B55)&amp;PROPER(C55),J54)</f>
-        <v>TbspukMl</v>
+        <v>CupukMl</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="18">
       <c r="A56" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F56" s="60">
-        <f t="shared" si="1"/>
-        <v>0.16893638269370037</v>
-      </c>
-      <c r="G56" s="62">
+        <v>49</v>
+      </c>
+      <c r="F56" s="36">
+        <f t="shared" si="7"/>
+        <v>5.6312127564566473E-2</v>
+      </c>
+      <c r="G56" s="39">
         <f>IF(M56="multiply",F56,F57)</f>
-        <v>5.9193880208333001</v>
+        <v>17.758164062500001</v>
       </c>
       <c r="H56" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I56" s="9">
-        <f t="shared" si="13"/>
-        <v>5.9193880208333001</v>
+        <f t="shared" si="19"/>
+        <v>17.758164062500001</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="3"/>
-        <v>MlTspuk</v>
+        <f t="shared" si="9"/>
+        <v>MlTbspuk</v>
       </c>
       <c r="K56" t="str">
         <f>"constFactor"&amp;J56</f>
-        <v>constFactorMlTspuk</v>
-      </c>
-      <c r="M56" s="62" t="str">
+        <v>constFactorMlTbspuk</v>
+      </c>
+      <c r="M56" s="39" t="str">
         <f>IF(H56&gt;I56,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N56" s="62" t="str">
+      <c r="N56" s="39" t="str">
         <f>IF(M56="multiply",PROPER(B56)&amp;PROPER(C56),J57)</f>
-        <v>TspukMl</v>
+        <v>TbspukMl</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="18">
       <c r="A57" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>76</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F57" s="60">
-        <f t="shared" si="1"/>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="G57" s="62">
+        <v>51</v>
+      </c>
+      <c r="F57" s="36">
+        <f t="shared" si="7"/>
+        <v>17.758164062500001</v>
+      </c>
+      <c r="G57" s="39">
         <f>IF(M57="multiply",F57,F56)</f>
-        <v>5.9193880208333001</v>
+        <v>17.758164062500001</v>
       </c>
       <c r="H57" s="9">
-        <f t="shared" si="12"/>
-        <v>5.9193880208333001</v>
+        <f t="shared" si="18"/>
+        <v>17.758164062500001</v>
       </c>
       <c r="I57" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J57" t="str">
-        <f t="shared" si="3"/>
-        <v>TspukMl</v>
+        <f t="shared" si="9"/>
+        <v>TbspukMl</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" ref="K57" si="20">"constFactor"&amp;J57</f>
-        <v>constFactorTspukMl</v>
-      </c>
-      <c r="M57" s="62" t="str">
+        <f t="shared" ref="K57" si="25">"constFactor"&amp;J57</f>
+        <v>constFactorTbspukMl</v>
+      </c>
+      <c r="M57" s="39" t="str">
         <f>IF(M56="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N57" s="62" t="str">
+      <c r="N57" s="39" t="str">
         <f>IF(M57="multiply",PROPER(B57)&amp;PROPER(C57),J56)</f>
-        <v>TspukMl</v>
+        <v>TbspukMl</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="18">
       <c r="A58" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" s="60">
-        <f t="shared" si="1"/>
-        <v>4.8000063351143778</v>
-      </c>
-      <c r="G58" s="63">
+        <v>53</v>
+      </c>
+      <c r="F58" s="36">
+        <f t="shared" si="7"/>
+        <v>0.1689363826936994</v>
+      </c>
+      <c r="G58" s="38">
         <f>IF(M58="multiply",F58,F59)</f>
-        <v>4.8000063351143778</v>
+        <v>5.9193880208333338</v>
       </c>
       <c r="H58" s="9">
-        <f t="shared" si="12"/>
-        <v>28.4131</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I58" s="9">
-        <f t="shared" si="13"/>
-        <v>5.9193880208333001</v>
+        <f t="shared" si="19"/>
+        <v>5.9193880208333338</v>
       </c>
       <c r="J58" t="str">
-        <f t="shared" si="3"/>
-        <v>FzukTspuk</v>
+        <f t="shared" si="9"/>
+        <v>MlTspuk</v>
       </c>
       <c r="K58" t="str">
         <f>"constFactor"&amp;J58</f>
-        <v>constFactorFzukTspuk</v>
-      </c>
-      <c r="M58" s="63" t="str">
+        <v>constFactorMlTspuk</v>
+      </c>
+      <c r="M58" s="38" t="str">
         <f>IF(H58&gt;I58,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N58" s="63" t="str">
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N58" s="38" t="str">
         <f>IF(M58="multiply",PROPER(B58)&amp;PROPER(C58),J59)</f>
-        <v>FzukTspuk</v>
+        <v>TspukMl</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="18">
       <c r="A59" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>73</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="36">
+        <f t="shared" si="7"/>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="G59" s="38">
+        <f>IF(M59="multiply",F59,F58)</f>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="H59" s="9">
+        <f t="shared" si="18"/>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="I59" s="9">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="9"/>
+        <v>TspukMl</v>
+      </c>
+      <c r="K59" t="str">
+        <f t="shared" ref="K59" si="26">"constFactor"&amp;J59</f>
+        <v>constFactorTspukMl</v>
+      </c>
+      <c r="M59" s="38" t="str">
+        <f>IF(M58="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N59" s="38" t="str">
+        <f>IF(M59="multiply",PROPER(B59)&amp;PROPER(C59),J58)</f>
+        <v>TspukMl</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="18">
+      <c r="A60" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="70" t="s">
+      <c r="C60" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F60" s="36">
+        <f t="shared" si="7"/>
+        <v>4.8</v>
+      </c>
+      <c r="G60" s="39">
+        <f>IF(M60="multiply",F60,F61)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H60" s="9">
+        <f t="shared" si="18"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="I60" s="9">
+        <f t="shared" si="19"/>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="9"/>
+        <v>FzukTspuk</v>
+      </c>
+      <c r="K60" t="str">
+        <f>"constFactor"&amp;J60</f>
+        <v>constFactorFzukTspuk</v>
+      </c>
+      <c r="M60" s="39" t="str">
+        <f>IF(H60&gt;I60,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N60" s="39" t="str">
+        <f>IF(M60="multiply",PROPER(B60)&amp;PROPER(C60),J61)</f>
+        <v>FzukTspuk</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="18">
+      <c r="A61" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="E59" s="71" t="s">
+      <c r="E61" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="F59" s="60">
-        <f t="shared" si="1"/>
-        <v>0.2083330583721347</v>
-      </c>
-      <c r="G59" s="63">
-        <f>IF(M59="multiply",F59,F58)</f>
-        <v>4.8000063351143778</v>
-      </c>
-      <c r="H59" s="9">
-        <f t="shared" si="12"/>
-        <v>5.9193880208333001</v>
-      </c>
-      <c r="I59" s="9">
-        <f t="shared" si="13"/>
-        <v>28.4131</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="3"/>
+      <c r="F61" s="36">
+        <f t="shared" si="7"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="G61" s="39">
+        <f>IF(M61="multiply",F61,F60)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H61" s="9">
+        <f t="shared" si="18"/>
+        <v>5.9193880208333338</v>
+      </c>
+      <c r="I61" s="9">
+        <f t="shared" si="19"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="9"/>
         <v>TspukFzuk</v>
       </c>
-      <c r="K59" t="str">
-        <f>"constFactor"&amp;J59</f>
+      <c r="K61" t="str">
+        <f>"constFactor"&amp;J61</f>
         <v>constFactorTspukFzuk</v>
       </c>
-      <c r="M59" s="63" t="str">
-        <f>IF(M58="multiply","  divide","multiply")</f>
+      <c r="M61" s="39" t="str">
+        <f>IF(M60="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N59" s="63" t="str">
-        <f>IF(M59="multiply",PROPER(B59)&amp;PROPER(C59),J58)</f>
+      <c r="N61" s="39" t="str">
+        <f>IF(M61="multiply",PROPER(B61)&amp;PROPER(C61),J60)</f>
         <v>FzukTspuk</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="18">
-      <c r="A60" s="76" t="str">
-        <f>MID(D60,5,99)</f>
+    <row r="62" spans="1:14" ht="18">
+      <c r="A62" s="51" t="str">
+        <f>MID(D62,5,99)</f>
         <v>MLtoIN3</v>
       </c>
-      <c r="B60" s="77" t="str">
-        <f>MID(A60,1,SEARCH("to",A60)-1)</f>
+      <c r="B62" s="52" t="str">
+        <f>MID(A62,1,SEARCH("to",A62)-1)</f>
         <v>ML</v>
       </c>
-      <c r="C60" s="77" t="str">
-        <f>MID(A60,SEARCH("to",A60)+2,99)</f>
+      <c r="C62" s="52" t="str">
+        <f>MID(A62,SEARCH("to",A62)+2,99)</f>
         <v>IN3</v>
       </c>
-      <c r="D60" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="E60" s="73" t="s">
-        <v>208</v>
-      </c>
-      <c r="F60" s="60">
-        <f t="shared" si="1"/>
+      <c r="D62" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="F62" s="36">
+        <f t="shared" si="7"/>
         <v>6.1023744094732289E-2</v>
       </c>
-      <c r="G60" s="62">
-        <f>IF(M60="multiply",F60,F61)</f>
+      <c r="G62" s="38">
+        <f>IF(M62="multiply",F62,F63)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="H60" s="9">
-        <f xml:space="preserve"> VLOOKUP(B60,units,4,0)</f>
+      <c r="H62" s="9">
+        <f xml:space="preserve"> VLOOKUP(B62,units,4,0)</f>
         <v>1</v>
       </c>
-      <c r="I60" s="9">
-        <f t="shared" ref="I60:I67" si="21" xml:space="preserve"> VLOOKUP(C60,units,4,0)</f>
+      <c r="I62" s="9">
+        <f t="shared" ref="I62:I69" si="27" xml:space="preserve"> VLOOKUP(C62,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="J60" t="str">
-        <f t="shared" ref="J60:J67" si="22">PROPER(B60)&amp;PROPER(C60)</f>
+      <c r="J62" t="str">
+        <f t="shared" ref="J62:J69" si="28">PROPER(B62)&amp;PROPER(C62)</f>
         <v>MlIn3</v>
       </c>
-      <c r="K60" t="str">
-        <f t="shared" ref="K60:K67" si="23">"constFactor"&amp;J60</f>
+      <c r="K62" t="str">
+        <f t="shared" ref="K62:K69" si="29">"constFactor"&amp;J62</f>
         <v>constFactorMlIn3</v>
       </c>
-      <c r="M60" s="62" t="str">
-        <f>IF(H60&gt;I60,"multiply","  divide")</f>
+      <c r="M62" s="38" t="str">
+        <f>IF(H62&gt;I62,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N60" s="62" t="str">
-        <f>IF(M60="multiply",PROPER(B60)&amp;PROPER(C60),J61)</f>
+      <c r="N62" s="38" t="str">
+        <f>IF(M62="multiply",PROPER(B62)&amp;PROPER(C62),J63)</f>
         <v>In3Ml</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="18">
-      <c r="A61" s="76" t="str">
-        <f t="shared" ref="A61:A67" si="24">MID(D61,5,99)</f>
+    <row r="63" spans="1:14" ht="18">
+      <c r="A63" s="51" t="str">
+        <f t="shared" ref="A63:A69" si="30">MID(D63,5,99)</f>
         <v>IN3toML</v>
       </c>
-      <c r="B61" s="77" t="str">
-        <f t="shared" ref="B61:B67" si="25">MID(A61,1,SEARCH("to",A61)-1)</f>
+      <c r="B63" s="52" t="str">
+        <f t="shared" ref="B63:B69" si="31">MID(A63,1,SEARCH("to",A63)-1)</f>
         <v>IN3</v>
       </c>
-      <c r="C61" s="77" t="str">
-        <f t="shared" ref="C61:C67" si="26">MID(A61,SEARCH("to",A61)+2,99)</f>
+      <c r="C63" s="52" t="str">
+        <f t="shared" ref="C63:C69" si="32">MID(A63,SEARCH("to",A63)+2,99)</f>
         <v>ML</v>
       </c>
-      <c r="D61" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="E61" s="73" t="s">
-        <v>209</v>
-      </c>
-      <c r="F61" s="60">
-        <f t="shared" si="1"/>
+      <c r="D63" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="F63" s="36">
+        <f t="shared" si="7"/>
         <v>16.387063999999999</v>
       </c>
-      <c r="G61" s="62">
-        <f>IF(M61="multiply",F61,F60)</f>
+      <c r="G63" s="38">
+        <f>IF(M63="multiply",F63,F62)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="H61" s="9">
-        <f t="shared" ref="H61:H67" si="27" xml:space="preserve"> VLOOKUP(B61,units,4,0)</f>
+      <c r="H63" s="9">
+        <f t="shared" ref="H63:H69" si="33" xml:space="preserve"> VLOOKUP(B63,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="I61" s="9">
-        <f t="shared" si="21"/>
+      <c r="I63" s="9">
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
-      <c r="J61" t="str">
-        <f t="shared" si="22"/>
+      <c r="J63" t="str">
+        <f t="shared" si="28"/>
         <v>In3Ml</v>
       </c>
-      <c r="K61" t="str">
-        <f t="shared" si="23"/>
+      <c r="K63" t="str">
+        <f t="shared" si="29"/>
         <v>constFactorIn3Ml</v>
       </c>
-      <c r="M61" s="62" t="str">
-        <f>IF(M60="multiply","  divide","multiply")</f>
+      <c r="M63" s="38" t="str">
+        <f>IF(M62="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N61" s="62" t="str">
-        <f>IF(M61="multiply",PROPER(B61)&amp;PROPER(C61),J60)</f>
+      <c r="N63" s="38" t="str">
+        <f>IF(M63="multiply",PROPER(B63)&amp;PROPER(C63),J62)</f>
         <v>In3Ml</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="18">
-      <c r="A62" s="76" t="str">
-        <f t="shared" si="24"/>
+    <row r="64" spans="1:14" ht="18">
+      <c r="A64" s="51" t="str">
+        <f t="shared" si="30"/>
         <v>FT3toGLUK</v>
       </c>
-      <c r="B62" s="77" t="str">
-        <f t="shared" si="25"/>
+      <c r="B64" s="52" t="str">
+        <f t="shared" si="31"/>
         <v>FT3</v>
       </c>
-      <c r="C62" s="77" t="str">
-        <f t="shared" si="26"/>
+      <c r="C64" s="52" t="str">
+        <f t="shared" si="32"/>
         <v>GLUK</v>
       </c>
-      <c r="D62" s="72" t="s">
-        <v>202</v>
-      </c>
-      <c r="E62" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="F62" s="60">
-        <f t="shared" si="1"/>
-        <v>6.2302059127542027</v>
-      </c>
-      <c r="G62" s="63">
-        <f>IF(M62="multiply",F62,F63)</f>
-        <v>6.2302059127542027</v>
-      </c>
-      <c r="H62" s="9">
+      <c r="D64" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64" s="36">
+        <f t="shared" si="7"/>
+        <v>6.2288354590428261</v>
+      </c>
+      <c r="G64" s="39">
+        <f>IF(M64="multiply",F64,F65)</f>
+        <v>6.2288354590428261</v>
+      </c>
+      <c r="H64" s="9">
+        <f t="shared" si="33"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="I64" s="9">
+        <f t="shared" si="27"/>
+        <v>4546.09</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="28"/>
+        <v>Ft3Gluk</v>
+      </c>
+      <c r="K64" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorFt3Gluk</v>
+      </c>
+      <c r="M64" s="39" t="str">
+        <f>IF(H64&gt;I64,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N64" s="39" t="str">
+        <f>IF(M64="multiply",PROPER(B64)&amp;PROPER(C64),J65)</f>
+        <v>Ft3Gluk</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="18">
+      <c r="A65" s="51" t="str">
+        <f t="shared" si="30"/>
+        <v>GLUKtoFT3</v>
+      </c>
+      <c r="B65" s="52" t="str">
+        <f t="shared" si="31"/>
+        <v>GLUK</v>
+      </c>
+      <c r="C65" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>FT3</v>
+      </c>
+      <c r="D65" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="F65" s="36">
+        <f t="shared" si="7"/>
+        <v>0.16054365323589206</v>
+      </c>
+      <c r="G65" s="39">
+        <f>IF(M65="multiply",F65,F64)</f>
+        <v>6.2288354590428261</v>
+      </c>
+      <c r="H65" s="9">
+        <f t="shared" si="33"/>
+        <v>4546.09</v>
+      </c>
+      <c r="I65" s="9">
         <f t="shared" si="27"/>
         <v>28316.846592000002</v>
       </c>
-      <c r="I62" s="9">
-        <f t="shared" si="21"/>
-        <v>4545.09</v>
-      </c>
-      <c r="J62" t="str">
-        <f t="shared" si="22"/>
+      <c r="J65" t="str">
+        <f t="shared" si="28"/>
+        <v>GlukFt3</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorGlukFt3</v>
+      </c>
+      <c r="M65" s="39" t="str">
+        <f>IF(M64="multiply","  divide","multiply")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N65" s="39" t="str">
+        <f>IF(M65="multiply",PROPER(B65)&amp;PROPER(C65),J64)</f>
         <v>Ft3Gluk</v>
       </c>
-      <c r="K62" t="str">
-        <f t="shared" si="23"/>
-        <v>constFactorFt3Gluk</v>
-      </c>
-      <c r="M62" s="63" t="str">
-        <f>IF(H62&gt;I62,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N62" s="63" t="str">
-        <f>IF(M62="multiply",PROPER(B62)&amp;PROPER(C62),J63)</f>
-        <v>Ft3Gluk</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="18">
-      <c r="A63" s="76" t="str">
-        <f t="shared" si="24"/>
-        <v>GLUKtoFT3</v>
-      </c>
-      <c r="B63" s="77" t="str">
-        <f t="shared" si="25"/>
-        <v>GLUK</v>
-      </c>
-      <c r="C63" s="77" t="str">
-        <f t="shared" si="26"/>
+    </row>
+    <row r="66" spans="1:14" ht="18">
+      <c r="A66" s="51" t="str">
+        <f t="shared" si="30"/>
+        <v>LtoFT3</v>
+      </c>
+      <c r="B66" s="52" t="str">
+        <f t="shared" si="31"/>
+        <v>L</v>
+      </c>
+      <c r="C66" s="52" t="str">
+        <f t="shared" si="32"/>
         <v>FT3</v>
       </c>
-      <c r="D63" s="72" t="s">
-        <v>203</v>
-      </c>
-      <c r="E63" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="F63" s="60">
-        <f t="shared" si="1"/>
-        <v>0.16050833856917057</v>
-      </c>
-      <c r="G63" s="63">
-        <f>IF(M63="multiply",F63,F62)</f>
-        <v>6.2302059127542027</v>
-      </c>
-      <c r="H63" s="9">
+      <c r="D66" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="F66" s="36">
+        <f t="shared" si="7"/>
+        <v>3.5314666721488586E-2</v>
+      </c>
+      <c r="G66" s="38">
+        <f>IF(M66="multiply",F66,F67)</f>
+        <v>28.316846592000001</v>
+      </c>
+      <c r="H66" s="9">
+        <f t="shared" si="33"/>
+        <v>1000</v>
+      </c>
+      <c r="I66" s="9">
         <f t="shared" si="27"/>
-        <v>4545.09</v>
-      </c>
-      <c r="I63" s="9">
-        <f t="shared" si="21"/>
         <v>28316.846592000002</v>
       </c>
-      <c r="J63" t="str">
-        <f t="shared" si="22"/>
-        <v>GlukFt3</v>
-      </c>
-      <c r="K63" t="str">
-        <f t="shared" si="23"/>
-        <v>constFactorGlukFt3</v>
-      </c>
-      <c r="M63" s="63" t="str">
-        <f>IF(M62="multiply","  divide","multiply")</f>
+      <c r="J66" t="str">
+        <f t="shared" si="28"/>
+        <v>LFt3</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorLFt3</v>
+      </c>
+      <c r="M66" s="38" t="str">
+        <f>IF(H66&gt;I66,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N63" s="63" t="str">
-        <f>IF(M63="multiply",PROPER(B63)&amp;PROPER(C63),J62)</f>
-        <v>Ft3Gluk</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="18">
-      <c r="A64" s="76" t="str">
-        <f t="shared" si="24"/>
-        <v>LtoFT3</v>
-      </c>
-      <c r="B64" s="77" t="str">
-        <f t="shared" si="25"/>
+      <c r="N66" s="38" t="str">
+        <f>IF(M66="multiply",PROPER(B66)&amp;PROPER(C66),J67)</f>
+        <v>Ft3L</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="18">
+      <c r="A67" s="51" t="str">
+        <f t="shared" si="30"/>
+        <v>FT3toL</v>
+      </c>
+      <c r="B67" s="52" t="str">
+        <f t="shared" si="31"/>
+        <v>FT3</v>
+      </c>
+      <c r="C67" s="52" t="str">
+        <f t="shared" si="32"/>
         <v>L</v>
       </c>
-      <c r="C64" s="77" t="str">
-        <f t="shared" si="26"/>
-        <v>FT3</v>
-      </c>
-      <c r="D64" s="72" t="s">
-        <v>204</v>
-      </c>
-      <c r="E64" s="73" t="s">
-        <v>212</v>
-      </c>
-      <c r="F64" s="60">
-        <f t="shared" si="1"/>
-        <v>3.5314666721488586E-2</v>
-      </c>
-      <c r="G64" s="62">
-        <f>IF(M64="multiply",F64,F65)</f>
+      <c r="D67" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="F67" s="36">
+        <f t="shared" si="7"/>
         <v>28.316846592000001</v>
       </c>
-      <c r="H64" s="9">
+      <c r="G67" s="38">
+        <f>IF(M67="multiply",F67,F66)</f>
+        <v>28.316846592000001</v>
+      </c>
+      <c r="H67" s="9">
+        <f t="shared" si="33"/>
+        <v>28316.846592000002</v>
+      </c>
+      <c r="I67" s="9">
         <f t="shared" si="27"/>
         <v>1000</v>
       </c>
-      <c r="I64" s="9">
-        <f t="shared" si="21"/>
-        <v>28316.846592000002</v>
-      </c>
-      <c r="J64" t="str">
-        <f t="shared" si="22"/>
-        <v>LFt3</v>
-      </c>
-      <c r="K64" t="str">
-        <f t="shared" si="23"/>
-        <v>constFactorLFt3</v>
-      </c>
-      <c r="M64" s="62" t="str">
-        <f>IF(H64&gt;I64,"multiply","  divide")</f>
-        <v xml:space="preserve">  divide</v>
-      </c>
-      <c r="N64" s="62" t="str">
-        <f>IF(M64="multiply",PROPER(B64)&amp;PROPER(C64),J65)</f>
+      <c r="J67" t="str">
+        <f t="shared" si="28"/>
         <v>Ft3L</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="18">
-      <c r="A65" s="76" t="str">
-        <f t="shared" si="24"/>
-        <v>FT3toL</v>
-      </c>
-      <c r="B65" s="77" t="str">
-        <f t="shared" si="25"/>
-        <v>FT3</v>
-      </c>
-      <c r="C65" s="77" t="str">
-        <f t="shared" si="26"/>
+      <c r="K67" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorFt3L</v>
+      </c>
+      <c r="M67" s="38" t="str">
+        <f>IF(M66="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N67" s="38" t="str">
+        <f>IF(M67="multiply",PROPER(B67)&amp;PROPER(C67),J66)</f>
+        <v>Ft3L</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="18">
+      <c r="A68" s="51" t="str">
+        <f t="shared" si="30"/>
+        <v>LtoQTUS</v>
+      </c>
+      <c r="B68" s="52" t="str">
+        <f t="shared" si="31"/>
         <v>L</v>
       </c>
-      <c r="D65" s="72" t="s">
-        <v>205</v>
-      </c>
-      <c r="E65" s="73" t="s">
-        <v>213</v>
-      </c>
-      <c r="F65" s="60">
-        <f t="shared" si="1"/>
-        <v>28.316846592000001</v>
-      </c>
-      <c r="G65" s="62">
-        <f>IF(M65="multiply",F65,F64)</f>
-        <v>28.316846592000001</v>
-      </c>
-      <c r="H65" s="9">
+      <c r="C68" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>QTUS</v>
+      </c>
+      <c r="D68" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="E68" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="F68" s="36">
+        <f t="shared" si="7"/>
+        <v>1.0566882094325938</v>
+      </c>
+      <c r="G68" s="39">
+        <f>IF(M68="multiply",F68,F69)</f>
+        <v>1.0566882094325938</v>
+      </c>
+      <c r="H68" s="9">
+        <f t="shared" si="33"/>
+        <v>1000</v>
+      </c>
+      <c r="I68" s="9">
         <f t="shared" si="27"/>
-        <v>28316.846592000002</v>
-      </c>
-      <c r="I65" s="9">
-        <f t="shared" si="21"/>
-        <v>1000</v>
-      </c>
-      <c r="J65" t="str">
-        <f t="shared" si="22"/>
-        <v>Ft3L</v>
-      </c>
-      <c r="K65" t="str">
-        <f t="shared" si="23"/>
-        <v>constFactorFt3L</v>
-      </c>
-      <c r="M65" s="62" t="str">
-        <f>IF(M64="multiply","  divide","multiply")</f>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="28"/>
+        <v>LQtus</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorLQtus</v>
+      </c>
+      <c r="M68" s="39" t="str">
+        <f>IF(H68&gt;I68,"multiply","  divide")</f>
         <v>multiply</v>
       </c>
-      <c r="N65" s="62" t="str">
-        <f>IF(M65="multiply",PROPER(B65)&amp;PROPER(C65),J64)</f>
-        <v>Ft3L</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="18">
-      <c r="A66" s="76" t="str">
-        <f t="shared" si="24"/>
-        <v>LtoQTUS</v>
-      </c>
-      <c r="B66" s="77" t="str">
-        <f t="shared" si="25"/>
+      <c r="N68" s="39" t="str">
+        <f>IF(M68="multiply",PROPER(B68)&amp;PROPER(C68),J69)</f>
+        <v>LQtus</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="19" thickBot="1">
+      <c r="A69" s="51" t="str">
+        <f t="shared" si="30"/>
+        <v>QTUStoL</v>
+      </c>
+      <c r="B69" s="52" t="str">
+        <f t="shared" si="31"/>
+        <v>QTUS</v>
+      </c>
+      <c r="C69" s="52" t="str">
+        <f t="shared" si="32"/>
         <v>L</v>
       </c>
-      <c r="C66" s="77" t="str">
-        <f t="shared" si="26"/>
-        <v>QTUS</v>
-      </c>
-      <c r="D66" s="72" t="s">
-        <v>206</v>
-      </c>
-      <c r="E66" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="F66" s="60">
-        <f t="shared" si="1"/>
+      <c r="D69" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E69" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="F69" s="36">
+        <f t="shared" si="7"/>
+        <v>0.94635294599999997</v>
+      </c>
+      <c r="G69" s="39">
+        <f>IF(M69="multiply",F69,F68)</f>
         <v>1.0566882094325938</v>
       </c>
-      <c r="G66" s="63">
-        <f>IF(M66="multiply",F66,F67)</f>
-        <v>1.0566882094325938</v>
-      </c>
-      <c r="H66" s="9">
+      <c r="H69" s="9">
+        <f t="shared" si="33"/>
+        <v>946.35294599999997</v>
+      </c>
+      <c r="I69" s="9">
         <f t="shared" si="27"/>
         <v>1000</v>
       </c>
-      <c r="I66" s="9">
-        <f t="shared" si="21"/>
-        <v>946.35294599999997</v>
-      </c>
-      <c r="J66" t="str">
-        <f t="shared" si="22"/>
-        <v>LQtus</v>
-      </c>
-      <c r="K66" t="str">
-        <f t="shared" si="23"/>
-        <v>constFactorLQtus</v>
-      </c>
-      <c r="M66" s="63" t="str">
-        <f>IF(H66&gt;I66,"multiply","  divide")</f>
-        <v>multiply</v>
-      </c>
-      <c r="N66" s="63" t="str">
-        <f>IF(M66="multiply",PROPER(B66)&amp;PROPER(C66),J67)</f>
-        <v>LQtus</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="19" thickBot="1">
-      <c r="A67" s="76" t="str">
-        <f t="shared" si="24"/>
-        <v>QTUStoL</v>
-      </c>
-      <c r="B67" s="77" t="str">
-        <f t="shared" si="25"/>
-        <v>QTUS</v>
-      </c>
-      <c r="C67" s="77" t="str">
-        <f t="shared" si="26"/>
-        <v>L</v>
-      </c>
-      <c r="D67" s="74" t="s">
-        <v>207</v>
-      </c>
-      <c r="E67" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="F67" s="60">
-        <f t="shared" si="1"/>
-        <v>0.94635294599999997</v>
-      </c>
-      <c r="G67" s="63">
-        <f>IF(M67="multiply",F67,F66)</f>
-        <v>1.0566882094325938</v>
-      </c>
-      <c r="H67" s="9">
-        <f t="shared" si="27"/>
-        <v>946.35294599999997</v>
-      </c>
-      <c r="I67" s="9">
-        <f t="shared" si="21"/>
-        <v>1000</v>
-      </c>
-      <c r="J67" t="str">
-        <f t="shared" si="22"/>
+      <c r="J69" t="str">
+        <f t="shared" si="28"/>
         <v>QtusL</v>
       </c>
-      <c r="K67" t="str">
-        <f t="shared" si="23"/>
+      <c r="K69" t="str">
+        <f t="shared" si="29"/>
         <v>constFactorQtusL</v>
       </c>
-      <c r="M67" s="63" t="str">
-        <f>IF(M66="multiply","  divide","multiply")</f>
+      <c r="M69" s="39" t="str">
+        <f>IF(M68="multiply","  divide","multiply")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N67" s="63" t="str">
-        <f>IF(M67="multiply",PROPER(B67)&amp;PROPER(C67),J66)</f>
+      <c r="N69" s="39" t="str">
+        <f>IF(M69="multiply",PROPER(B69)&amp;PROPER(C69),J68)</f>
         <v>LQtus</v>
       </c>
     </row>
@@ -6314,6 +6923,154 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32695F14-DF7A-BF44-9CBA-957C747116B4}">
+  <dimension ref="B2:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="76.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="65" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="46">
+      <c r="B3" s="64" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" ht="46">
+      <c r="B4" s="64" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="66" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="20">
+      <c r="B12" s="57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="51">
+      <c r="B19" s="67" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5705588-DD07-C34D-9121-E2F0B7E47917}">
+  <dimension ref="C1:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="2" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="66.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:4">
+      <c r="C1" s="68" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4">
+      <c r="C4" s="66" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4">
+      <c r="C5" s="66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4">
+      <c r="C8" s="66" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4">
+      <c r="C9" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4">
+      <c r="C12" s="68" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" ht="119">
+      <c r="C13" s="63" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4">
+      <c r="C15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4">
+      <c r="C16" s="66" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="68" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="66" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF49E5-C5CF-EF45-BD21-7588D88F54A2}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -6327,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6335,7 +7092,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6343,7 +7100,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6351,7 +7108,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6359,7 +7116,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6367,7 +7124,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6375,7 +7132,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6383,7 +7140,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6391,7 +7148,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6399,7 +7156,7 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6407,7 +7164,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6415,7 +7172,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6423,7 +7180,7 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6431,7 +7188,7 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6439,7 +7196,7 @@
         <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6447,7 +7204,7 @@
         <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6455,7 +7212,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6463,7 +7220,7 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6471,7 +7228,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6479,7 +7236,7 @@
         <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6487,7 +7244,7 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6495,7 +7252,7 @@
         <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6503,7 +7260,7 @@
         <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6511,7 +7268,7 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -6519,7 +7276,7 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -6527,7 +7284,7 @@
         <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6535,7 +7292,7 @@
         <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -6543,7 +7300,7 @@
         <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -6551,7 +7308,7 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -6559,7 +7316,7 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -6567,7 +7324,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6575,7 +7332,7 @@
         <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6583,95 +7340,95 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="18">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="69" t="s">
-        <v>208</v>
+        <v>202</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="18">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>229</v>
-      </c>
-      <c r="C37" s="69" t="s">
-        <v>209</v>
+        <v>211</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
-      </c>
-      <c r="C38" s="69" t="s">
-        <v>210</v>
+        <v>209</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="18">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>228</v>
-      </c>
-      <c r="C39" s="69" t="s">
-        <v>211</v>
+        <v>210</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="18">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
-      </c>
-      <c r="C40" s="69" t="s">
-        <v>212</v>
+        <v>203</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>219</v>
-      </c>
-      <c r="C41" s="69" t="s">
-        <v>213</v>
+        <v>204</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="18">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
-      </c>
-      <c r="C42" s="69" t="s">
-        <v>214</v>
+        <v>205</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="18">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
-      </c>
-      <c r="C43" s="69" t="s">
-        <v>215</v>
+        <v>206</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14D795B-DB59-2B4E-9AA5-C58D6E9605F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C17E99C-2B47-CF48-8EA2-F06D21EC4DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="20500" activeTab="1" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="270">
   <si>
     <t>ITM_PINTLQtoML</t>
   </si>
@@ -985,6 +985,30 @@
   <si>
     <t>"ml" STD_RIGHT_ARROW "qt" STD_UK</t>
   </si>
+  <si>
+    <t>ITM_GLUKtoFZUK</t>
+  </si>
+  <si>
+    <t>ITM_FZUKtoGLUK</t>
+  </si>
+  <si>
+    <t>ITM_GLUStoFZUS</t>
+  </si>
+  <si>
+    <t>ITM_FZUStoGLUS</t>
+  </si>
+  <si>
+    <t>"gal" STD_UK STD_RIGHT_ARROW "floz" STD_UK</t>
+  </si>
+  <si>
+    <t>"floz" STD_UK STD_RIGHT_ARROW "gal" STD_UK</t>
+  </si>
+  <si>
+    <t>"gal" STD_US STD_RIGHT_ARROW "floz" STD_US</t>
+  </si>
+  <si>
+    <t>"floz" STD_US STD_RIGHT_ARROW "gal" STD_US</t>
+  </si>
 </sst>
 </file>
 
@@ -998,9 +1022,9 @@
     <numFmt numFmtId="168" formatCode="0.0000000"/>
     <numFmt numFmtId="169" formatCode="0.00000000000"/>
     <numFmt numFmtId="170" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000000000"/>
+    <numFmt numFmtId="171" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1179,8 +1203,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="C47__StandardFont StandardFont"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1280,6 +1323,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1466,7 +1515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1580,9 +1629,6 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1679,7 +1725,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="10" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1689,6 +1735,16 @@
     <xf numFmtId="0" fontId="28" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2023,16 +2079,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8086E2D2-A619-CD41-963B-CA5F79ED1F95}">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="7" width="10.5" style="53" customWidth="1"/>
+    <col min="5" max="7" width="10.5" style="52" customWidth="1"/>
     <col min="8" max="8" width="225" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="5.83203125" style="53" customWidth="1"/>
+    <col min="9" max="11" width="5.83203125" style="52" customWidth="1"/>
     <col min="12" max="12" width="144.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2040,7 +2096,7 @@
     <row r="1" spans="1:14" ht="16">
       <c r="A1"/>
       <c r="B1"/>
-      <c r="F1" s="53">
+      <c r="F1" s="52">
         <f>LEN(F24)</f>
         <v>57</v>
       </c>
@@ -2065,25 +2121,25 @@
       <c r="D3" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="G3" s="54" t="s">
+      <c r="G3" s="53" t="s">
         <v>184</v>
       </c>
       <c r="H3" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="J3" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="K3" s="54" t="s">
+      <c r="K3" s="53" t="s">
         <v>184</v>
       </c>
       <c r="L3" s="33" t="s">
@@ -2100,22 +2156,22 @@
       <c r="B4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="91" t="s">
+      <c r="C4" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D4" s="40" t="str">
         <f>VLOOKUP(A4,Factors!D:K,8,0)</f>
         <v>constFactorCupcFzus</v>
       </c>
-      <c r="E4" s="53" t="str">
+      <c r="E4" s="52" t="str">
         <f>VLOOKUP(A4,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F4" s="55" t="str">
-        <f t="shared" ref="F4:F43" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
+      <c r="F4" s="54" t="str">
+        <f t="shared" ref="F4:F47" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G4" s="55" t="str">
+      <c r="G4" s="54" t="str">
         <f>MID(F4,1,SEARCH("STD_RIGHT_ARROW",F4)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
@@ -2123,15 +2179,15 @@
         <f>"/* NNNN */  UNIT_CONV("&amp;D4&amp;","&amp;REPT(CHAR(32),21-LEN(D4))&amp;"    "&amp;E4&amp;",      "&amp;F4&amp;","&amp;REPT(CHAR(32),60-LEN(F4))&amp;G4&amp;REPT(CHAR(32),60-LEN(G4))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcFzus,      multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="55">
         <f>VLOOKUP(A4,Factors!D:G,4,0)</f>
         <v>8</v>
       </c>
-      <c r="J4" s="53" t="str">
+      <c r="J4" s="52" t="str">
         <f>SUBSTITUTE(TEXT(I4,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>8.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K4" s="56" t="str">
+      <c r="K4" s="55" t="str">
         <f>VLOOKUP(A4,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
@@ -2151,47 +2207,47 @@
       <c r="B5" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="91" t="s">
+      <c r="C5" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>VLOOKUP(A5,Factors!D:K,8,0)</f>
         <v>constFactorCupcMl</v>
       </c>
-      <c r="E5" s="53" t="str">
+      <c r="E5" s="52" t="str">
         <f>VLOOKUP(A5,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F5" s="55" t="str">
+      <c r="F5" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G5" s="55" t="str">
-        <f t="shared" ref="G5:G43" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
+      <c r="G5" s="54" t="str">
+        <f t="shared" ref="G5:G47" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
       <c r="H5" s="30" t="str">
-        <f t="shared" ref="H5:H43" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
+        <f t="shared" ref="H5:H47" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcMl,        multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I5" s="53">
+      <c r="I5" s="52">
         <f>VLOOKUP(A5,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J5" s="53" t="str">
-        <f t="shared" ref="J5:J43" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+      <c r="J5" s="52" t="str">
+        <f t="shared" ref="J5:J47" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K5" s="56" t="str">
+      <c r="K5" s="55" t="str">
         <f>VLOOKUP(A5,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
       <c r="L5" s="31" t="str">
-        <f t="shared" ref="L5:L43" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
+        <f t="shared" ref="L5:L47" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("CupcMl",        "+2.365882365000000000000000000000000000000000000000000000e+02");</v>
       </c>
       <c r="N5" s="41" t="str">
-        <f t="shared" ref="N5:N43" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
+        <f t="shared" ref="N5:N47" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcMl] = &amp;const_CupcMl,</v>
       </c>
     </row>
@@ -2202,22 +2258,22 @@
       <c r="B6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>VLOOKUP(A6,Factors!D:K,8,0)</f>
         <v>constFactorCupukFzuk</v>
       </c>
-      <c r="E6" s="53" t="str">
+      <c r="E6" s="52" t="str">
         <f>VLOOKUP(A6,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F6" s="55" t="str">
+      <c r="F6" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G6" s="55" t="str">
+      <c r="G6" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -2225,15 +2281,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukFzuk,     multiply,      "cup" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="52">
         <f>VLOOKUP(A6,Factors!D:G,4,0)</f>
         <v>10</v>
       </c>
-      <c r="J6" s="53" t="str">
+      <c r="J6" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.000000000000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K6" s="56" t="str">
+      <c r="K6" s="55" t="str">
         <f>VLOOKUP(A6,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
@@ -2253,22 +2309,22 @@
       <c r="B7" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>VLOOKUP(A7,Factors!D:K,8,0)</f>
         <v>constFactorCupukMl</v>
       </c>
-      <c r="E7" s="53" t="str">
+      <c r="E7" s="52" t="str">
         <f>VLOOKUP(A7,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F7" s="55" t="str">
+      <c r="F7" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G7" s="55" t="str">
+      <c r="G7" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"cup" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -2276,15 +2332,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorCupukMl,       multiply,      "cup" STD_UK STD_RIGHT_ARROW "ml",                           "cup" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="52">
         <f>VLOOKUP(A7,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J7" s="53" t="str">
+      <c r="J7" s="52" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K7" s="56" t="str">
+      <c r="K7" s="55" t="str">
         <f>VLOOKUP(A7,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
@@ -2304,22 +2360,22 @@
       <c r="B8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D8" s="40" t="str">
         <f>VLOOKUP(A8,Factors!D:K,8,0)</f>
         <v>constFactorFzukCupuk</v>
       </c>
-      <c r="E8" s="53" t="str">
+      <c r="E8" s="52" t="str">
         <f>VLOOKUP(A8,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F8" s="55" t="str">
+      <c r="F8" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G8" s="55" t="str">
+      <c r="G8" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -2327,15 +2383,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukCupuk,       divide,      "floz" STD_UK STD_RIGHT_ARROW "cup" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="52">
         <f>VLOOKUP(A8,Factors!D:G,4,0)</f>
         <v>10</v>
       </c>
-      <c r="J8" s="53" t="str">
+      <c r="J8" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.000000000000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K8" s="56" t="str">
+      <c r="K8" s="55" t="str">
         <f>VLOOKUP(A8,Factors!D:N,11,0)</f>
         <v>CupukFzuk</v>
       </c>
@@ -2355,22 +2411,22 @@
       <c r="B9" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="91" t="s">
+      <c r="C9" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D9" s="40" t="str">
         <f>VLOOKUP(A9,Factors!D:K,8,0)</f>
         <v>constFactorFzukTbspuk</v>
       </c>
-      <c r="E9" s="53" t="str">
+      <c r="E9" s="52" t="str">
         <f>VLOOKUP(A9,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F9" s="55" t="str">
+      <c r="F9" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G9" s="55" t="str">
+      <c r="G9" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -2378,15 +2434,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTbspuk,    multiply,      "floz" STD_UK STD_RIGHT_ARROW "Tbsp" STD_UK,                 "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="52">
         <f>VLOOKUP(A9,Factors!D:G,4,0)</f>
         <v>1.6</v>
       </c>
-      <c r="J9" s="53" t="str">
+      <c r="J9" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.600000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K9" s="56" t="str">
+      <c r="K9" s="55" t="str">
         <f>VLOOKUP(A9,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
@@ -2406,22 +2462,22 @@
       <c r="B10" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D10" s="40" t="str">
         <f>VLOOKUP(A10,Factors!D:K,8,0)</f>
         <v>constFactorFzukTspuk</v>
       </c>
-      <c r="E10" s="53" t="str">
+      <c r="E10" s="52" t="str">
         <f>VLOOKUP(A10,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F10" s="55" t="str">
+      <c r="F10" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G10" s="55" t="str">
+      <c r="G10" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -2429,15 +2485,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzukTspuk,     multiply,      "floz" STD_UK STD_RIGHT_ARROW "tsp" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I10" s="53">
+      <c r="I10" s="52">
         <f>VLOOKUP(A10,Factors!D:G,4,0)</f>
         <v>4.8</v>
       </c>
-      <c r="J10" s="53" t="str">
+      <c r="J10" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.800000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K10" s="56" t="str">
+      <c r="K10" s="55" t="str">
         <f>VLOOKUP(A10,Factors!D:N,11,0)</f>
         <v>FzukTspuk</v>
       </c>
@@ -2457,22 +2513,22 @@
       <c r="B11" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="40" t="str">
         <f>VLOOKUP(A11,Factors!D:K,8,0)</f>
         <v>constFactorFzusCupc</v>
       </c>
-      <c r="E11" s="53" t="str">
+      <c r="E11" s="52" t="str">
         <f>VLOOKUP(A11,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F11" s="55" t="str">
+      <c r="F11" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G11" s="55" t="str">
+      <c r="G11" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
@@ -2480,15 +2536,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusCupc,        divide,      "floz" STD_US STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="52">
         <f>VLOOKUP(A11,Factors!D:G,4,0)</f>
         <v>8</v>
       </c>
-      <c r="J11" s="53" t="str">
+      <c r="J11" s="52" t="str">
         <f t="shared" si="3"/>
         <v>8.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K11" s="56" t="str">
+      <c r="K11" s="55" t="str">
         <f>VLOOKUP(A11,Factors!D:N,11,0)</f>
         <v>CupcFzus</v>
       </c>
@@ -2508,22 +2564,22 @@
       <c r="B12" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D12" s="40" t="str">
         <f>VLOOKUP(A12,Factors!D:K,8,0)</f>
         <v>constFactorFzusTbspc</v>
       </c>
-      <c r="E12" s="53" t="str">
+      <c r="E12" s="52" t="str">
         <f>VLOOKUP(A12,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F12" s="55" t="str">
+      <c r="F12" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G12" s="55" t="str">
+      <c r="G12" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
@@ -2531,15 +2587,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTbspc,     multiply,      "floz" STD_US STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,       "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I12" s="53">
+      <c r="I12" s="52">
         <f>VLOOKUP(A12,Factors!D:G,4,0)</f>
         <v>2</v>
       </c>
-      <c r="J12" s="53" t="str">
+      <c r="J12" s="52" t="str">
         <f t="shared" si="3"/>
         <v>2.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K12" s="56" t="str">
+      <c r="K12" s="55" t="str">
         <f>VLOOKUP(A12,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
@@ -2559,22 +2615,22 @@
       <c r="B13" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D13" s="40" t="str">
         <f>VLOOKUP(A13,Factors!D:K,8,0)</f>
         <v>constFactorFzusTspc</v>
       </c>
-      <c r="E13" s="53" t="str">
+      <c r="E13" s="52" t="str">
         <f>VLOOKUP(A13,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F13" s="55" t="str">
+      <c r="F13" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G13" s="55" t="str">
+      <c r="G13" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
@@ -2582,15 +2638,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusTspc,      multiply,      "floz" STD_US STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,        "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I13" s="53">
+      <c r="I13" s="52">
         <f>VLOOKUP(A13,Factors!D:G,4,0)</f>
         <v>6</v>
       </c>
-      <c r="J13" s="53" t="str">
+      <c r="J13" s="52" t="str">
         <f t="shared" si="3"/>
         <v>6.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K13" s="56" t="str">
+      <c r="K13" s="55" t="str">
         <f>VLOOKUP(A13,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
@@ -2610,22 +2666,22 @@
       <c r="B14" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D14" s="40" t="str">
         <f>VLOOKUP(A14,Factors!D:K,8,0)</f>
         <v>constFactorMlCupc</v>
       </c>
-      <c r="E14" s="53" t="str">
+      <c r="E14" s="52" t="str">
         <f>VLOOKUP(A14,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F14" s="55" t="str">
+      <c r="F14" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c</v>
       </c>
-      <c r="G14" s="55" t="str">
+      <c r="G14" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2633,15 +2689,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupc,          divide,      "ml" STD_RIGHT_ARROW "cup" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="52">
         <f>VLOOKUP(A14,Factors!D:G,4,0)</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="J14" s="53" t="str">
+      <c r="J14" s="52" t="str">
         <f t="shared" si="3"/>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K14" s="56" t="str">
+      <c r="K14" s="55" t="str">
         <f>VLOOKUP(A14,Factors!D:N,11,0)</f>
         <v>CupcMl</v>
       </c>
@@ -2661,22 +2717,22 @@
       <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D15" s="40" t="str">
         <f>VLOOKUP(A15,Factors!D:K,8,0)</f>
         <v>constFactorMlCupuk</v>
       </c>
-      <c r="E15" s="53" t="str">
+      <c r="E15" s="52" t="str">
         <f>VLOOKUP(A15,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F15" s="55" t="str">
+      <c r="F15" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "cup" STD_UK</v>
       </c>
-      <c r="G15" s="55" t="str">
+      <c r="G15" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2684,15 +2740,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlCupuk,         divide,      "ml" STD_RIGHT_ARROW "cup" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I15" s="53">
+      <c r="I15" s="52">
         <f>VLOOKUP(A15,Factors!D:G,4,0)</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="J15" s="53" t="str">
+      <c r="J15" s="52" t="str">
         <f t="shared" si="3"/>
         <v>2.841306250000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K15" s="56" t="str">
+      <c r="K15" s="55" t="str">
         <f>VLOOKUP(A15,Factors!D:N,11,0)</f>
         <v>CupukMl</v>
       </c>
@@ -2712,22 +2768,22 @@
       <c r="B16" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D16" s="40" t="str">
         <f>VLOOKUP(A16,Factors!D:K,8,0)</f>
         <v>constFactorMlPintlq</v>
       </c>
-      <c r="E16" s="53" t="str">
+      <c r="E16" s="52" t="str">
         <f>VLOOKUP(A16,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F16" s="55" t="str">
+      <c r="F16" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q</v>
       </c>
-      <c r="G16" s="55" t="str">
+      <c r="G16" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2735,15 +2791,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintlq,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_SUB_l STD_SUB_i STD_SUB_q,   "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I16" s="53">
+      <c r="I16" s="52">
         <f>VLOOKUP(A16,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J16" s="53" t="str">
+      <c r="J16" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K16" s="56" t="str">
+      <c r="K16" s="55" t="str">
         <f>VLOOKUP(A16,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
@@ -2763,22 +2819,22 @@
       <c r="B17" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D17" s="40" t="str">
         <f>VLOOKUP(A17,Factors!D:K,8,0)</f>
         <v>constFactorMlPintuk</v>
       </c>
-      <c r="E17" s="53" t="str">
+      <c r="E17" s="52" t="str">
         <f>VLOOKUP(A17,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F17" s="55" t="str">
+      <c r="F17" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "pint" STD_UK</v>
       </c>
-      <c r="G17" s="55" t="str">
+      <c r="G17" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2786,15 +2842,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlPintuk,        divide,      "ml" STD_RIGHT_ARROW "pint" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I17" s="53">
+      <c r="I17" s="52">
         <f>VLOOKUP(A17,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J17" s="53" t="str">
+      <c r="J17" s="52" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K17" s="56" t="str">
+      <c r="K17" s="55" t="str">
         <f>VLOOKUP(A17,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
@@ -2814,22 +2870,22 @@
       <c r="B18" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D18" s="40" t="str">
         <f>VLOOKUP(A18,Factors!D:K,8,0)</f>
         <v>constFactorMlQt</v>
       </c>
-      <c r="E18" s="53" t="str">
+      <c r="E18" s="52" t="str">
         <f>VLOOKUP(A18,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F18" s="55" t="str">
+      <c r="F18" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "qt" STD_UK</v>
       </c>
-      <c r="G18" s="55" t="str">
+      <c r="G18" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2837,15 +2893,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlQt,            divide,      "ml" STD_RIGHT_ARROW "qt" STD_UK,                            "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="52">
         <f>VLOOKUP(A18,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J18" s="53" t="str">
+      <c r="J18" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K18" s="56" t="str">
+      <c r="K18" s="55" t="str">
         <f>VLOOKUP(A18,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
@@ -2865,22 +2921,22 @@
       <c r="B19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="40" t="str">
         <f>VLOOKUP(A19,Factors!D:K,8,0)</f>
         <v>constFactorMlQtus</v>
       </c>
-      <c r="E19" s="53" t="str">
+      <c r="E19" s="52" t="str">
         <f>VLOOKUP(A19,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F19" s="55" t="str">
+      <c r="F19" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "qt" STD_US</v>
       </c>
-      <c r="G19" s="55" t="str">
+      <c r="G19" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2888,15 +2944,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlQtus,          divide,      "ml" STD_RIGHT_ARROW "qt" STD_US,                            "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I19" s="53">
+      <c r="I19" s="52">
         <f>VLOOKUP(A19,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J19" s="53" t="str">
+      <c r="J19" s="52" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K19" s="56" t="str">
+      <c r="K19" s="55" t="str">
         <f>VLOOKUP(A19,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
@@ -2916,22 +2972,22 @@
       <c r="B20" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="91" t="s">
+      <c r="C20" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="40" t="str">
         <f>VLOOKUP(A20,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspc</v>
       </c>
-      <c r="E20" s="53" t="str">
+      <c r="E20" s="52" t="str">
         <f>VLOOKUP(A20,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F20" s="55" t="str">
+      <c r="F20" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G20" s="55" t="str">
+      <c r="G20" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2939,15 +2995,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspc,         divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_US STD_SUB_c,                "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I20" s="53">
+      <c r="I20" s="52">
         <f>VLOOKUP(A20,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J20" s="53" t="str">
+      <c r="J20" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K20" s="56" t="str">
+      <c r="K20" s="55" t="str">
         <f>VLOOKUP(A20,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
@@ -2967,22 +3023,22 @@
       <c r="B21" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D21" s="40" t="str">
         <f>VLOOKUP(A21,Factors!D:K,8,0)</f>
         <v>constFactorMlTbspuk</v>
       </c>
-      <c r="E21" s="53" t="str">
+      <c r="E21" s="52" t="str">
         <f>VLOOKUP(A21,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F21" s="55" t="str">
+      <c r="F21" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "Tbsp" STD_UK</v>
       </c>
-      <c r="G21" s="55" t="str">
+      <c r="G21" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -2990,15 +3046,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTbspuk,        divide,      "ml" STD_RIGHT_ARROW "Tbsp" STD_UK,                          "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I21" s="53">
+      <c r="I21" s="52">
         <f>VLOOKUP(A21,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J21" s="53" t="str">
+      <c r="J21" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K21" s="56" t="str">
+      <c r="K21" s="55" t="str">
         <f>VLOOKUP(A21,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
@@ -3018,22 +3074,22 @@
       <c r="B22" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="91" t="s">
+      <c r="C22" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D22" s="40" t="str">
         <f>VLOOKUP(A22,Factors!D:K,8,0)</f>
         <v>constFactorMlTspc</v>
       </c>
-      <c r="E22" s="53" t="str">
+      <c r="E22" s="52" t="str">
         <f>VLOOKUP(A22,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F22" s="55" t="str">
+      <c r="F22" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c</v>
       </c>
-      <c r="G22" s="55" t="str">
+      <c r="G22" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -3041,15 +3097,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspc,          divide,      "ml" STD_RIGHT_ARROW "tsp" STD_US STD_SUB_c,                 "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I22" s="53">
+      <c r="I22" s="52">
         <f>VLOOKUP(A22,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J22" s="53" t="str">
+      <c r="J22" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K22" s="56" t="str">
+      <c r="K22" s="55" t="str">
         <f>VLOOKUP(A22,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
@@ -3069,22 +3125,22 @@
       <c r="B23" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="91" t="s">
+      <c r="C23" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D23" s="40" t="str">
         <f>VLOOKUP(A23,Factors!D:K,8,0)</f>
         <v>constFactorMlTspuk</v>
       </c>
-      <c r="E23" s="53" t="str">
+      <c r="E23" s="52" t="str">
         <f>VLOOKUP(A23,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F23" s="55" t="str">
+      <c r="F23" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"ml" STD_RIGHT_ARROW "tsp" STD_UK</v>
       </c>
-      <c r="G23" s="55" t="str">
+      <c r="G23" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"ml" STD_RIGHT_ARROW</v>
       </c>
@@ -3092,15 +3148,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlTspuk,         divide,      "ml" STD_RIGHT_ARROW "tsp" STD_UK,                           "ml" STD_RIGHT_ARROW                                        ),</v>
       </c>
-      <c r="I23" s="53">
+      <c r="I23" s="52">
         <f>VLOOKUP(A23,Factors!D:G,4,0)</f>
         <v>5.9193880208333338</v>
       </c>
-      <c r="J23" s="53" t="str">
+      <c r="J23" s="52" t="str">
         <f t="shared" si="3"/>
         <v>5.919388020833330000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K23" s="56" t="str">
+      <c r="K23" s="55" t="str">
         <f>VLOOKUP(A23,Factors!D:N,11,0)</f>
         <v>TspukMl</v>
       </c>
@@ -3120,22 +3176,22 @@
       <c r="B24" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="91" t="s">
+      <c r="C24" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D24" s="40" t="str">
         <f>VLOOKUP(A24,Factors!D:K,8,0)</f>
         <v>constFactorPintlqMl</v>
       </c>
-      <c r="E24" s="53" t="str">
+      <c r="E24" s="52" t="str">
         <f>VLOOKUP(A24,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F24" s="55" t="str">
+      <c r="F24" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G24" s="55" t="str">
+      <c r="G24" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW</v>
       </c>
@@ -3143,15 +3199,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintlqMl,      multiply,      "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW "ml",   "pint" STD_SUB_l STD_SUB_i STD_SUB_q STD_RIGHT_ARROW        ),</v>
       </c>
-      <c r="I24" s="53">
+      <c r="I24" s="52">
         <f>VLOOKUP(A24,Factors!D:G,4,0)</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="J24" s="53" t="str">
+      <c r="J24" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.731764730000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K24" s="56" t="str">
+      <c r="K24" s="55" t="str">
         <f>VLOOKUP(A24,Factors!D:N,11,0)</f>
         <v>PintlqMl</v>
       </c>
@@ -3171,22 +3227,22 @@
       <c r="B25" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D25" s="40" t="str">
         <f>VLOOKUP(A25,Factors!D:K,8,0)</f>
         <v>constFactorPintukMl</v>
       </c>
-      <c r="E25" s="53" t="str">
+      <c r="E25" s="52" t="str">
         <f>VLOOKUP(A25,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F25" s="55" t="str">
+      <c r="F25" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G25" s="55" t="str">
+      <c r="G25" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"pint" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3194,15 +3250,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorPintukMl,      multiply,      "pint" STD_UK STD_RIGHT_ARROW "ml",                          "pint" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I25" s="53">
+      <c r="I25" s="52">
         <f>VLOOKUP(A25,Factors!D:G,4,0)</f>
         <v>568.26125000000002</v>
       </c>
-      <c r="J25" s="53" t="str">
+      <c r="J25" s="52" t="str">
         <f t="shared" si="3"/>
         <v>5.682612500000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K25" s="56" t="str">
+      <c r="K25" s="55" t="str">
         <f>VLOOKUP(A25,Factors!D:N,11,0)</f>
         <v>PintukMl</v>
       </c>
@@ -3222,22 +3278,22 @@
       <c r="B26" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D26" s="40" t="str">
         <f>VLOOKUP(A26,Factors!D:K,8,0)</f>
         <v>constFactorQtMl</v>
       </c>
-      <c r="E26" s="53" t="str">
+      <c r="E26" s="52" t="str">
         <f>VLOOKUP(A26,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F26" s="55" t="str">
+      <c r="F26" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"qt" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G26" s="55" t="str">
+      <c r="G26" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"qt" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3245,15 +3301,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtMl,          multiply,      "qt" STD_UK STD_RIGHT_ARROW "ml",                            "qt" STD_UK STD_RIGHT_ARROW                                 ),</v>
       </c>
-      <c r="I26" s="53">
+      <c r="I26" s="52">
         <f>VLOOKUP(A26,Factors!D:G,4,0)</f>
         <v>1136.5225</v>
       </c>
-      <c r="J26" s="53" t="str">
+      <c r="J26" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.136522500000000000000000000000000000000000000000000000e+03</v>
       </c>
-      <c r="K26" s="56" t="str">
+      <c r="K26" s="55" t="str">
         <f>VLOOKUP(A26,Factors!D:N,11,0)</f>
         <v>QtMl</v>
       </c>
@@ -3273,22 +3329,22 @@
       <c r="B27" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="91" t="s">
+      <c r="C27" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D27" s="40" t="str">
         <f>VLOOKUP(A27,Factors!D:K,8,0)</f>
         <v>constFactorQtusMl</v>
       </c>
-      <c r="E27" s="53" t="str">
+      <c r="E27" s="52" t="str">
         <f>VLOOKUP(A27,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F27" s="55" t="str">
+      <c r="F27" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"qt" STD_US STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G27" s="55" t="str">
+      <c r="G27" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"qt" STD_US STD_RIGHT_ARROW</v>
       </c>
@@ -3296,15 +3352,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtusMl,        multiply,      "qt" STD_US STD_RIGHT_ARROW "ml",                            "qt" STD_US STD_RIGHT_ARROW                                 ),</v>
       </c>
-      <c r="I27" s="53">
+      <c r="I27" s="52">
         <f>VLOOKUP(A27,Factors!D:G,4,0)</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="J27" s="53" t="str">
+      <c r="J27" s="52" t="str">
         <f t="shared" si="3"/>
         <v>9.463529460000000000000000000000000000000000000000000000e+02</v>
       </c>
-      <c r="K27" s="56" t="str">
+      <c r="K27" s="55" t="str">
         <f>VLOOKUP(A27,Factors!D:N,11,0)</f>
         <v>QtusMl</v>
       </c>
@@ -3324,22 +3380,22 @@
       <c r="B28" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="91" t="s">
+      <c r="C28" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D28" s="40" t="str">
         <f>VLOOKUP(A28,Factors!D:K,8,0)</f>
         <v>constFactorTbspcFzus</v>
       </c>
-      <c r="E28" s="53" t="str">
+      <c r="E28" s="52" t="str">
         <f>VLOOKUP(A28,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F28" s="55" t="str">
+      <c r="F28" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G28" s="55" t="str">
+      <c r="G28" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
@@ -3347,15 +3403,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcFzus,       divide,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,       "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I28" s="53">
+      <c r="I28" s="52">
         <f>VLOOKUP(A28,Factors!D:G,4,0)</f>
         <v>2</v>
       </c>
-      <c r="J28" s="53" t="str">
+      <c r="J28" s="52" t="str">
         <f t="shared" si="3"/>
         <v>2.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K28" s="56" t="str">
+      <c r="K28" s="55" t="str">
         <f>VLOOKUP(A28,Factors!D:N,11,0)</f>
         <v>FzusTbspc</v>
       </c>
@@ -3375,22 +3431,22 @@
       <c r="B29" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="91" t="s">
+      <c r="C29" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D29" s="40" t="str">
         <f>VLOOKUP(A29,Factors!D:K,8,0)</f>
         <v>constFactorTbspcMl</v>
       </c>
-      <c r="E29" s="53" t="str">
+      <c r="E29" s="52" t="str">
         <f>VLOOKUP(A29,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F29" s="55" t="str">
+      <c r="F29" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G29" s="55" t="str">
+      <c r="G29" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
@@ -3398,15 +3454,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspcMl,       multiply,      "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                "Tbsp" STD_US STD_SUB_c STD_RIGHT_ARROW                     ),</v>
       </c>
-      <c r="I29" s="53">
+      <c r="I29" s="52">
         <f>VLOOKUP(A29,Factors!D:G,4,0)</f>
         <v>14.78676478125</v>
       </c>
-      <c r="J29" s="53" t="str">
+      <c r="J29" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.478676478125000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K29" s="56" t="str">
+      <c r="K29" s="55" t="str">
         <f>VLOOKUP(A29,Factors!D:N,11,0)</f>
         <v>TbspcMl</v>
       </c>
@@ -3426,22 +3482,22 @@
       <c r="B30" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="91" t="s">
+      <c r="C30" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="40" t="str">
         <f>VLOOKUP(A30,Factors!D:K,8,0)</f>
         <v>constFactorTbspukFzuk</v>
       </c>
-      <c r="E30" s="53" t="str">
+      <c r="E30" s="52" t="str">
         <f>VLOOKUP(A30,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F30" s="55" t="str">
+      <c r="F30" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G30" s="55" t="str">
+      <c r="G30" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3449,15 +3505,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukFzuk,      divide,      "Tbsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                 "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I30" s="53">
+      <c r="I30" s="52">
         <f>VLOOKUP(A30,Factors!D:G,4,0)</f>
         <v>1.6</v>
       </c>
-      <c r="J30" s="53" t="str">
+      <c r="J30" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.600000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K30" s="56" t="str">
+      <c r="K30" s="55" t="str">
         <f>VLOOKUP(A30,Factors!D:N,11,0)</f>
         <v>FzukTbspuk</v>
       </c>
@@ -3477,22 +3533,22 @@
       <c r="B31" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D31" s="40" t="str">
         <f>VLOOKUP(A31,Factors!D:K,8,0)</f>
         <v>constFactorTbspukMl</v>
       </c>
-      <c r="E31" s="53" t="str">
+      <c r="E31" s="52" t="str">
         <f>VLOOKUP(A31,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F31" s="55" t="str">
+      <c r="F31" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G31" s="55" t="str">
+      <c r="G31" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"Tbsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3500,15 +3556,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTbspukMl,      multiply,      "Tbsp" STD_UK STD_RIGHT_ARROW "ml",                          "Tbsp" STD_UK STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I31" s="53">
+      <c r="I31" s="52">
         <f>VLOOKUP(A31,Factors!D:G,4,0)</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="J31" s="53" t="str">
+      <c r="J31" s="52" t="str">
         <f t="shared" si="3"/>
         <v>1.775816406250000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K31" s="56" t="str">
+      <c r="K31" s="55" t="str">
         <f>VLOOKUP(A31,Factors!D:N,11,0)</f>
         <v>TbspukMl</v>
       </c>
@@ -3528,22 +3584,22 @@
       <c r="B32" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="91" t="s">
+      <c r="C32" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="40" t="str">
         <f>VLOOKUP(A32,Factors!D:K,8,0)</f>
         <v>constFactorTspcFzus</v>
       </c>
-      <c r="E32" s="53" t="str">
+      <c r="E32" s="52" t="str">
         <f>VLOOKUP(A32,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F32" s="55" t="str">
+      <c r="F32" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
-      <c r="G32" s="55" t="str">
+      <c r="G32" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
@@ -3551,15 +3607,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcFzus,        divide,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US,        "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I32" s="53">
+      <c r="I32" s="52">
         <f>VLOOKUP(A32,Factors!D:G,4,0)</f>
         <v>6</v>
       </c>
-      <c r="J32" s="53" t="str">
+      <c r="J32" s="52" t="str">
         <f t="shared" si="3"/>
         <v>6.000000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K32" s="56" t="str">
+      <c r="K32" s="55" t="str">
         <f>VLOOKUP(A32,Factors!D:N,11,0)</f>
         <v>FzusTspc</v>
       </c>
@@ -3579,22 +3635,22 @@
       <c r="B33" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="91" t="s">
+      <c r="C33" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D33" s="40" t="str">
         <f>VLOOKUP(A33,Factors!D:K,8,0)</f>
         <v>constFactorTspcMl</v>
       </c>
-      <c r="E33" s="53" t="str">
+      <c r="E33" s="52" t="str">
         <f>VLOOKUP(A33,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F33" s="55" t="str">
+      <c r="F33" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G33" s="55" t="str">
+      <c r="G33" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
@@ -3602,15 +3658,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspcMl,        multiply,      "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "tsp" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
-      <c r="I33" s="53">
+      <c r="I33" s="52">
         <f>VLOOKUP(A33,Factors!D:G,4,0)</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="J33" s="53" t="str">
+      <c r="J33" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.928921593750000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K33" s="56" t="str">
+      <c r="K33" s="55" t="str">
         <f>VLOOKUP(A33,Factors!D:N,11,0)</f>
         <v>TspcMl</v>
       </c>
@@ -3630,22 +3686,22 @@
       <c r="B34" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D34" s="40" t="str">
         <f>VLOOKUP(A34,Factors!D:K,8,0)</f>
         <v>constFactorTspukFzuk</v>
       </c>
-      <c r="E34" s="53" t="str">
+      <c r="E34" s="52" t="str">
         <f>VLOOKUP(A34,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F34" s="55" t="str">
+      <c r="F34" s="54" t="str">
         <f t="shared" si="0"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
       </c>
-      <c r="G34" s="55" t="str">
+      <c r="G34" s="54" t="str">
         <f t="shared" si="1"/>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3653,15 +3709,15 @@
         <f t="shared" si="2"/>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukFzuk,       divide,      "tsp" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I34" s="53">
+      <c r="I34" s="52">
         <f>VLOOKUP(A34,Factors!D:G,4,0)</f>
         <v>4.8</v>
       </c>
-      <c r="J34" s="53" t="str">
+      <c r="J34" s="52" t="str">
         <f t="shared" si="3"/>
         <v>4.800000000000000000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K34" s="56" t="str">
+      <c r="K34" s="55" t="str">
         <f>VLOOKUP(A34,Factors!D:N,11,0)</f>
         <v>FzukTspuk</v>
       </c>
@@ -3681,47 +3737,47 @@
       <c r="B35" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="91" t="s">
+      <c r="C35" s="90" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="40" t="str">
         <f>VLOOKUP(A35,Factors!D:K,8,0)</f>
         <v>constFactorTspukMl</v>
       </c>
-      <c r="E35" s="53" t="str">
+      <c r="E35" s="52" t="str">
         <f>VLOOKUP(A35,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F35" s="55" t="str">
-        <f t="shared" ref="F35:F42" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
+      <c r="F35" s="54" t="str">
+        <f t="shared" ref="F35:F46" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
-      <c r="G35" s="55" t="str">
-        <f t="shared" ref="G35:G42" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
+      <c r="G35" s="54" t="str">
+        <f t="shared" ref="G35:G46" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
       <c r="H35" s="30" t="str">
-        <f t="shared" ref="H35:H42" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
+        <f t="shared" ref="H35:H46" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I35" s="53">
+      <c r="I35" s="52">
         <f>VLOOKUP(A35,Factors!D:G,4,0)</f>
         <v>5.9193880208333338</v>
       </c>
-      <c r="J35" s="53" t="str">
-        <f t="shared" ref="J35:J42" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+      <c r="J35" s="52" t="str">
+        <f t="shared" ref="J35:J46" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>5.919388020833330000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K35" s="56" t="str">
+      <c r="K35" s="55" t="str">
         <f>VLOOKUP(A35,Factors!D:N,11,0)</f>
         <v>TspukMl</v>
       </c>
       <c r="L35" s="31" t="str">
-        <f t="shared" ref="L35:L42" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
+        <f t="shared" ref="L35:L46" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833330000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N35" s="41" t="str">
-        <f t="shared" ref="N35:N42" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
+        <f t="shared" ref="N35:N46" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
         <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
       </c>
     </row>
@@ -3732,22 +3788,22 @@
       <c r="B36" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="92" t="s">
+      <c r="C36" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D36" s="40" t="str">
         <f>VLOOKUP(A36,Factors!D:K,8,0)</f>
         <v>constFactorMlIn3</v>
       </c>
-      <c r="E36" s="53" t="str">
+      <c r="E36" s="52" t="str">
         <f>VLOOKUP(A36,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F36" s="55" t="str">
+      <c r="F36" s="54" t="str">
         <f t="shared" si="6"/>
         <v>"m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3</v>
       </c>
-      <c r="G36" s="55" t="str">
+      <c r="G36" s="54" t="str">
         <f t="shared" si="7"/>
         <v>"m" STD_litre STD_RIGHT_ARROW</v>
       </c>
@@ -3755,15 +3811,15 @@
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorMlIn3,           divide,      "m" STD_litre STD_RIGHT_ARROW "in" STD_SUP_3,                "m" STD_litre STD_RIGHT_ARROW                               ),</v>
       </c>
-      <c r="I36" s="53">
+      <c r="I36" s="52">
         <f>VLOOKUP(A36,Factors!D:G,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="J36" s="53" t="str">
+      <c r="J36" s="52" t="str">
         <f t="shared" si="9"/>
         <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K36" s="56" t="str">
+      <c r="K36" s="55" t="str">
         <f>VLOOKUP(A36,Factors!D:N,11,0)</f>
         <v>In3Ml</v>
       </c>
@@ -3783,22 +3839,22 @@
       <c r="B37" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="C37" s="92" t="s">
+      <c r="C37" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D37" s="40" t="str">
         <f>VLOOKUP(A37,Factors!D:K,8,0)</f>
         <v>constFactorIn3Ml</v>
       </c>
-      <c r="E37" s="53" t="str">
+      <c r="E37" s="52" t="str">
         <f>VLOOKUP(A37,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F37" s="55" t="str">
+      <c r="F37" s="54" t="str">
         <f t="shared" si="6"/>
         <v>"in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre</v>
       </c>
-      <c r="G37" s="55" t="str">
+      <c r="G37" s="54" t="str">
         <f t="shared" si="7"/>
         <v>"in" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
@@ -3806,15 +3862,15 @@
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorIn3Ml,         multiply,      "in" STD_SUP_3 STD_RIGHT_ARROW "m" STD_litre,                "in" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I37" s="53">
+      <c r="I37" s="52">
         <f>VLOOKUP(A37,Factors!D:G,4,0)</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="J37" s="53" t="str">
+      <c r="J37" s="52" t="str">
         <f t="shared" si="9"/>
         <v>1.638706400000000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K37" s="56" t="str">
+      <c r="K37" s="55" t="str">
         <f>VLOOKUP(A37,Factors!D:N,11,0)</f>
         <v>In3Ml</v>
       </c>
@@ -3834,22 +3890,22 @@
       <c r="B38" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="92" t="s">
+      <c r="C38" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D38" s="40" t="str">
         <f>VLOOKUP(A38,Factors!D:K,8,0)</f>
         <v>constFactorFt3Gluk</v>
       </c>
-      <c r="E38" s="53" t="str">
+      <c r="E38" s="52" t="str">
         <f>VLOOKUP(A38,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F38" s="55" t="str">
+      <c r="F38" s="54" t="str">
         <f t="shared" si="6"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK</v>
       </c>
-      <c r="G38" s="55" t="str">
+      <c r="G38" s="54" t="str">
         <f t="shared" si="7"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
@@ -3857,15 +3913,15 @@
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFt3Gluk,       multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW "gal" STD_UK,                 "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I38" s="53">
+      <c r="I38" s="52">
         <f>VLOOKUP(A38,Factors!D:G,4,0)</f>
         <v>6.2288354590428261</v>
       </c>
-      <c r="J38" s="53" t="str">
+      <c r="J38" s="52" t="str">
         <f t="shared" si="9"/>
         <v>6.228835459042830000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K38" s="56" t="str">
+      <c r="K38" s="55" t="str">
         <f>VLOOKUP(A38,Factors!D:N,11,0)</f>
         <v>Ft3Gluk</v>
       </c>
@@ -3885,22 +3941,22 @@
       <c r="B39" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="C39" s="92" t="s">
+      <c r="C39" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D39" s="40" t="str">
         <f>VLOOKUP(A39,Factors!D:K,8,0)</f>
         <v>constFactorGlukFt3</v>
       </c>
-      <c r="E39" s="53" t="str">
+      <c r="E39" s="52" t="str">
         <f>VLOOKUP(A39,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F39" s="55" t="str">
+      <c r="F39" s="54" t="str">
         <f t="shared" si="6"/>
         <v>"gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3</v>
       </c>
-      <c r="G39" s="55" t="str">
+      <c r="G39" s="54" t="str">
         <f t="shared" si="7"/>
         <v>"gal" STD_UK STD_RIGHT_ARROW</v>
       </c>
@@ -3908,15 +3964,15 @@
         <f t="shared" si="8"/>
         <v>/* NNNN */  UNIT_CONV(constFactorGlukFt3,         divide,      "gal" STD_UK STD_RIGHT_ARROW "ft" STD_SUP_3,                 "gal" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
-      <c r="I39" s="53">
+      <c r="I39" s="52">
         <f>VLOOKUP(A39,Factors!D:G,4,0)</f>
         <v>6.2288354590428261</v>
       </c>
-      <c r="J39" s="53" t="str">
+      <c r="J39" s="52" t="str">
         <f t="shared" si="9"/>
         <v>6.228835459042830000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K39" s="56" t="str">
+      <c r="K39" s="55" t="str">
         <f>VLOOKUP(A39,Factors!D:N,11,0)</f>
         <v>Ft3Gluk</v>
       </c>
@@ -3936,47 +3992,47 @@
       <c r="B40" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="C40" s="92" t="s">
+      <c r="C40" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D40" s="40" t="str">
         <f>VLOOKUP(A40,Factors!D:K,8,0)</f>
         <v>constFactorLFt3</v>
       </c>
-      <c r="E40" s="53" t="str">
+      <c r="E40" s="52" t="str">
         <f>VLOOKUP(A40,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F40" s="55" t="str">
-        <f t="shared" si="6"/>
+      <c r="F40" s="54" t="str">
+        <f t="shared" ref="F40:F43" si="12" xml:space="preserve"> VLOOKUP(A40,stdform,2,0)</f>
         <v>STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3</v>
       </c>
-      <c r="G40" s="55" t="str">
-        <f t="shared" si="7"/>
+      <c r="G40" s="54" t="str">
+        <f t="shared" ref="G40:G43" si="13">MID(F40,1,SEARCH("STD_RIGHT_ARROW",F40)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>STD_litre STD_RIGHT_ARROW</v>
       </c>
       <c r="H40" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H40:H43" si="14">"/* NNNN */  UNIT_CONV("&amp;D40&amp;","&amp;REPT(CHAR(32),21-LEN(D40))&amp;"    "&amp;E40&amp;",      "&amp;F40&amp;","&amp;REPT(CHAR(32),60-LEN(F40))&amp;G40&amp;REPT(CHAR(32),60-LEN(G40))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorLFt3,            divide,      STD_litre STD_RIGHT_ARROW "ft" STD_SUP_3,                    STD_litre STD_RIGHT_ARROW                                   ),</v>
       </c>
-      <c r="I40" s="53">
+      <c r="I40" s="52">
         <f>VLOOKUP(A40,Factors!D:G,4,0)</f>
         <v>28.316846592000001</v>
       </c>
-      <c r="J40" s="53" t="str">
-        <f t="shared" si="9"/>
+      <c r="J40" s="52" t="str">
+        <f t="shared" ref="J40:J43" si="15">SUBSTITUTE(TEXT(I40,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K40" s="56" t="str">
+      <c r="K40" s="55" t="str">
         <f>VLOOKUP(A40,Factors!D:N,11,0)</f>
         <v>Ft3L</v>
       </c>
       <c r="L40" s="31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="L40:L43" si="16">IF(E40="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K40&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K40))&amp;CHAR(34)&amp;"+"&amp;J40&amp;CHAR(34)&amp;");","")</f>
         <v/>
       </c>
       <c r="N40" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="N40:N43" si="17">"    ["&amp;D40&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K40&amp;","</f>
         <v xml:space="preserve">    [constFactorLFt3] = &amp;const_Ft3L,</v>
       </c>
     </row>
@@ -3987,47 +4043,47 @@
       <c r="B41" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C41" s="92" t="s">
+      <c r="C41" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D41" s="40" t="str">
         <f>VLOOKUP(A41,Factors!D:K,8,0)</f>
         <v>constFactorFt3L</v>
       </c>
-      <c r="E41" s="53" t="str">
+      <c r="E41" s="52" t="str">
         <f>VLOOKUP(A41,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F41" s="55" t="str">
-        <f t="shared" si="6"/>
+      <c r="F41" s="54" t="str">
+        <f t="shared" si="12"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre</v>
       </c>
-      <c r="G41" s="55" t="str">
-        <f t="shared" si="7"/>
+      <c r="G41" s="54" t="str">
+        <f t="shared" si="13"/>
         <v>"ft" STD_SUP_3 STD_RIGHT_ARROW</v>
       </c>
       <c r="H41" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFt3L,          multiply,      "ft" STD_SUP_3 STD_RIGHT_ARROW STD_litre,                    "ft" STD_SUP_3 STD_RIGHT_ARROW                              ),</v>
       </c>
-      <c r="I41" s="53">
+      <c r="I41" s="52">
         <f>VLOOKUP(A41,Factors!D:G,4,0)</f>
         <v>28.316846592000001</v>
       </c>
-      <c r="J41" s="53" t="str">
-        <f t="shared" si="9"/>
+      <c r="J41" s="52" t="str">
+        <f t="shared" si="15"/>
         <v>2.831684659200000000000000000000000000000000000000000000e+01</v>
       </c>
-      <c r="K41" s="56" t="str">
+      <c r="K41" s="55" t="str">
         <f>VLOOKUP(A41,Factors!D:N,11,0)</f>
         <v>Ft3L</v>
       </c>
       <c r="L41" s="31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">  generateConstantArray("Ft3L",          "+2.831684659200000000000000000000000000000000000000000000e+01");</v>
       </c>
       <c r="N41" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">    [constFactorFt3L] = &amp;const_Ft3L,</v>
       </c>
     </row>
@@ -4038,47 +4094,47 @@
       <c r="B42" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="C42" s="92" t="s">
+      <c r="C42" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D42" s="40" t="str">
         <f>VLOOKUP(A42,Factors!D:K,8,0)</f>
         <v>constFactorLQtus</v>
       </c>
-      <c r="E42" s="53" t="str">
+      <c r="E42" s="52" t="str">
         <f>VLOOKUP(A42,Factors!D:N,10,0)</f>
         <v>multiply</v>
       </c>
-      <c r="F42" s="55" t="str">
-        <f t="shared" si="6"/>
+      <c r="F42" s="54" t="str">
+        <f t="shared" si="12"/>
         <v>STD_litre STD_RIGHT_ARROW "qt" STD_US</v>
       </c>
-      <c r="G42" s="55" t="str">
-        <f t="shared" si="7"/>
+      <c r="G42" s="54" t="str">
+        <f t="shared" si="13"/>
         <v>STD_litre STD_RIGHT_ARROW</v>
       </c>
       <c r="H42" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>/* NNNN */  UNIT_CONV(constFactorLQtus,         multiply,      STD_litre STD_RIGHT_ARROW "qt" STD_US,                       STD_litre STD_RIGHT_ARROW                                   ),</v>
       </c>
-      <c r="I42" s="53">
+      <c r="I42" s="52">
         <f>VLOOKUP(A42,Factors!D:G,4,0)</f>
         <v>1.0566882094325938</v>
       </c>
-      <c r="J42" s="53" t="str">
-        <f t="shared" si="9"/>
+      <c r="J42" s="52" t="str">
+        <f t="shared" si="15"/>
         <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K42" s="56" t="str">
+      <c r="K42" s="55" t="str">
         <f>VLOOKUP(A42,Factors!D:N,11,0)</f>
         <v>LQtus</v>
       </c>
       <c r="L42" s="31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">  generateConstantArray("LQtus",         "+1.056688209432590000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N42" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">    [constFactorLQtus] = &amp;const_LQtus,</v>
       </c>
     </row>
@@ -4089,75 +4145,271 @@
       <c r="B43" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="92" t="s">
+      <c r="C43" s="91" t="s">
         <v>70</v>
       </c>
       <c r="D43" s="40" t="str">
         <f>VLOOKUP(A43,Factors!D:K,8,0)</f>
         <v>constFactorQtusL</v>
       </c>
-      <c r="E43" s="53" t="str">
+      <c r="E43" s="52" t="str">
         <f>VLOOKUP(A43,Factors!D:N,10,0)</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="F43" s="55" t="str">
-        <f t="shared" si="0"/>
+      <c r="F43" s="54" t="str">
+        <f t="shared" si="12"/>
         <v>"qt" STD_US STD_RIGHT_ARROW STD_litre</v>
       </c>
-      <c r="G43" s="55" t="str">
-        <f t="shared" si="1"/>
+      <c r="G43" s="54" t="str">
+        <f t="shared" si="13"/>
         <v>"qt" STD_US STD_RIGHT_ARROW</v>
       </c>
       <c r="H43" s="30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="14"/>
         <v>/* NNNN */  UNIT_CONV(constFactorQtusL,           divide,      "qt" STD_US STD_RIGHT_ARROW STD_litre,                       "qt" STD_US STD_RIGHT_ARROW                                 ),</v>
       </c>
-      <c r="I43" s="53">
+      <c r="I43" s="52">
         <f>VLOOKUP(A43,Factors!D:G,4,0)</f>
         <v>1.0566882094325938</v>
       </c>
-      <c r="J43" s="53" t="str">
-        <f t="shared" si="3"/>
+      <c r="J43" s="52" t="str">
+        <f t="shared" si="15"/>
         <v>1.056688209432590000000000000000000000000000000000000000e+00</v>
       </c>
-      <c r="K43" s="56" t="str">
+      <c r="K43" s="55" t="str">
         <f>VLOOKUP(A43,Factors!D:N,11,0)</f>
         <v>LQtus</v>
       </c>
       <c r="L43" s="31" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N43" s="41" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">    [constFactorQtusL] = &amp;const_LQtus,</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" s="44"/>
+      <c r="C44" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="40" t="str">
+        <f>VLOOKUP(A44,Factors!D:K,8,0)</f>
+        <v>constFactorGlukFzuk</v>
+      </c>
+      <c r="E44" s="52" t="str">
+        <f>VLOOKUP(A44,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F44" s="54" t="str">
+        <f t="shared" si="6"/>
+        <v>"gal" STD_UK STD_RIGHT_ARROW "floz" STD_UK</v>
+      </c>
+      <c r="G44" s="54" t="str">
+        <f t="shared" si="7"/>
+        <v>"gal" STD_UK STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H44" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorGlukFzuk,      multiply,      "gal" STD_UK STD_RIGHT_ARROW "floz" STD_UK,                  "gal" STD_UK STD_RIGHT_ARROW                                ),</v>
+      </c>
+      <c r="I44" s="52">
+        <f>VLOOKUP(A44,Factors!D:G,4,0)</f>
+        <v>160</v>
+      </c>
+      <c r="J44" s="52" t="str">
+        <f t="shared" si="9"/>
+        <v>1.600000000000000000000000000000000000000000000000000000e+02</v>
+      </c>
+      <c r="K44" s="55" t="str">
+        <f>VLOOKUP(A44,Factors!D:N,11,0)</f>
+        <v>GlukFzuk</v>
+      </c>
+      <c r="L44" s="31" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("GlukFzuk",      "+1.600000000000000000000000000000000000000000000000000000e+02");</v>
+      </c>
+      <c r="N44" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorGlukFzuk] = &amp;const_GlukFzuk,</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" s="44"/>
+      <c r="C45" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="40" t="str">
+        <f>VLOOKUP(A45,Factors!D:K,8,0)</f>
+        <v>constFactorFzukGluk</v>
+      </c>
+      <c r="E45" s="52" t="str">
+        <f>VLOOKUP(A45,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F45" s="54" t="str">
+        <f t="shared" si="6"/>
+        <v>"floz" STD_UK STD_RIGHT_ARROW "gal" STD_UK</v>
+      </c>
+      <c r="G45" s="54" t="str">
+        <f t="shared" si="7"/>
+        <v>"floz" STD_UK STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H45" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorFzukGluk,        divide,      "floz" STD_UK STD_RIGHT_ARROW "gal" STD_UK,                  "floz" STD_UK STD_RIGHT_ARROW                               ),</v>
+      </c>
+      <c r="I45" s="52">
+        <f>VLOOKUP(A45,Factors!D:G,4,0)</f>
+        <v>160</v>
+      </c>
+      <c r="J45" s="52" t="str">
+        <f t="shared" si="9"/>
+        <v>1.600000000000000000000000000000000000000000000000000000e+02</v>
+      </c>
+      <c r="K45" s="55" t="str">
+        <f>VLOOKUP(A45,Factors!D:N,11,0)</f>
+        <v>GlukFzuk</v>
+      </c>
+      <c r="L45" s="31" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N45" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorFzukGluk] = &amp;const_GlukFzuk,</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="B46" s="44"/>
+      <c r="C46" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="40" t="str">
+        <f>VLOOKUP(A46,Factors!D:K,8,0)</f>
+        <v>constFactorGlusFzus</v>
+      </c>
+      <c r="E46" s="52" t="str">
+        <f>VLOOKUP(A46,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F46" s="54" t="str">
+        <f t="shared" si="6"/>
+        <v>"gal" STD_US STD_RIGHT_ARROW "floz" STD_US</v>
+      </c>
+      <c r="G46" s="54" t="str">
+        <f t="shared" si="7"/>
+        <v>"gal" STD_US STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H46" s="30" t="str">
+        <f t="shared" si="8"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorGlusFzus,      multiply,      "gal" STD_US STD_RIGHT_ARROW "floz" STD_US,                  "gal" STD_US STD_RIGHT_ARROW                                ),</v>
+      </c>
+      <c r="I46" s="52">
+        <f>VLOOKUP(A46,Factors!D:G,4,0)</f>
+        <v>128</v>
+      </c>
+      <c r="J46" s="52" t="str">
+        <f t="shared" si="9"/>
+        <v>1.280000000000000000000000000000000000000000000000000000e+02</v>
+      </c>
+      <c r="K46" s="55" t="str">
+        <f>VLOOKUP(A46,Factors!D:N,11,0)</f>
+        <v>GlusFzus</v>
+      </c>
+      <c r="L46" s="31" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">  generateConstantArray("GlusFzus",      "+1.280000000000000000000000000000000000000000000000000000e+02");</v>
+      </c>
+      <c r="N46" s="41" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    [constFactorGlusFzus] = &amp;const_GlusFzus,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="B47" s="44"/>
+      <c r="C47" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="40" t="str">
+        <f>VLOOKUP(A47,Factors!D:K,8,0)</f>
+        <v>constFactorFzusGlus</v>
+      </c>
+      <c r="E47" s="52" t="str">
+        <f>VLOOKUP(A47,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F47" s="54" t="str">
+        <f t="shared" si="0"/>
+        <v>"floz" STD_US STD_RIGHT_ARROW "gal" STD_US</v>
+      </c>
+      <c r="G47" s="54" t="str">
+        <f t="shared" si="1"/>
+        <v>"floz" STD_US STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H47" s="30" t="str">
+        <f t="shared" si="2"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorFzusGlus,        divide,      "floz" STD_US STD_RIGHT_ARROW "gal" STD_US,                  "floz" STD_US STD_RIGHT_ARROW                               ),</v>
+      </c>
+      <c r="I47" s="52">
+        <f>VLOOKUP(A47,Factors!D:G,4,0)</f>
+        <v>128</v>
+      </c>
+      <c r="J47" s="52" t="str">
+        <f t="shared" si="3"/>
+        <v>1.280000000000000000000000000000000000000000000000000000e+02</v>
+      </c>
+      <c r="K47" s="55" t="str">
+        <f>VLOOKUP(A47,Factors!D:N,11,0)</f>
+        <v>GlusFzus</v>
+      </c>
+      <c r="L47" s="31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N43" s="41" t="str">
+      <c r="N47" s="41" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    [constFactorQtusL] = &amp;const_LQtus,</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="4" t="s">
+        <v xml:space="preserve">    [constFactorFzusGlus] = &amp;const_GlusFzus,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="4" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B47">
-    <sortCondition ref="A4:A47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B51">
+    <sortCondition ref="A4:A51"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4166,7 +4418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAAB5F5-5A0E-F540-8CD7-68987B744E5F}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -4182,17 +4434,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17" thickBot="1">
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="68" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="59" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="17" thickBot="1">
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="60" t="s">
         <v>216</v>
       </c>
     </row>
@@ -4214,24 +4466,24 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="69" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="71"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="74">
+      <c r="F6" s="73">
         <v>3785.4117839999999</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="57" t="s">
         <v>229</v>
       </c>
-      <c r="H6" s="82">
+      <c r="H6" s="81">
         <f>231 * 0.0254^3 * 1000000</f>
         <v>3785.4117839999999</v>
       </c>
-      <c r="I6" s="83">
+      <c r="I6" s="82">
         <f>H6/$H$12</f>
         <v>768</v>
       </c>
@@ -4251,27 +4503,27 @@
       <c r="Q6" s="25"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="78" t="s">
+      <c r="E7" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="94">
         <f>H7</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="57" t="s">
         <v>228</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="83">
         <f>(231*0.0254^3/128*1000000)/2*32*2</f>
         <v>946.35294599999997</v>
       </c>
-      <c r="I7" s="83">
+      <c r="I7" s="82">
         <f t="shared" ref="I7:I11" si="2">H7/$H$12</f>
         <v>192</v>
       </c>
@@ -4292,26 +4544,26 @@
       <c r="R7" s="25"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="58">
         <v>473.17647299999999</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="83">
         <f>(231 * 0.0254^3 / 128 * 1000000) / 2 * 32</f>
         <v>473.17647299999999</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="82">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
@@ -4331,26 +4583,26 @@
       <c r="Q8" s="25"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="79" t="s">
+      <c r="D9" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="58">
         <v>236.58823649999999</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="84">
         <f>(231*0.0254^3/128*1000000)/2*32/2</f>
         <v>236.58823649999999</v>
       </c>
-      <c r="I9" s="83">
+      <c r="I9" s="82">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
@@ -4370,27 +4622,27 @@
       <c r="Q9" s="25"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="71"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="73">
         <v>29.573529562499999</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="H10" s="82">
+      <c r="H10" s="81">
         <f>231 * 0.0254^3 / 128 * 1000000</f>
         <v>29.573529562499999</v>
       </c>
-      <c r="I10" s="96">
+      <c r="I10" s="95">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -4409,33 +4661,33 @@
       <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="58">
         <v>14.78676478125</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="H11" s="86">
+      <c r="H11" s="85">
         <f>(231 * 0.0254^3 / 128 * 1000000) / 2</f>
         <v>14.78676478125</v>
       </c>
-      <c r="I11" s="83">
+      <c r="I11" s="82">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="J11" t="s">
         <v>255</v>
       </c>
-      <c r="K11" s="93">
+      <c r="K11" s="92">
         <f t="shared" si="0"/>
         <v>14.78676478125</v>
       </c>
@@ -4447,33 +4699,33 @@
       <c r="P11" s="26"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="79" t="s">
+      <c r="D12" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="58">
         <v>4.9289215937500002</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="85">
         <f>(231 * 0.0254^3 / 128 * 1000000) / 2 / 3</f>
         <v>4.9289215937500002</v>
       </c>
-      <c r="I12" s="83">
+      <c r="I12" s="82">
         <f>H12/$H$12</f>
         <v>1</v>
       </c>
       <c r="J12" t="s">
         <v>255</v>
       </c>
-      <c r="K12" s="93">
+      <c r="K12" s="92">
         <f>$H$6/$I$6*I12</f>
         <v>4.9289215937500002</v>
       </c>
@@ -4485,25 +4737,25 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="71"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="94">
         <f>H13</f>
         <v>4546.09</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G13" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="H13" s="82">
+      <c r="H13" s="81">
         <f>0.00454609 * 1000000</f>
         <v>4546.09</v>
       </c>
-      <c r="I13" s="87">
+      <c r="I13" s="86">
         <f t="shared" ref="I13:I19" si="3">H13/$H$19</f>
         <v>768</v>
       </c>
@@ -4523,27 +4775,27 @@
       <c r="Q13" s="25"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="52"/>
-      <c r="C14" s="73" t="s">
+      <c r="A14" s="51"/>
+      <c r="C14" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D14" s="79" t="s">
         <v>131</v>
       </c>
-      <c r="E14" s="81" t="s">
+      <c r="E14" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="58">
         <v>1136.5225</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="81">
         <f>0.00454609 / 4 * 1000000</f>
         <v>1136.5225</v>
       </c>
-      <c r="I14" s="87">
+      <c r="I14" s="86">
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
@@ -4564,26 +4816,26 @@
       <c r="Q14" s="25"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="52"/>
-      <c r="C15" s="72" t="s">
+      <c r="A15" s="51"/>
+      <c r="C15" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="79" t="s">
+      <c r="D15" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="58">
         <v>568.26125000000002</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="H15" s="82">
+      <c r="H15" s="81">
         <v>568.26125000000002</v>
       </c>
-      <c r="I15" s="87">
+      <c r="I15" s="86">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
@@ -4604,27 +4856,27 @@
       <c r="Q15" s="28"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="52"/>
-      <c r="C16" s="72" t="s">
+      <c r="A16" s="51"/>
+      <c r="C16" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="78" t="s">
         <v>129</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="58">
         <v>284.13062500000001</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="57" t="s">
         <v>252</v>
       </c>
-      <c r="H16" s="82">
+      <c r="H16" s="81">
         <f>0.00454609 / 16 * 1000000</f>
         <v>284.13062500000001</v>
       </c>
-      <c r="I16" s="87">
+      <c r="I16" s="86">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
@@ -4645,25 +4897,25 @@
       <c r="Q16" s="28"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="52"/>
-      <c r="C17" s="70" t="s">
+      <c r="A17" s="51"/>
+      <c r="C17" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="71"/>
+      <c r="D17" s="70"/>
       <c r="E17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="74">
+      <c r="F17" s="73">
         <v>28.413062500000002</v>
       </c>
-      <c r="G17" s="58" t="s">
+      <c r="G17" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="H17" s="82">
+      <c r="H17" s="81">
         <f xml:space="preserve"> 0.00454609 / 160 * 1000000</f>
         <v>28.413062500000002</v>
       </c>
-      <c r="I17" s="97">
+      <c r="I17" s="96">
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
@@ -4682,29 +4934,29 @@
       <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="79" t="s">
+      <c r="D18" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="77" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="59">
+      <c r="F18" s="58">
         <v>17.758164062500001</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="H18" s="88">
+      <c r="H18" s="87">
         <f>568.26125/32</f>
         <v>17.758164062500001</v>
       </c>
-      <c r="I18" s="87">
+      <c r="I18" s="86">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -4724,37 +4976,37 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="79" t="s">
+      <c r="D19" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="74">
         <f>H19</f>
         <v>5.9193880208333338</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="57" t="s">
         <v>254</v>
       </c>
-      <c r="H19" s="89">
+      <c r="H19" s="88">
         <f>568.26125/96</f>
         <v>5.9193880208333338</v>
       </c>
-      <c r="I19" s="87">
+      <c r="I19" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J19" t="s">
         <v>256</v>
       </c>
-      <c r="K19" s="94">
+      <c r="K19" s="93">
         <f>$H$13/$I$13*I19</f>
         <v>5.9193880208333338</v>
       </c>
@@ -4767,100 +5019,100 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="70" t="s">
         <v>123</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="59">
+      <c r="F20" s="58">
         <v>1</v>
       </c>
-      <c r="G20" s="58" t="s">
+      <c r="G20" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="H20" s="82">
+      <c r="H20" s="81">
         <v>1</v>
       </c>
-      <c r="I20" s="90"/>
+      <c r="I20" s="89"/>
       <c r="M20" s="7"/>
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="69" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="71"/>
+      <c r="D21" s="70"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="59">
+      <c r="F21" s="58">
         <f>2.54^3</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="H21" s="82">
+      <c r="H21" s="81">
         <f>2.54^3</f>
         <v>16.387063999999999</v>
       </c>
-      <c r="I21" s="90"/>
+      <c r="I21" s="89"/>
       <c r="J21" s="24"/>
       <c r="K21" s="25"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="71"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="76">
+      <c r="F22" s="75">
         <f>(12*2.54)^3</f>
         <v>28316.846592000002</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="H22" s="84">
+      <c r="H22" s="83">
         <f>(12*2.54)^3</f>
         <v>28316.846592000002</v>
       </c>
-      <c r="I22" s="90"/>
+      <c r="I22" s="89"/>
       <c r="J22" s="24"/>
       <c r="K22" s="25"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="71"/>
+      <c r="D23" s="70"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="59">
+      <c r="F23" s="58">
         <v>1000</v>
       </c>
-      <c r="G23" s="58" t="s">
+      <c r="G23" s="57" t="s">
         <v>249</v>
       </c>
-      <c r="H23" s="82"/>
-      <c r="I23" s="90"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="89"/>
       <c r="J23" s="24"/>
       <c r="K23" s="25"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="C24" s="52"/>
+      <c r="C24" s="51"/>
       <c r="F24" s="34"/>
-      <c r="G24" s="66"/>
+      <c r="G24" s="65"/>
       <c r="J24" s="24"/>
       <c r="K24" s="25"/>
     </row>
     <row r="25" spans="1:16">
       <c r="F25" s="1"/>
-      <c r="H25" s="62">
+      <c r="H25" s="61">
         <f xml:space="preserve"> 568.26125 / 20</f>
         <v>28.413062500000002</v>
       </c>
@@ -4945,7 +5197,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="36">
-        <f t="shared" ref="F29:F69" si="7">H29/I29</f>
+        <f t="shared" ref="F29:F73" si="7">H29/I29</f>
         <v>2.1133764188651875E-3</v>
       </c>
       <c r="G29" s="38">
@@ -6501,15 +6753,15 @@
       </c>
     </row>
     <row r="62" spans="1:14" ht="18">
-      <c r="A62" s="51" t="str">
+      <c r="A62" s="50" t="str">
         <f>MID(D62,5,99)</f>
         <v>MLtoIN3</v>
       </c>
-      <c r="B62" s="52" t="str">
+      <c r="B62" s="51" t="str">
         <f>MID(A62,1,SEARCH("to",A62)-1)</f>
         <v>ML</v>
       </c>
-      <c r="C62" s="52" t="str">
+      <c r="C62" s="51" t="str">
         <f>MID(A62,SEARCH("to",A62)+2,99)</f>
         <v>IN3</v>
       </c>
@@ -6532,15 +6784,15 @@
         <v>1</v>
       </c>
       <c r="I62" s="9">
-        <f t="shared" ref="I62:I69" si="27" xml:space="preserve"> VLOOKUP(C62,units,4,0)</f>
+        <f t="shared" ref="I62:I73" si="27" xml:space="preserve"> VLOOKUP(C62,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
       <c r="J62" t="str">
-        <f t="shared" ref="J62:J69" si="28">PROPER(B62)&amp;PROPER(C62)</f>
+        <f t="shared" ref="J62:J73" si="28">PROPER(B62)&amp;PROPER(C62)</f>
         <v>MlIn3</v>
       </c>
       <c r="K62" t="str">
-        <f t="shared" ref="K62:K69" si="29">"constFactor"&amp;J62</f>
+        <f t="shared" ref="K62:K73" si="29">"constFactor"&amp;J62</f>
         <v>constFactorMlIn3</v>
       </c>
       <c r="M62" s="38" t="str">
@@ -6553,16 +6805,16 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="18">
-      <c r="A63" s="51" t="str">
-        <f t="shared" ref="A63:A69" si="30">MID(D63,5,99)</f>
+      <c r="A63" s="50" t="str">
+        <f t="shared" ref="A63:A73" si="30">MID(D63,5,99)</f>
         <v>IN3toML</v>
       </c>
-      <c r="B63" s="52" t="str">
-        <f t="shared" ref="B63:B69" si="31">MID(A63,1,SEARCH("to",A63)-1)</f>
+      <c r="B63" s="51" t="str">
+        <f t="shared" ref="B63:B73" si="31">MID(A63,1,SEARCH("to",A63)-1)</f>
         <v>IN3</v>
       </c>
-      <c r="C63" s="52" t="str">
-        <f t="shared" ref="C63:C69" si="32">MID(A63,SEARCH("to",A63)+2,99)</f>
+      <c r="C63" s="51" t="str">
+        <f t="shared" ref="C63:C73" si="32">MID(A63,SEARCH("to",A63)+2,99)</f>
         <v>ML</v>
       </c>
       <c r="D63" s="47" t="s">
@@ -6580,7 +6832,7 @@
         <v>16.387063999999999</v>
       </c>
       <c r="H63" s="9">
-        <f t="shared" ref="H63:H69" si="33" xml:space="preserve"> VLOOKUP(B63,units,4,0)</f>
+        <f t="shared" ref="H63:H73" si="33" xml:space="preserve"> VLOOKUP(B63,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
       <c r="I63" s="9">
@@ -6605,15 +6857,15 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="18">
-      <c r="A64" s="51" t="str">
+      <c r="A64" s="50" t="str">
         <f t="shared" si="30"/>
         <v>FT3toGLUK</v>
       </c>
-      <c r="B64" s="52" t="str">
+      <c r="B64" s="51" t="str">
         <f t="shared" si="31"/>
         <v>FT3</v>
       </c>
-      <c r="C64" s="52" t="str">
+      <c r="C64" s="51" t="str">
         <f t="shared" si="32"/>
         <v>GLUK</v>
       </c>
@@ -6657,15 +6909,15 @@
       </c>
     </row>
     <row r="65" spans="1:14" ht="18">
-      <c r="A65" s="51" t="str">
+      <c r="A65" s="50" t="str">
         <f t="shared" si="30"/>
         <v>GLUKtoFT3</v>
       </c>
-      <c r="B65" s="52" t="str">
+      <c r="B65" s="51" t="str">
         <f t="shared" si="31"/>
         <v>GLUK</v>
       </c>
-      <c r="C65" s="52" t="str">
+      <c r="C65" s="51" t="str">
         <f t="shared" si="32"/>
         <v>FT3</v>
       </c>
@@ -6709,16 +6961,16 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="18">
-      <c r="A66" s="51" t="str">
-        <f t="shared" si="30"/>
+      <c r="A66" s="50" t="str">
+        <f t="shared" ref="A66:A69" si="34">MID(D66,5,99)</f>
         <v>LtoFT3</v>
       </c>
-      <c r="B66" s="52" t="str">
-        <f t="shared" si="31"/>
+      <c r="B66" s="51" t="str">
+        <f t="shared" ref="B66:B69" si="35">MID(A66,1,SEARCH("to",A66)-1)</f>
         <v>L</v>
       </c>
-      <c r="C66" s="52" t="str">
-        <f t="shared" si="32"/>
+      <c r="C66" s="51" t="str">
+        <f t="shared" ref="C66:C69" si="36">MID(A66,SEARCH("to",A66)+2,99)</f>
         <v>FT3</v>
       </c>
       <c r="D66" s="47" t="s">
@@ -6728,49 +6980,49 @@
         <v>197</v>
       </c>
       <c r="F66" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F66:F69" si="37">H66/I66</f>
         <v>3.5314666721488586E-2</v>
       </c>
-      <c r="G66" s="38">
+      <c r="G66" s="39">
         <f>IF(M66="multiply",F66,F67)</f>
         <v>28.316846592000001</v>
       </c>
       <c r="H66" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="H66:H69" si="38" xml:space="preserve"> VLOOKUP(B66,units,4,0)</f>
         <v>1000</v>
       </c>
       <c r="I66" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="I66:I69" si="39" xml:space="preserve"> VLOOKUP(C66,units,4,0)</f>
         <v>28316.846592000002</v>
       </c>
       <c r="J66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="J66:J69" si="40">PROPER(B66)&amp;PROPER(C66)</f>
         <v>LFt3</v>
       </c>
       <c r="K66" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="K66:K69" si="41">"constFactor"&amp;J66</f>
         <v>constFactorLFt3</v>
       </c>
-      <c r="M66" s="38" t="str">
+      <c r="M66" s="39" t="str">
         <f>IF(H66&gt;I66,"multiply","  divide")</f>
         <v xml:space="preserve">  divide</v>
       </c>
-      <c r="N66" s="38" t="str">
+      <c r="N66" s="39" t="str">
         <f>IF(M66="multiply",PROPER(B66)&amp;PROPER(C66),J67)</f>
         <v>Ft3L</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="18">
-      <c r="A67" s="51" t="str">
-        <f t="shared" si="30"/>
+      <c r="A67" s="50" t="str">
+        <f t="shared" si="34"/>
         <v>FT3toL</v>
       </c>
-      <c r="B67" s="52" t="str">
-        <f t="shared" si="31"/>
+      <c r="B67" s="51" t="str">
+        <f t="shared" si="35"/>
         <v>FT3</v>
       </c>
-      <c r="C67" s="52" t="str">
-        <f t="shared" si="32"/>
+      <c r="C67" s="51" t="str">
+        <f t="shared" si="36"/>
         <v>L</v>
       </c>
       <c r="D67" s="47" t="s">
@@ -6780,49 +7032,49 @@
         <v>198</v>
       </c>
       <c r="F67" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>28.316846592000001</v>
       </c>
-      <c r="G67" s="38">
+      <c r="G67" s="39">
         <f>IF(M67="multiply",F67,F66)</f>
         <v>28.316846592000001</v>
       </c>
       <c r="H67" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>28316.846592000002</v>
       </c>
       <c r="I67" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>1000</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>Ft3L</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>constFactorFt3L</v>
       </c>
-      <c r="M67" s="38" t="str">
+      <c r="M67" s="39" t="str">
         <f>IF(M66="multiply","  divide","multiply")</f>
         <v>multiply</v>
       </c>
-      <c r="N67" s="38" t="str">
+      <c r="N67" s="39" t="str">
         <f>IF(M67="multiply",PROPER(B67)&amp;PROPER(C67),J66)</f>
         <v>Ft3L</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="18">
-      <c r="A68" s="51" t="str">
-        <f t="shared" si="30"/>
+      <c r="A68" s="50" t="str">
+        <f t="shared" si="34"/>
         <v>LtoQTUS</v>
       </c>
-      <c r="B68" s="52" t="str">
-        <f t="shared" si="31"/>
+      <c r="B68" s="51" t="str">
+        <f t="shared" si="35"/>
         <v>L</v>
       </c>
-      <c r="C68" s="52" t="str">
-        <f t="shared" si="32"/>
+      <c r="C68" s="51" t="str">
+        <f t="shared" si="36"/>
         <v>QTUS</v>
       </c>
       <c r="D68" s="47" t="s">
@@ -6832,7 +7084,7 @@
         <v>199</v>
       </c>
       <c r="F68" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>1.0566882094325938</v>
       </c>
       <c r="G68" s="39">
@@ -6840,19 +7092,19 @@
         <v>1.0566882094325938</v>
       </c>
       <c r="H68" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>1000</v>
       </c>
       <c r="I68" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>946.35294599999997</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>LQtus</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>constFactorLQtus</v>
       </c>
       <c r="M68" s="39" t="str">
@@ -6864,27 +7116,27 @@
         <v>LQtus</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="19" thickBot="1">
-      <c r="A69" s="51" t="str">
-        <f t="shared" si="30"/>
+    <row r="69" spans="1:14" ht="18">
+      <c r="A69" s="50" t="str">
+        <f t="shared" si="34"/>
         <v>QTUStoL</v>
       </c>
-      <c r="B69" s="52" t="str">
-        <f t="shared" si="31"/>
+      <c r="B69" s="51" t="str">
+        <f t="shared" si="35"/>
         <v>QTUS</v>
       </c>
-      <c r="C69" s="52" t="str">
-        <f t="shared" si="32"/>
+      <c r="C69" s="51" t="str">
+        <f t="shared" si="36"/>
         <v>L</v>
       </c>
-      <c r="D69" s="49" t="s">
+      <c r="D69" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="E69" s="50" t="s">
+      <c r="E69" s="48" t="s">
         <v>200</v>
       </c>
       <c r="F69" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>0.94635294599999997</v>
       </c>
       <c r="G69" s="39">
@@ -6892,19 +7144,19 @@
         <v>1.0566882094325938</v>
       </c>
       <c r="H69" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>946.35294599999997</v>
       </c>
       <c r="I69" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="39"/>
         <v>1000</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="40"/>
         <v>QtusL</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="41"/>
         <v>constFactorQtusL</v>
       </c>
       <c r="M69" s="39" t="str">
@@ -6914,6 +7166,206 @@
       <c r="N69" s="39" t="str">
         <f>IF(M69="multiply",PROPER(B69)&amp;PROPER(C69),J68)</f>
         <v>LQtus</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="18">
+      <c r="A70" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>GLUKtoFZUK</v>
+      </c>
+      <c r="B70" s="51" t="str">
+        <f t="shared" ref="B70:B73" si="42">MID(A70,1,SEARCH("to",A70)-1)</f>
+        <v>GLUK</v>
+      </c>
+      <c r="C70" s="51" t="str">
+        <f t="shared" ref="C70:C73" si="43">MID(A70,SEARCH("to",A70)+2,99)</f>
+        <v>FZUK</v>
+      </c>
+      <c r="D70" s="97" t="s">
+        <v>262</v>
+      </c>
+      <c r="E70" s="99"/>
+      <c r="F70" s="36">
+        <f t="shared" si="7"/>
+        <v>160</v>
+      </c>
+      <c r="G70" s="38">
+        <f>IF(M70="multiply",F70,F71)</f>
+        <v>160</v>
+      </c>
+      <c r="H70" s="9">
+        <f t="shared" si="33"/>
+        <v>4546.09</v>
+      </c>
+      <c r="I70" s="9">
+        <f t="shared" si="27"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="J70" t="str">
+        <f t="shared" si="28"/>
+        <v>GlukFzuk</v>
+      </c>
+      <c r="K70" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorGlukFzuk</v>
+      </c>
+      <c r="M70" s="38" t="str">
+        <f>IF(H70&gt;I70,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N70" s="38" t="str">
+        <f>IF(M70="multiply",PROPER(B70)&amp;PROPER(C70),J71)</f>
+        <v>GlukFzuk</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="18">
+      <c r="A71" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>FZUKtoGLUK</v>
+      </c>
+      <c r="B71" s="51" t="str">
+        <f t="shared" si="42"/>
+        <v>FZUK</v>
+      </c>
+      <c r="C71" s="51" t="str">
+        <f t="shared" si="43"/>
+        <v>GLUK</v>
+      </c>
+      <c r="D71" s="97" t="s">
+        <v>263</v>
+      </c>
+      <c r="E71" s="48"/>
+      <c r="F71" s="36">
+        <f t="shared" si="7"/>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="G71" s="38">
+        <f>IF(M71="multiply",F71,F70)</f>
+        <v>160</v>
+      </c>
+      <c r="H71" s="9">
+        <f t="shared" si="33"/>
+        <v>28.413062500000002</v>
+      </c>
+      <c r="I71" s="9">
+        <f t="shared" si="27"/>
+        <v>4546.09</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" si="28"/>
+        <v>FzukGluk</v>
+      </c>
+      <c r="K71" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorFzukGluk</v>
+      </c>
+      <c r="M71" s="38" t="str">
+        <f>IF(M70="multiply","  divide","multiply")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N71" s="38" t="str">
+        <f>IF(M71="multiply",PROPER(B71)&amp;PROPER(C71),J70)</f>
+        <v>GlukFzuk</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="18">
+      <c r="A72" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>GLUStoFZUS</v>
+      </c>
+      <c r="B72" s="51" t="str">
+        <f t="shared" si="42"/>
+        <v>GLUS</v>
+      </c>
+      <c r="C72" s="51" t="str">
+        <f t="shared" si="43"/>
+        <v>FZUS</v>
+      </c>
+      <c r="D72" s="97" t="s">
+        <v>264</v>
+      </c>
+      <c r="E72" s="48"/>
+      <c r="F72" s="36">
+        <f t="shared" si="7"/>
+        <v>128</v>
+      </c>
+      <c r="G72" s="39">
+        <f>IF(M72="multiply",F72,F73)</f>
+        <v>128</v>
+      </c>
+      <c r="H72" s="9">
+        <f t="shared" si="33"/>
+        <v>3785.4117839999999</v>
+      </c>
+      <c r="I72" s="9">
+        <f t="shared" si="27"/>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="28"/>
+        <v>GlusFzus</v>
+      </c>
+      <c r="K72" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorGlusFzus</v>
+      </c>
+      <c r="M72" s="39" t="str">
+        <f>IF(H72&gt;I72,"multiply","  divide")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N72" s="39" t="str">
+        <f>IF(M72="multiply",PROPER(B72)&amp;PROPER(C72),J73)</f>
+        <v>GlusFzus</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="19" thickBot="1">
+      <c r="A73" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>FZUStoGLUS</v>
+      </c>
+      <c r="B73" s="51" t="str">
+        <f t="shared" si="42"/>
+        <v>FZUS</v>
+      </c>
+      <c r="C73" s="51" t="str">
+        <f t="shared" si="43"/>
+        <v>GLUS</v>
+      </c>
+      <c r="D73" s="98" t="s">
+        <v>265</v>
+      </c>
+      <c r="E73" s="49"/>
+      <c r="F73" s="36">
+        <f t="shared" si="7"/>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="G73" s="39">
+        <f>IF(M73="multiply",F73,F72)</f>
+        <v>128</v>
+      </c>
+      <c r="H73" s="9">
+        <f t="shared" si="33"/>
+        <v>29.573529562499999</v>
+      </c>
+      <c r="I73" s="9">
+        <f t="shared" si="27"/>
+        <v>3785.4117839999999</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="28"/>
+        <v>FzusGlus</v>
+      </c>
+      <c r="K73" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorFzusGlus</v>
+      </c>
+      <c r="M73" s="39" t="str">
+        <f>IF(M72="multiply","  divide","multiply")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N73" s="39" t="str">
+        <f>IF(M73="multiply",PROPER(B73)&amp;PROPER(C73),J72)</f>
+        <v>GlusFzus</v>
       </c>
     </row>
   </sheetData>
@@ -6931,17 +7383,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="64" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="46">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="63" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="46">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="63" t="s">
         <v>221</v>
       </c>
     </row>
@@ -6951,12 +7403,12 @@
       </c>
     </row>
     <row r="9" spans="2:2">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="65" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="20">
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="56" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6981,7 +7433,7 @@
       </c>
     </row>
     <row r="19" spans="2:2" ht="51">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="66" t="s">
         <v>224</v>
       </c>
     </row>
@@ -7005,43 +7457,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:4">
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4" spans="3:4">
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="65" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="3:4">
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="65" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="8" spans="3:4">
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="65" t="s">
         <v>238</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="67" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="9" spans="3:4">
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="65" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="12" spans="3:4">
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="67" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="13" spans="3:4" ht="119">
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="62" t="s">
         <v>243</v>
       </c>
     </row>
@@ -7051,17 +7503,17 @@
       </c>
     </row>
     <row r="16" spans="3:4">
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="65" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="18" spans="3:3">
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="67" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="19" spans="3:3">
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="65" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7072,7 +7524,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF49E5-C5CF-EF45-BD21-7588D88F54A2}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -7431,6 +7883,38 @@
         <v>200</v>
       </c>
     </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="100" t="s">
+        <v>262</v>
+      </c>
+      <c r="B44" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="100" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="B46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="B47" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
+++ b/src/index spreadsheet/New and updated labels for Chef menu_rj_jm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/wp43s/src/index spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C17E99C-2B47-CF48-8EA2-F06D21EC4DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9BD331-D894-3E44-9D03-48B0ED8A6173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="20500" activeTab="1" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="32660" windowHeight="20500" xr2:uid="{95F5296B-734B-A140-B6F4-11B4F81E2566}"/>
   </bookViews>
   <sheets>
     <sheet name="Items and code" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="280">
   <si>
     <t>ITM_PINTLQtoML</t>
   </si>
@@ -1008,6 +1008,36 @@
   </si>
   <si>
     <t>"floz" STD_US STD_RIGHT_ARROW "gal" STD_US</t>
+  </si>
+  <si>
+    <t>ITM_EVtoJ</t>
+  </si>
+  <si>
+    <t>ITM_JtoEV</t>
+  </si>
+  <si>
+    <t>constFactoreVJ</t>
+  </si>
+  <si>
+    <t>constFactorJeV</t>
+  </si>
+  <si>
+    <t>eV</t>
+  </si>
+  <si>
+    <t>eV→J</t>
+  </si>
+  <si>
+    <t>J→eV</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>"eV" STD_RIGHT_ARROW "J"</t>
+  </si>
+  <si>
+    <t>"J" STD_RIGHT_ARROW "eV"</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1745,6 +1775,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2079,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8086E2D2-A619-CD41-963B-CA5F79ED1F95}">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" bestFit="1" customWidth="1"/>
@@ -2168,7 +2202,7 @@
         <v>multiply</v>
       </c>
       <c r="F4" s="54" t="str">
-        <f t="shared" ref="F4:F47" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
+        <f t="shared" ref="F4:F49" si="0" xml:space="preserve"> VLOOKUP(A4,stdform,2,0)</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
       <c r="G4" s="54" t="str">
@@ -2223,11 +2257,11 @@
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml"</v>
       </c>
       <c r="G5" s="54" t="str">
-        <f t="shared" ref="G5:G47" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
+        <f t="shared" ref="G5:G49" si="1">MID(F5,1,SEARCH("STD_RIGHT_ARROW",F5)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"cup" STD_US STD_SUB_c STD_RIGHT_ARROW</v>
       </c>
       <c r="H5" s="30" t="str">
-        <f t="shared" ref="H5:H47" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
+        <f t="shared" ref="H5:H49" si="2">"/* NNNN */  UNIT_CONV("&amp;D5&amp;","&amp;REPT(CHAR(32),21-LEN(D5))&amp;"    "&amp;E5&amp;",      "&amp;F5&amp;","&amp;REPT(CHAR(32),60-LEN(F5))&amp;G5&amp;REPT(CHAR(32),60-LEN(G5))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorCupcMl,        multiply,      "cup" STD_US STD_SUB_c STD_RIGHT_ARROW "ml",                 "cup" STD_US STD_SUB_c STD_RIGHT_ARROW                      ),</v>
       </c>
       <c r="I5" s="52">
@@ -2235,7 +2269,7 @@
         <v>236.58823649999999</v>
       </c>
       <c r="J5" s="52" t="str">
-        <f t="shared" ref="J5:J47" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+        <f t="shared" ref="J5:J49" si="3">SUBSTITUTE(TEXT(I5,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>2.365882365000000000000000000000000000000000000000000000e+02</v>
       </c>
       <c r="K5" s="55" t="str">
@@ -2243,11 +2277,11 @@
         <v>CupcMl</v>
       </c>
       <c r="L5" s="31" t="str">
-        <f t="shared" ref="L5:L47" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
+        <f t="shared" ref="L5:L49" si="4">IF(E5="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K5&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K5))&amp;CHAR(34)&amp;"+"&amp;J5&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("CupcMl",        "+2.365882365000000000000000000000000000000000000000000000e+02");</v>
       </c>
       <c r="N5" s="41" t="str">
-        <f t="shared" ref="N5:N47" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
+        <f t="shared" ref="N5:N49" si="5">"    ["&amp;D5&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K5&amp;","</f>
         <v xml:space="preserve">    [constFactorCupcMl] = &amp;const_CupcMl,</v>
       </c>
     </row>
@@ -3749,15 +3783,15 @@
         <v>multiply</v>
       </c>
       <c r="F35" s="54" t="str">
-        <f t="shared" ref="F35:F46" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
+        <f t="shared" ref="F35:F48" si="6" xml:space="preserve"> VLOOKUP(A35,stdform,2,0)</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW "ml"</v>
       </c>
       <c r="G35" s="54" t="str">
-        <f t="shared" ref="G35:G46" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
+        <f t="shared" ref="G35:G48" si="7">MID(F35,1,SEARCH("STD_RIGHT_ARROW",F35)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"tsp" STD_UK STD_RIGHT_ARROW</v>
       </c>
       <c r="H35" s="30" t="str">
-        <f t="shared" ref="H35:H46" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
+        <f t="shared" ref="H35:H48" si="8">"/* NNNN */  UNIT_CONV("&amp;D35&amp;","&amp;REPT(CHAR(32),21-LEN(D35))&amp;"    "&amp;E35&amp;",      "&amp;F35&amp;","&amp;REPT(CHAR(32),60-LEN(F35))&amp;G35&amp;REPT(CHAR(32),60-LEN(G35))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorTspukMl,       multiply,      "tsp" STD_UK STD_RIGHT_ARROW "ml",                           "tsp" STD_UK STD_RIGHT_ARROW                                ),</v>
       </c>
       <c r="I35" s="52">
@@ -3765,7 +3799,7 @@
         <v>5.9193880208333338</v>
       </c>
       <c r="J35" s="52" t="str">
-        <f t="shared" ref="J35:J46" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+        <f t="shared" ref="J35:J48" si="9">SUBSTITUTE(TEXT(I35,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>5.919388020833330000000000000000000000000000000000000000e+00</v>
       </c>
       <c r="K35" s="55" t="str">
@@ -3773,11 +3807,11 @@
         <v>TspukMl</v>
       </c>
       <c r="L35" s="31" t="str">
-        <f t="shared" ref="L35:L46" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
+        <f t="shared" ref="L35:L48" si="10">IF(E35="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K35&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K35))&amp;CHAR(34)&amp;"+"&amp;J35&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("TspukMl",       "+5.919388020833330000000000000000000000000000000000000000e+00");</v>
       </c>
       <c r="N35" s="41" t="str">
-        <f t="shared" ref="N35:N46" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
+        <f t="shared" ref="N35:N48" si="11">"    ["&amp;D35&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K35&amp;","</f>
         <v xml:space="preserve">    [constFactorTspukMl] = &amp;const_TspukMl,</v>
       </c>
     </row>
@@ -4304,15 +4338,15 @@
         <v>multiply</v>
       </c>
       <c r="F46" s="54" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F46:F47" si="18" xml:space="preserve"> VLOOKUP(A46,stdform,2,0)</f>
         <v>"gal" STD_US STD_RIGHT_ARROW "floz" STD_US</v>
       </c>
       <c r="G46" s="54" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="G46:G47" si="19">MID(F46,1,SEARCH("STD_RIGHT_ARROW",F46)-2)&amp;" STD_RIGHT_ARROW"</f>
         <v>"gal" STD_US STD_RIGHT_ARROW</v>
       </c>
       <c r="H46" s="30" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H46:H47" si="20">"/* NNNN */  UNIT_CONV("&amp;D46&amp;","&amp;REPT(CHAR(32),21-LEN(D46))&amp;"    "&amp;E46&amp;",      "&amp;F46&amp;","&amp;REPT(CHAR(32),60-LEN(F46))&amp;G46&amp;REPT(CHAR(32),60-LEN(G46))&amp;"),"</f>
         <v>/* NNNN */  UNIT_CONV(constFactorGlusFzus,      multiply,      "gal" STD_US STD_RIGHT_ARROW "floz" STD_US,                  "gal" STD_US STD_RIGHT_ARROW                                ),</v>
       </c>
       <c r="I46" s="52">
@@ -4320,7 +4354,7 @@
         <v>128</v>
       </c>
       <c r="J46" s="52" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J46:J47" si="21">SUBSTITUTE(TEXT(I46,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
         <v>1.280000000000000000000000000000000000000000000000000000e+02</v>
       </c>
       <c r="K46" s="55" t="str">
@@ -4328,11 +4362,11 @@
         <v>GlusFzus</v>
       </c>
       <c r="L46" s="31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="L46:L47" si="22">IF(E46="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K46&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K46))&amp;CHAR(34)&amp;"+"&amp;J46&amp;CHAR(34)&amp;");","")</f>
         <v xml:space="preserve">  generateConstantArray("GlusFzus",      "+1.280000000000000000000000000000000000000000000000000000e+02");</v>
       </c>
       <c r="N46" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="N46:N47" si="23">"    ["&amp;D46&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K46&amp;","</f>
         <v xml:space="preserve">    [constFactorGlusFzus] = &amp;const_GlusFzus,</v>
       </c>
     </row>
@@ -4353,15 +4387,15 @@
         <v xml:space="preserve">  divide</v>
       </c>
       <c r="F47" s="54" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="18"/>
         <v>"floz" STD_US STD_RIGHT_ARROW "gal" STD_US</v>
       </c>
       <c r="G47" s="54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="19"/>
         <v>"floz" STD_US STD_RIGHT_ARROW</v>
       </c>
       <c r="H47" s="30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="20"/>
         <v>/* NNNN */  UNIT_CONV(constFactorFzusGlus,        divide,      "floz" STD_US STD_RIGHT_ARROW "gal" STD_US,                  "floz" STD_US STD_RIGHT_ARROW                               ),</v>
       </c>
       <c r="I47" s="52">
@@ -4369,7 +4403,7 @@
         <v>128</v>
       </c>
       <c r="J47" s="52" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>1.280000000000000000000000000000000000000000000000000000e+02</v>
       </c>
       <c r="K47" s="55" t="str">
@@ -4377,39 +4411,135 @@
         <v>GlusFzus</v>
       </c>
       <c r="L47" s="31" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N47" s="41" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">    [constFactorFzusGlus] = &amp;const_GlusFzus,</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
+    <row r="48" spans="1:14">
+      <c r="A48" s="101" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" s="44"/>
+      <c r="C48" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="102" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" s="52" t="str">
+        <f>VLOOKUP(A48,Factors!D:N,10,0)</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="F48" s="54" t="str">
+        <f t="shared" si="6"/>
+        <v>"eV" STD_RIGHT_ARROW "J"</v>
+      </c>
+      <c r="G48" s="54" t="str">
+        <f t="shared" si="7"/>
+        <v>"eV" STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H48" s="30" t="str">
+        <f t="shared" ref="H48:H49" si="24">"/* NNNN */  UNIT_CONV("&amp;D48&amp;","&amp;REPT(CHAR(32),21-LEN(D48))&amp;"    "&amp;E48&amp;",      "&amp;F48&amp;","&amp;REPT(CHAR(32),60-LEN(F48))&amp;G48&amp;REPT(CHAR(32),60-LEN(G48))&amp;"),"</f>
+        <v>/* NNNN */  UNIT_CONV(constFactoreVJ,             divide,      "eV" STD_RIGHT_ARROW "J",                                    "eV" STD_RIGHT_ARROW                                        ),</v>
+      </c>
+      <c r="I48" s="52">
+        <f>VLOOKUP(A48,Factors!D:G,4,0)</f>
+        <v>6.2415090744607631E+18</v>
+      </c>
+      <c r="J48" s="52" t="str">
+        <f t="shared" ref="J48:J49" si="25">SUBSTITUTE(TEXT(I48,"0.000000000000000000000000000000000000000000000000000000E+00"),"E","e")</f>
+        <v>6.241509074460760000000000000000000000000000000000000000e+18</v>
+      </c>
+      <c r="K48" s="55" t="str">
+        <f>VLOOKUP(A48,Factors!D:N,11,0)</f>
+        <v>JEv</v>
+      </c>
+      <c r="L48" s="31" t="str">
+        <f t="shared" ref="L48:L49" si="26">IF(E48="multiply","  generateConstantArray("&amp;CHAR(34)&amp;K48&amp;CHAR(34)&amp;","&amp;REPT(CHAR(32),14-LEN(K48))&amp;CHAR(34)&amp;"+"&amp;J48&amp;CHAR(34)&amp;");","")</f>
+        <v/>
+      </c>
+      <c r="N48" s="41" t="str">
+        <f t="shared" ref="N48:N49" si="27">"    ["&amp;D48&amp;"] = "&amp;CHAR(38)&amp;"const_"&amp;K48&amp;","</f>
+        <v xml:space="preserve">    [constFactoreVJ] = &amp;const_JEv,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="B49" s="44"/>
+      <c r="C49" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="102" t="s">
+        <v>273</v>
+      </c>
+      <c r="E49" s="52" t="str">
+        <f>VLOOKUP(A49,Factors!D:N,10,0)</f>
+        <v>multiply</v>
+      </c>
+      <c r="F49" s="54" t="str">
+        <f t="shared" si="0"/>
+        <v>"J" STD_RIGHT_ARROW "eV"</v>
+      </c>
+      <c r="G49" s="54" t="str">
+        <f t="shared" si="1"/>
+        <v>"J" STD_RIGHT_ARROW</v>
+      </c>
+      <c r="H49" s="30" t="str">
+        <f t="shared" si="24"/>
+        <v>/* NNNN */  UNIT_CONV(constFactorJeV,           multiply,      "J" STD_RIGHT_ARROW "eV",                                    "J" STD_RIGHT_ARROW                                         ),</v>
+      </c>
+      <c r="I49" s="52">
+        <f>VLOOKUP(A49,Factors!D:G,4,0)</f>
+        <v>6.2415090744607631E+18</v>
+      </c>
+      <c r="J49" s="52" t="str">
+        <f t="shared" si="25"/>
+        <v>6.241509074460760000000000000000000000000000000000000000e+18</v>
+      </c>
+      <c r="K49" s="55" t="str">
+        <f>VLOOKUP(A49,Factors!D:N,11,0)</f>
+        <v>JEv</v>
+      </c>
+      <c r="L49" s="31" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">  generateConstantArray("JEv",           "+6.241509074460760000000000000000000000000000000000000000e+18");</v>
+      </c>
+      <c r="N49" s="41" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">    [constFactorJeV] = &amp;const_JEv,</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
+    <row r="52" spans="1:14">
+      <c r="A52" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B51">
-    <sortCondition ref="A4:A51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:B53">
+    <sortCondition ref="A4:A53"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4418,7 +4548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAAB5F5-5A0E-F540-8CD7-68987B744E5F}">
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -5104,14 +5234,24 @@
       <c r="K23" s="25"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="C24" s="51"/>
-      <c r="F24" s="34"/>
+      <c r="C24" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" s="34">
+        <f>1.602176634E-19</f>
+        <v>1.6021766339999999E-19</v>
+      </c>
       <c r="G24" s="65"/>
       <c r="J24" s="24"/>
       <c r="K24" s="25"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="F25" s="1"/>
+      <c r="C25" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
       <c r="H25" s="61">
         <f xml:space="preserve"> 568.26125 / 20</f>
         <v>28.413062500000002</v>
@@ -5197,7 +5337,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="36">
-        <f t="shared" ref="F29:F73" si="7">H29/I29</f>
+        <f t="shared" ref="F29:F75" si="7">H29/I29</f>
         <v>2.1133764188651875E-3</v>
       </c>
       <c r="G29" s="38">
@@ -6784,15 +6924,15 @@
         <v>1</v>
       </c>
       <c r="I62" s="9">
-        <f t="shared" ref="I62:I73" si="27" xml:space="preserve"> VLOOKUP(C62,units,4,0)</f>
+        <f t="shared" ref="I62:I75" si="27" xml:space="preserve"> VLOOKUP(C62,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
       <c r="J62" t="str">
-        <f t="shared" ref="J62:J73" si="28">PROPER(B62)&amp;PROPER(C62)</f>
+        <f t="shared" ref="J62:J75" si="28">PROPER(B62)&amp;PROPER(C62)</f>
         <v>MlIn3</v>
       </c>
       <c r="K62" t="str">
-        <f t="shared" ref="K62:K73" si="29">"constFactor"&amp;J62</f>
+        <f t="shared" ref="K62:K75" si="29">"constFactor"&amp;J62</f>
         <v>constFactorMlIn3</v>
       </c>
       <c r="M62" s="38" t="str">
@@ -6806,15 +6946,15 @@
     </row>
     <row r="63" spans="1:14" ht="18">
       <c r="A63" s="50" t="str">
-        <f t="shared" ref="A63:A73" si="30">MID(D63,5,99)</f>
+        <f t="shared" ref="A63:A75" si="30">MID(D63,5,99)</f>
         <v>IN3toML</v>
       </c>
       <c r="B63" s="51" t="str">
-        <f t="shared" ref="B63:B73" si="31">MID(A63,1,SEARCH("to",A63)-1)</f>
+        <f t="shared" ref="B63:B65" si="31">MID(A63,1,SEARCH("to",A63)-1)</f>
         <v>IN3</v>
       </c>
       <c r="C63" s="51" t="str">
-        <f t="shared" ref="C63:C73" si="32">MID(A63,SEARCH("to",A63)+2,99)</f>
+        <f t="shared" ref="C63:C65" si="32">MID(A63,SEARCH("to",A63)+2,99)</f>
         <v>ML</v>
       </c>
       <c r="D63" s="47" t="s">
@@ -6832,7 +6972,7 @@
         <v>16.387063999999999</v>
       </c>
       <c r="H63" s="9">
-        <f t="shared" ref="H63:H73" si="33" xml:space="preserve"> VLOOKUP(B63,units,4,0)</f>
+        <f t="shared" ref="H63:H75" si="33" xml:space="preserve"> VLOOKUP(B63,units,4,0)</f>
         <v>16.387063999999999</v>
       </c>
       <c r="I63" s="9">
@@ -7174,11 +7314,11 @@
         <v>GLUKtoFZUK</v>
       </c>
       <c r="B70" s="51" t="str">
-        <f t="shared" ref="B70:B73" si="42">MID(A70,1,SEARCH("to",A70)-1)</f>
+        <f t="shared" ref="B70:B75" si="42">MID(A70,1,SEARCH("to",A70)-1)</f>
         <v>GLUK</v>
       </c>
       <c r="C70" s="51" t="str">
-        <f t="shared" ref="C70:C73" si="43">MID(A70,SEARCH("to",A70)+2,99)</f>
+        <f t="shared" ref="C70:C75" si="43">MID(A70,SEARCH("to",A70)+2,99)</f>
         <v>FZUK</v>
       </c>
       <c r="D70" s="97" t="s">
@@ -7270,15 +7410,15 @@
     </row>
     <row r="72" spans="1:14" ht="18">
       <c r="A72" s="50" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="A72:A73" si="44">MID(D72,5,99)</f>
         <v>GLUStoFZUS</v>
       </c>
       <c r="B72" s="51" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="B72:B73" si="45">MID(A72,1,SEARCH("to",A72)-1)</f>
         <v>GLUS</v>
       </c>
       <c r="C72" s="51" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="C72:C73" si="46">MID(A72,SEARCH("to",A72)+2,99)</f>
         <v>FZUS</v>
       </c>
       <c r="D72" s="97" t="s">
@@ -7286,7 +7426,7 @@
       </c>
       <c r="E72" s="48"/>
       <c r="F72" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F72:F73" si="47">H72/I72</f>
         <v>128</v>
       </c>
       <c r="G72" s="39">
@@ -7294,19 +7434,19 @@
         <v>128</v>
       </c>
       <c r="H72" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="H72:H73" si="48" xml:space="preserve"> VLOOKUP(B72,units,4,0)</f>
         <v>3785.4117839999999</v>
       </c>
       <c r="I72" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="I72:I73" si="49" xml:space="preserve"> VLOOKUP(C72,units,4,0)</f>
         <v>29.573529562499999</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="J72:J73" si="50">PROPER(B72)&amp;PROPER(C72)</f>
         <v>GlusFzus</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="K72:K73" si="51">"constFactor"&amp;J72</f>
         <v>constFactorGlusFzus</v>
       </c>
       <c r="M72" s="39" t="str">
@@ -7320,15 +7460,15 @@
     </row>
     <row r="73" spans="1:14" ht="19" thickBot="1">
       <c r="A73" s="50" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="44"/>
         <v>FZUStoGLUS</v>
       </c>
       <c r="B73" s="51" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="45"/>
         <v>FZUS</v>
       </c>
       <c r="C73" s="51" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>GLUS</v>
       </c>
       <c r="D73" s="98" t="s">
@@ -7336,7 +7476,7 @@
       </c>
       <c r="E73" s="49"/>
       <c r="F73" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="47"/>
         <v>7.8125E-3</v>
       </c>
       <c r="G73" s="39">
@@ -7344,19 +7484,19 @@
         <v>128</v>
       </c>
       <c r="H73" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="48"/>
         <v>29.573529562499999</v>
       </c>
       <c r="I73" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="49"/>
         <v>3785.4117839999999</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="50"/>
         <v>FzusGlus</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="51"/>
         <v>constFactorFzusGlus</v>
       </c>
       <c r="M73" s="39" t="str">
@@ -7366,6 +7506,110 @@
       <c r="N73" s="39" t="str">
         <f>IF(M73="multiply",PROPER(B73)&amp;PROPER(C73),J72)</f>
         <v>GlusFzus</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="18">
+      <c r="A74" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>EVtoJ</v>
+      </c>
+      <c r="B74" s="51" t="str">
+        <f t="shared" si="42"/>
+        <v>EV</v>
+      </c>
+      <c r="C74" s="51" t="str">
+        <f t="shared" si="43"/>
+        <v>J</v>
+      </c>
+      <c r="D74" s="101" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="F74" s="36">
+        <f t="shared" si="7"/>
+        <v>1.6021766339999999E-19</v>
+      </c>
+      <c r="G74" s="39">
+        <f>IF(M74="multiply",F74,F75)</f>
+        <v>6.2415090744607631E+18</v>
+      </c>
+      <c r="H74" s="9">
+        <f t="shared" si="33"/>
+        <v>1.6021766339999999E-19</v>
+      </c>
+      <c r="I74" s="9">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="28"/>
+        <v>EvJ</v>
+      </c>
+      <c r="K74" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorEvJ</v>
+      </c>
+      <c r="M74" s="39" t="str">
+        <f>IF(H74&gt;I74,"multiply","  divide")</f>
+        <v xml:space="preserve">  divide</v>
+      </c>
+      <c r="N74" s="39" t="str">
+        <f>IF(M74="multiply",PROPER(B74)&amp;PROPER(C74),J75)</f>
+        <v>JEv</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="18">
+      <c r="A75" s="50" t="str">
+        <f t="shared" si="30"/>
+        <v>JtoEV</v>
+      </c>
+      <c r="B75" s="51" t="str">
+        <f t="shared" si="42"/>
+        <v>J</v>
+      </c>
+      <c r="C75" s="51" t="str">
+        <f t="shared" si="43"/>
+        <v>EV</v>
+      </c>
+      <c r="D75" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="E75" s="48" t="s">
+        <v>276</v>
+      </c>
+      <c r="F75" s="36">
+        <f t="shared" si="7"/>
+        <v>6.2415090744607631E+18</v>
+      </c>
+      <c r="G75" s="39">
+        <f>IF(M75="multiply",F75,F74)</f>
+        <v>6.2415090744607631E+18</v>
+      </c>
+      <c r="H75" s="9">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="I75" s="9">
+        <f t="shared" si="27"/>
+        <v>1.6021766339999999E-19</v>
+      </c>
+      <c r="J75" t="str">
+        <f t="shared" si="28"/>
+        <v>JEv</v>
+      </c>
+      <c r="K75" t="str">
+        <f t="shared" si="29"/>
+        <v>constFactorJEv</v>
+      </c>
+      <c r="M75" s="39" t="str">
+        <f>IF(M74="multiply","  divide","multiply")</f>
+        <v>multiply</v>
+      </c>
+      <c r="N75" s="39" t="str">
+        <f>IF(M75="multiply",PROPER(B75)&amp;PROPER(C75),J74)</f>
+        <v>JEv</v>
       </c>
     </row>
   </sheetData>
@@ -7524,7 +7768,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AF49E5-C5CF-EF45-BD21-7588D88F54A2}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -7915,6 +8159,22 @@
         <v>269</v>
       </c>
     </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="101" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="B49" t="s">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
